--- a/financials/PNJ/PNJ.xlsx
+++ b/financials/PNJ/PNJ.xlsx
@@ -11,6 +11,8 @@
     <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Dự phóng tăng trưởng" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,13 +21,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="167" formatCode="0.00\x"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="169" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -82,6 +86,12 @@
     </font>
     <font>
       <name val="Tahoma"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
       <charset val="1"/>
       <family val="2"/>
       <color rgb="FF008000"/>
@@ -92,11 +102,50 @@
       <charset val="1"/>
       <family val="2"/>
       <b val="1"/>
+      <color rgb="FF008000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF7030A0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
       <color theme="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <color rgb="FF7030A0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -106,6 +155,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.7999816888943144"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -160,24 +215,20 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color auto="1"/>
       </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -187,35 +238,56 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="6" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="41" fontId="14" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="41" fontId="15" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="41" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
@@ -234,6 +306,14 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6603,14 +6683,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:K86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38.33203125" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="3" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="38.375" customWidth="1" min="1" max="1"/>
+    <col width="18.25" customWidth="1" min="2" max="2"/>
+    <col width="20.5" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6651,6 +6729,12 @@
         <f>balance_sheet!I1</f>
         <v/>
       </c>
+      <c r="J1" s="6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K1" s="6" t="n">
+        <v>2027</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -6664,31 +6748,39 @@
         </is>
       </c>
       <c r="C2" s="8">
-        <f>IFERROR(C$39/((C$24+B$24)/2),"n/a")</f>
+        <f>IFERROR(C$52/((C$39+B$39)/2),"n/a")</f>
         <v/>
       </c>
       <c r="D2" s="8">
-        <f>IFERROR(D$39/((D$24+C$24)/2),"n/a")</f>
+        <f>IFERROR(D$52/((D$39+C$39)/2),"n/a")</f>
         <v/>
       </c>
       <c r="E2" s="8">
-        <f>IFERROR(E$39/((E$24+D$24)/2),"n/a")</f>
+        <f>IFERROR(E$52/((E$39+D$39)/2),"n/a")</f>
         <v/>
       </c>
       <c r="F2" s="8">
-        <f>IFERROR(F$39/((F$24+E$24)/2),"n/a")</f>
+        <f>IFERROR(F$52/((F$39+E$39)/2),"n/a")</f>
         <v/>
       </c>
       <c r="G2" s="8">
-        <f>IFERROR(G$39/((G$24+F$24)/2),"n/a")</f>
+        <f>IFERROR(G$52/((G$39+F$39)/2),"n/a")</f>
         <v/>
       </c>
       <c r="H2" s="8">
-        <f>IFERROR(H$39/((H$24+G$24)/2),"n/a")</f>
+        <f>IFERROR(H$52/((H$39+G$39)/2),"n/a")</f>
         <v/>
       </c>
       <c r="I2" s="8">
-        <f>IFERROR(I$39/((I$24+H$24)/2),"n/a")</f>
+        <f>IFERROR(I$52/((I$39+H$39)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="J2" s="8">
+        <f>IFERROR(J$52/((J$39+I$39)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="K2" s="8">
+        <f>IFERROR(K$52/((K$39+J$39)/2),"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6704,31 +6796,31 @@
         </is>
       </c>
       <c r="C3" s="8">
-        <f>IFERROR(C$38/((C$25+B$25)/2),"n/a")</f>
+        <f>IFERROR(C$51/((C$31+B$31)/2),"n/a")</f>
         <v/>
       </c>
       <c r="D3" s="8">
-        <f>IFERROR(D$38/((D$25+C$25)/2),"n/a")</f>
+        <f>IFERROR(D$51/((D$31+C$31)/2),"n/a")</f>
         <v/>
       </c>
       <c r="E3" s="8">
-        <f>IFERROR(E$38/((E$25+D$25)/2),"n/a")</f>
+        <f>IFERROR(E$51/((E$31+D$31)/2),"n/a")</f>
         <v/>
       </c>
       <c r="F3" s="8">
-        <f>IFERROR(F$38/((F$25+E$25)/2),"n/a")</f>
+        <f>IFERROR(F$51/((F$31+E$31)/2),"n/a")</f>
         <v/>
       </c>
       <c r="G3" s="8">
-        <f>IFERROR(G$38/((G$25+F$25)/2),"n/a")</f>
+        <f>IFERROR(G$51/((G$31+F$31)/2),"n/a")</f>
         <v/>
       </c>
       <c r="H3" s="8">
-        <f>IFERROR(H$38/((H$25+G$25)/2),"n/a")</f>
+        <f>IFERROR(H$51/((H$31+G$31)/2),"n/a")</f>
         <v/>
       </c>
       <c r="I3" s="8">
-        <f>IFERROR(I$38/((I$25+H$25)/2),"n/a")</f>
+        <f>IFERROR(I$51/((I$31+H$31)/2),"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6744,31 +6836,39 @@
         </is>
       </c>
       <c r="C4" s="8">
-        <f>IFERROR((C$39-B$39)/ABS(B$39),"n/a")</f>
+        <f>IFERROR((C$52-B$52)/ABS(B$52),"n/a")</f>
         <v/>
       </c>
       <c r="D4" s="8">
-        <f>IFERROR((D$39-C$39)/ABS(C$39),"n/a")</f>
+        <f>IFERROR((D$52-C$52)/ABS(C$52),"n/a")</f>
         <v/>
       </c>
       <c r="E4" s="8">
-        <f>IFERROR((E$39-D$39)/ABS(D$39),"n/a")</f>
+        <f>IFERROR((E$52-D$52)/ABS(D$52),"n/a")</f>
         <v/>
       </c>
       <c r="F4" s="8">
-        <f>IFERROR((F$39-E$39)/ABS(E$39),"n/a")</f>
+        <f>IFERROR((F$52-E$52)/ABS(E$52),"n/a")</f>
         <v/>
       </c>
       <c r="G4" s="8">
-        <f>IFERROR((G$39-F$39)/ABS(F$39),"n/a")</f>
+        <f>IFERROR((G$52-F$52)/ABS(F$52),"n/a")</f>
         <v/>
       </c>
       <c r="H4" s="8">
-        <f>IFERROR((H$39-G$39)/ABS(G$39),"n/a")</f>
+        <f>IFERROR((H$52-G$52)/ABS(G$52),"n/a")</f>
         <v/>
       </c>
       <c r="I4" s="8">
-        <f>IFERROR((I$39-H$39)/ABS(H$39),"n/a")</f>
+        <f>IFERROR((I$52-H$52)/ABS(H$52),"n/a")</f>
+        <v/>
+      </c>
+      <c r="J4" s="8">
+        <f>IFERROR((J$52-I$52)/ABS(I$52),"n/a")</f>
+        <v/>
+      </c>
+      <c r="K4" s="8">
+        <f>IFERROR((K$52-J$52)/ABS(J$52),"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6784,31 +6884,39 @@
         </is>
       </c>
       <c r="C5" s="8">
-        <f>IFERROR((C$31-B$31)/ABS(B$31),"n/a")</f>
+        <f>IFERROR((C$43-B$43)/ABS(B$43),"n/a")</f>
         <v/>
       </c>
       <c r="D5" s="8">
-        <f>IFERROR((D$31-C$31)/ABS(C$31),"n/a")</f>
+        <f>IFERROR((D$43-C$43)/ABS(C$43),"n/a")</f>
         <v/>
       </c>
       <c r="E5" s="8">
-        <f>IFERROR((E$31-D$31)/ABS(D$31),"n/a")</f>
+        <f>IFERROR((E$43-D$43)/ABS(D$43),"n/a")</f>
         <v/>
       </c>
       <c r="F5" s="8">
-        <f>IFERROR((F$31-E$31)/ABS(E$31),"n/a")</f>
+        <f>IFERROR((F$43-E$43)/ABS(E$43),"n/a")</f>
         <v/>
       </c>
       <c r="G5" s="8">
-        <f>IFERROR((G$31-F$31)/ABS(F$31),"n/a")</f>
+        <f>IFERROR((G$43-F$43)/ABS(F$43),"n/a")</f>
         <v/>
       </c>
       <c r="H5" s="8">
-        <f>IFERROR((H$31-G$31)/ABS(G$31),"n/a")</f>
+        <f>IFERROR((H$43-G$43)/ABS(G$43),"n/a")</f>
         <v/>
       </c>
       <c r="I5" s="8">
-        <f>IFERROR((I$31-H$31)/ABS(H$31),"n/a")</f>
+        <f>IFERROR((I$43-H$43)/ABS(H$43),"n/a")</f>
+        <v/>
+      </c>
+      <c r="J5" s="8">
+        <f>IFERROR((J$43-I$43)/ABS(I$43),"n/a")</f>
+        <v/>
+      </c>
+      <c r="K5" s="8">
+        <f>IFERROR((K$43-J$43)/ABS(J$43),"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6819,35 +6927,35 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <f>IFERROR(B$33/B$31,"n/a")</f>
+        <f>IFERROR(B$45/B$43,"n/a")</f>
         <v/>
       </c>
       <c r="C6" s="8">
-        <f>IFERROR(C$33/C$31,"n/a")</f>
+        <f>IFERROR(C$45/C$43,"n/a")</f>
         <v/>
       </c>
       <c r="D6" s="8">
-        <f>IFERROR(D$33/D$31,"n/a")</f>
+        <f>IFERROR(D$45/D$43,"n/a")</f>
         <v/>
       </c>
       <c r="E6" s="8">
-        <f>IFERROR(E$33/E$31,"n/a")</f>
+        <f>IFERROR(E$45/E$43,"n/a")</f>
         <v/>
       </c>
       <c r="F6" s="8">
-        <f>IFERROR(F$33/F$31,"n/a")</f>
+        <f>IFERROR(F$45/F$43,"n/a")</f>
         <v/>
       </c>
       <c r="G6" s="8">
-        <f>IFERROR(G$33/G$31,"n/a")</f>
+        <f>IFERROR(G$45/G$43,"n/a")</f>
         <v/>
       </c>
       <c r="H6" s="8">
-        <f>IFERROR(H$33/H$31,"n/a")</f>
+        <f>IFERROR(H$45/H$43,"n/a")</f>
         <v/>
       </c>
       <c r="I6" s="8">
-        <f>IFERROR(I$33/I$31,"n/a")</f>
+        <f>IFERROR(I$45/I$43,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6858,35 +6966,43 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>IFERROR(B$38/B$31,"n/a")</f>
+        <f>IFERROR(B$52/B$43,"n/a")</f>
         <v/>
       </c>
       <c r="C7" s="8">
-        <f>IFERROR(C$38/C$31,"n/a")</f>
+        <f>IFERROR(C$52/C$43,"n/a")</f>
         <v/>
       </c>
       <c r="D7" s="8">
-        <f>IFERROR(D$38/D$31,"n/a")</f>
+        <f>IFERROR(D$52/D$43,"n/a")</f>
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>IFERROR(E$38/E$31,"n/a")</f>
+        <f>IFERROR(E$52/E$43,"n/a")</f>
         <v/>
       </c>
       <c r="F7" s="8">
-        <f>IFERROR(F$38/F$31,"n/a")</f>
+        <f>IFERROR(F$52/F$43,"n/a")</f>
         <v/>
       </c>
       <c r="G7" s="8">
-        <f>IFERROR(G$38/G$31,"n/a")</f>
+        <f>IFERROR(G$52/G$43,"n/a")</f>
         <v/>
       </c>
       <c r="H7" s="8">
-        <f>IFERROR(H$38/H$31,"n/a")</f>
+        <f>IFERROR(H$52/H$43,"n/a")</f>
         <v/>
       </c>
       <c r="I7" s="8">
-        <f>IFERROR(I$38/I$31,"n/a")</f>
+        <f>IFERROR(I$52/I$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J7" s="8">
+        <f>IFERROR(J$52/J$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="K7" s="8">
+        <f>IFERROR(K$52/K$43,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6897,35 +7013,35 @@
         </is>
       </c>
       <c r="B8" s="9">
-        <f>IFERROR((B$29+B$30)/B$24,"n/a")</f>
+        <f>IFERROR((B$34+B$36)/B$39,"n/a")</f>
         <v/>
       </c>
       <c r="C8" s="9">
-        <f>IFERROR((C$29+C$30)/C$24,"n/a")</f>
+        <f>IFERROR((C$34+C$36)/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D8" s="9">
-        <f>IFERROR((D$29+D$30)/D$24,"n/a")</f>
+        <f>IFERROR((D$34+D$36)/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E8" s="9">
-        <f>IFERROR((E$29+E$30)/E$24,"n/a")</f>
+        <f>IFERROR((E$34+E$36)/E$39,"n/a")</f>
         <v/>
       </c>
       <c r="F8" s="9">
-        <f>IFERROR((F$29+F$30)/F$24,"n/a")</f>
+        <f>IFERROR((F$34+F$36)/F$39,"n/a")</f>
         <v/>
       </c>
       <c r="G8" s="9">
-        <f>IFERROR((G$29+G$30)/G$24,"n/a")</f>
+        <f>IFERROR((G$34+G$36)/G$39,"n/a")</f>
         <v/>
       </c>
       <c r="H8" s="9">
-        <f>IFERROR((H$29+H$30)/H$24,"n/a")</f>
+        <f>IFERROR((H$34+H$36)/H$39,"n/a")</f>
         <v/>
       </c>
       <c r="I8" s="9">
-        <f>IFERROR((I$29+I$30)/I$24,"n/a")</f>
+        <f>IFERROR((I$34+I$36)/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6936,35 +7052,35 @@
         </is>
       </c>
       <c r="B9" s="9">
-        <f>IFERROR(B$30/B$24,"n/a")</f>
+        <f>IFERROR(B$36/B$39,"n/a")</f>
         <v/>
       </c>
       <c r="C9" s="9">
-        <f>IFERROR(C$30/C$24,"n/a")</f>
+        <f>IFERROR(C$36/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D9" s="9">
-        <f>IFERROR(D$30/D$24,"n/a")</f>
+        <f>IFERROR(D$36/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E9" s="9">
-        <f>IFERROR(E$30/E$24,"n/a")</f>
+        <f>IFERROR(E$36/E$39,"n/a")</f>
         <v/>
       </c>
       <c r="F9" s="9">
-        <f>IFERROR(F$30/F$24,"n/a")</f>
+        <f>IFERROR(F$36/F$39,"n/a")</f>
         <v/>
       </c>
       <c r="G9" s="9">
-        <f>IFERROR(G$30/G$24,"n/a")</f>
+        <f>IFERROR(G$36/G$39,"n/a")</f>
         <v/>
       </c>
       <c r="H9" s="9">
-        <f>IFERROR(H$30/H$24,"n/a")</f>
+        <f>IFERROR(H$36/H$39,"n/a")</f>
         <v/>
       </c>
       <c r="I9" s="9">
-        <f>IFERROR(I$30/I$24,"n/a")</f>
+        <f>IFERROR(I$36/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6975,35 +7091,35 @@
         </is>
       </c>
       <c r="B10" s="9">
-        <f>IFERROR(B$29/B$24,"n/a")</f>
+        <f>IFERROR(B$34/B$39,"n/a")</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(C$29/C$24,"n/a")</f>
+        <f>IFERROR(C$34/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>IFERROR(D$29/D$24,"n/a")</f>
+        <f>IFERROR(D$34/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E10" s="9">
-        <f>IFERROR(E$29/E$24,"n/a")</f>
+        <f>IFERROR(E$34/E$39,"n/a")</f>
         <v/>
       </c>
       <c r="F10" s="9">
-        <f>IFERROR(F$29/F$24,"n/a")</f>
+        <f>IFERROR(F$34/F$39,"n/a")</f>
         <v/>
       </c>
       <c r="G10" s="9">
-        <f>IFERROR(G$29/G$24,"n/a")</f>
+        <f>IFERROR(G$34/G$39,"n/a")</f>
         <v/>
       </c>
       <c r="H10" s="9">
-        <f>IFERROR(H$29/H$24,"n/a")</f>
+        <f>IFERROR(H$34/H$39,"n/a")</f>
         <v/>
       </c>
       <c r="I10" s="9">
-        <f>IFERROR(I$29/I$24,"n/a")</f>
+        <f>IFERROR(I$34/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7014,35 +7130,35 @@
         </is>
       </c>
       <c r="B11" s="9">
-        <f>IFERROR(B$26/B$24,"n/a")</f>
+        <f>IFERROR(B$38/B$39,"n/a")</f>
         <v/>
       </c>
       <c r="C11" s="9">
-        <f>IFERROR(C$26/C$24,"n/a")</f>
+        <f>IFERROR(C$38/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D11" s="9">
-        <f>IFERROR(D$26/D$24,"n/a")</f>
+        <f>IFERROR(D$38/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E11" s="9">
-        <f>IFERROR(E$26/E$24,"n/a")</f>
+        <f>IFERROR(E$38/E$39,"n/a")</f>
         <v/>
       </c>
       <c r="F11" s="9">
-        <f>IFERROR(F$26/F$24,"n/a")</f>
+        <f>IFERROR(F$38/F$39,"n/a")</f>
         <v/>
       </c>
       <c r="G11" s="9">
-        <f>IFERROR(G$26/G$24,"n/a")</f>
+        <f>IFERROR(G$38/G$39,"n/a")</f>
         <v/>
       </c>
       <c r="H11" s="9">
-        <f>IFERROR(H$26/H$24,"n/a")</f>
+        <f>IFERROR(H$38/H$39,"n/a")</f>
         <v/>
       </c>
       <c r="I11" s="9">
-        <f>IFERROR(I$26/I$24,"n/a")</f>
+        <f>IFERROR(I$38/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7053,35 +7169,35 @@
         </is>
       </c>
       <c r="B12" s="9">
-        <f>IFERROR(B$28/B$24,"n/a")</f>
+        <f>IFERROR(B$37/B$39,"n/a")</f>
         <v/>
       </c>
       <c r="C12" s="9">
-        <f>IFERROR(C$28/C$24,"n/a")</f>
+        <f>IFERROR(C$37/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D12" s="9">
-        <f>IFERROR(D$28/D$24,"n/a")</f>
+        <f>IFERROR(D$37/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E12" s="9">
-        <f>IFERROR(E$28/E$24,"n/a")</f>
+        <f>IFERROR(E$37/E$39,"n/a")</f>
         <v/>
       </c>
       <c r="F12" s="9">
-        <f>IFERROR(F$28/F$24,"n/a")</f>
+        <f>IFERROR(F$37/F$39,"n/a")</f>
         <v/>
       </c>
       <c r="G12" s="9">
-        <f>IFERROR(G$28/G$24,"n/a")</f>
+        <f>IFERROR(G$37/G$39,"n/a")</f>
         <v/>
       </c>
       <c r="H12" s="9">
-        <f>IFERROR(H$28/H$24,"n/a")</f>
+        <f>IFERROR(H$37/H$39,"n/a")</f>
         <v/>
       </c>
       <c r="I12" s="9">
-        <f>IFERROR(I$28/I$24,"n/a")</f>
+        <f>IFERROR(I$37/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7092,35 +7208,35 @@
         </is>
       </c>
       <c r="B13" s="9">
-        <f>IFERROR(B$27/B$24,"n/a")</f>
+        <f>IFERROR(B$35/B$39,"n/a")</f>
         <v/>
       </c>
       <c r="C13" s="9">
-        <f>IFERROR(C$27/C$24,"n/a")</f>
+        <f>IFERROR(C$35/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D13" s="9">
-        <f>IFERROR(D$27/D$24,"n/a")</f>
+        <f>IFERROR(D$35/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E13" s="9">
-        <f>IFERROR(E$27/E$24,"n/a")</f>
+        <f>IFERROR(E$35/E$39,"n/a")</f>
         <v/>
       </c>
       <c r="F13" s="9">
-        <f>IFERROR(F$27/F$24,"n/a")</f>
+        <f>IFERROR(F$35/F$39,"n/a")</f>
         <v/>
       </c>
       <c r="G13" s="9">
-        <f>IFERROR(G$27/G$24,"n/a")</f>
+        <f>IFERROR(G$35/G$39,"n/a")</f>
         <v/>
       </c>
       <c r="H13" s="9">
-        <f>IFERROR(H$27/H$24,"n/a")</f>
+        <f>IFERROR(H$35/H$39,"n/a")</f>
         <v/>
       </c>
       <c r="I13" s="9">
-        <f>IFERROR(I$27/I$24,"n/a")</f>
+        <f>IFERROR(I$35/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7131,35 +7247,35 @@
         </is>
       </c>
       <c r="B14" s="8">
-        <f>IFERROR((ABS(B$34)+ABS(B$35))/B$33,"n/a")</f>
+        <f>IFERROR((ABS(B$46)+ABS(B$47))/B$45,"n/a")</f>
         <v/>
       </c>
       <c r="C14" s="8">
-        <f>IFERROR((ABS(C$34)+ABS(C$35))/C$33,"n/a")</f>
+        <f>IFERROR((ABS(C$46)+ABS(C$47))/C$45,"n/a")</f>
         <v/>
       </c>
       <c r="D14" s="8">
-        <f>IFERROR((ABS(D$34)+ABS(D$35))/D$33,"n/a")</f>
+        <f>IFERROR((ABS(D$46)+ABS(D$47))/D$45,"n/a")</f>
         <v/>
       </c>
       <c r="E14" s="8">
-        <f>IFERROR((ABS(E$34)+ABS(E$35))/E$33,"n/a")</f>
+        <f>IFERROR((ABS(E$46)+ABS(E$47))/E$45,"n/a")</f>
         <v/>
       </c>
       <c r="F14" s="8">
-        <f>IFERROR((ABS(F$34)+ABS(F$35))/F$33,"n/a")</f>
+        <f>IFERROR((ABS(F$46)+ABS(F$47))/F$45,"n/a")</f>
         <v/>
       </c>
       <c r="G14" s="8">
-        <f>IFERROR((ABS(G$34)+ABS(G$35))/G$33,"n/a")</f>
+        <f>IFERROR((ABS(G$46)+ABS(G$47))/G$45,"n/a")</f>
         <v/>
       </c>
       <c r="H14" s="8">
-        <f>IFERROR((ABS(H$34)+ABS(H$35))/H$33,"n/a")</f>
+        <f>IFERROR((ABS(H$46)+ABS(H$47))/H$45,"n/a")</f>
         <v/>
       </c>
       <c r="I14" s="8">
-        <f>IFERROR((ABS(I$34)+ABS(I$35))/I$33,"n/a")</f>
+        <f>IFERROR((ABS(I$46)+ABS(I$47))/I$45,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7170,35 +7286,35 @@
         </is>
       </c>
       <c r="B15" s="8">
-        <f>IFERROR(ABS(B$37)/B$36,"n/a")</f>
+        <f>IFERROR(ABS(B$49)/B$48,"n/a")</f>
         <v/>
       </c>
       <c r="C15" s="8">
-        <f>IFERROR(ABS(C$37)/C$36,"n/a")</f>
+        <f>IFERROR(ABS(C$49)/C$48,"n/a")</f>
         <v/>
       </c>
       <c r="D15" s="8">
-        <f>IFERROR(ABS(D$37)/D$36,"n/a")</f>
+        <f>IFERROR(ABS(D$49)/D$48,"n/a")</f>
         <v/>
       </c>
       <c r="E15" s="8">
-        <f>IFERROR(ABS(E$37)/E$36,"n/a")</f>
+        <f>IFERROR(ABS(E$49)/E$48,"n/a")</f>
         <v/>
       </c>
       <c r="F15" s="8">
-        <f>IFERROR(ABS(F$37)/F$36,"n/a")</f>
+        <f>IFERROR(ABS(F$49)/F$48,"n/a")</f>
         <v/>
       </c>
       <c r="G15" s="8">
-        <f>IFERROR(ABS(G$37)/G$36,"n/a")</f>
+        <f>IFERROR(ABS(G$49)/G$48,"n/a")</f>
         <v/>
       </c>
       <c r="H15" s="8">
-        <f>IFERROR(ABS(H$37)/H$36,"n/a")</f>
+        <f>IFERROR(ABS(H$49)/H$48,"n/a")</f>
         <v/>
       </c>
       <c r="I15" s="8">
-        <f>IFERROR(ABS(I$37)/I$36,"n/a")</f>
+        <f>IFERROR(ABS(I$49)/I$48,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7214,31 +7330,31 @@
         </is>
       </c>
       <c r="C16" s="12">
-        <f>IFERROR(((C$41+B$41)/2)/ABS(C$32)*365,"n/a")</f>
+        <f>IFERROR(((C$33+B$33)/2)/ABS(C$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="D16" s="12">
-        <f>IFERROR(((D$41+C$41)/2)/ABS(D$32)*365,"n/a")</f>
+        <f>IFERROR(((D$33+C$33)/2)/ABS(D$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="E16" s="12">
-        <f>IFERROR(((E$41+D$41)/2)/ABS(E$32)*365,"n/a")</f>
+        <f>IFERROR(((E$33+D$33)/2)/ABS(E$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="F16" s="12">
-        <f>IFERROR(((F$41+E$41)/2)/ABS(F$32)*365,"n/a")</f>
+        <f>IFERROR(((F$33+E$33)/2)/ABS(F$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="G16" s="12">
-        <f>IFERROR(((G$41+F$41)/2)/ABS(G$32)*365,"n/a")</f>
+        <f>IFERROR(((G$33+F$33)/2)/ABS(G$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="H16" s="12">
-        <f>IFERROR(((H$41+G$41)/2)/ABS(H$32)*365,"n/a")</f>
+        <f>IFERROR(((H$33+G$33)/2)/ABS(H$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="I16" s="12">
-        <f>IFERROR(((I$41+H$41)/2)/ABS(I$32)*365,"n/a")</f>
+        <f>IFERROR(((I$33+H$33)/2)/ABS(I$44)*365,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7254,31 +7370,31 @@
         </is>
       </c>
       <c r="C17" s="12">
-        <f>IFERROR(((C$40+B$40)/2)/C$31*365,"n/a")</f>
+        <f>IFERROR(((C$27+B$27)/2)/C$43*365,"n/a")</f>
         <v/>
       </c>
       <c r="D17" s="12">
-        <f>IFERROR(((D$40+C$40)/2)/D$31*365,"n/a")</f>
+        <f>IFERROR(((D$27+C$27)/2)/D$43*365,"n/a")</f>
         <v/>
       </c>
       <c r="E17" s="12">
-        <f>IFERROR(((E$40+D$40)/2)/E$31*365,"n/a")</f>
+        <f>IFERROR(((E$27+D$27)/2)/E$43*365,"n/a")</f>
         <v/>
       </c>
       <c r="F17" s="12">
-        <f>IFERROR(((F$40+E$40)/2)/F$31*365,"n/a")</f>
+        <f>IFERROR(((F$27+E$27)/2)/F$43*365,"n/a")</f>
         <v/>
       </c>
       <c r="G17" s="12">
-        <f>IFERROR(((G$40+F$40)/2)/G$31*365,"n/a")</f>
+        <f>IFERROR(((G$27+F$27)/2)/G$43*365,"n/a")</f>
         <v/>
       </c>
       <c r="H17" s="12">
-        <f>IFERROR(((H$40+G$40)/2)/H$31*365,"n/a")</f>
+        <f>IFERROR(((H$27+G$27)/2)/H$43*365,"n/a")</f>
         <v/>
       </c>
       <c r="I17" s="12">
-        <f>IFERROR(((I$40+H$40)/2)/I$31*365,"n/a")</f>
+        <f>IFERROR(((I$27+H$27)/2)/I$43*365,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7294,31 +7410,31 @@
         </is>
       </c>
       <c r="C18" s="12">
-        <f>IFERROR(((C$42+B$42)/2)/ABS(C$32)*365,"n/a")</f>
+        <f>IFERROR(((C$28+B$28)/2)/ABS(C$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="D18" s="12">
-        <f>IFERROR(((D$42+C$42)/2)/ABS(D$32)*365,"n/a")</f>
+        <f>IFERROR(((D$28+C$28)/2)/ABS(D$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="E18" s="12">
-        <f>IFERROR(((E$42+D$42)/2)/ABS(E$32)*365,"n/a")</f>
+        <f>IFERROR(((E$28+D$28)/2)/ABS(E$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="F18" s="12">
-        <f>IFERROR(((F$42+E$42)/2)/ABS(F$32)*365,"n/a")</f>
+        <f>IFERROR(((F$28+E$28)/2)/ABS(F$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="G18" s="12">
-        <f>IFERROR(((G$42+F$42)/2)/ABS(G$32)*365,"n/a")</f>
+        <f>IFERROR(((G$28+F$28)/2)/ABS(G$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="H18" s="12">
-        <f>IFERROR(((H$42+G$42)/2)/ABS(H$32)*365,"n/a")</f>
+        <f>IFERROR(((H$28+G$28)/2)/ABS(H$44)*365,"n/a")</f>
         <v/>
       </c>
       <c r="I18" s="12">
-        <f>IFERROR(((I$42+H$42)/2)/ABS(I$32)*365,"n/a")</f>
+        <f>IFERROR(((I$28+H$28)/2)/ABS(I$44)*365,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7329,35 +7445,35 @@
         </is>
       </c>
       <c r="B19" s="8">
-        <f>IFERROR(B$43/B$25,"n/a")</f>
+        <f>IFERROR(B$26/B$31,"n/a")</f>
         <v/>
       </c>
       <c r="C19" s="8">
-        <f>IFERROR(C$43/C$25,"n/a")</f>
+        <f>IFERROR(C$26/C$31,"n/a")</f>
         <v/>
       </c>
       <c r="D19" s="8">
-        <f>IFERROR(D$43/D$25,"n/a")</f>
+        <f>IFERROR(D$26/D$31,"n/a")</f>
         <v/>
       </c>
       <c r="E19" s="8">
-        <f>IFERROR(E$43/E$25,"n/a")</f>
+        <f>IFERROR(E$26/E$31,"n/a")</f>
         <v/>
       </c>
       <c r="F19" s="8">
-        <f>IFERROR(F$43/F$25,"n/a")</f>
+        <f>IFERROR(F$26/F$31,"n/a")</f>
         <v/>
       </c>
       <c r="G19" s="8">
-        <f>IFERROR(G$43/G$25,"n/a")</f>
+        <f>IFERROR(G$26/G$31,"n/a")</f>
         <v/>
       </c>
       <c r="H19" s="8">
-        <f>IFERROR(H$43/H$25,"n/a")</f>
+        <f>IFERROR(H$26/H$31,"n/a")</f>
         <v/>
       </c>
       <c r="I19" s="8">
-        <f>IFERROR(I$43/I$25,"n/a")</f>
+        <f>IFERROR(I$26/I$31,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7368,35 +7484,35 @@
         </is>
       </c>
       <c r="B20" s="8">
-        <f>IFERROR(B$42/B$25,"n/a")</f>
+        <f>IFERROR(B$28/B$31,"n/a")</f>
         <v/>
       </c>
       <c r="C20" s="8">
-        <f>IFERROR(C$42/C$25,"n/a")</f>
+        <f>IFERROR(C$28/C$31,"n/a")</f>
         <v/>
       </c>
       <c r="D20" s="8">
-        <f>IFERROR(D$42/D$25,"n/a")</f>
+        <f>IFERROR(D$28/D$31,"n/a")</f>
         <v/>
       </c>
       <c r="E20" s="8">
-        <f>IFERROR(E$42/E$25,"n/a")</f>
+        <f>IFERROR(E$28/E$31,"n/a")</f>
         <v/>
       </c>
       <c r="F20" s="8">
-        <f>IFERROR(F$42/F$25,"n/a")</f>
+        <f>IFERROR(F$28/F$31,"n/a")</f>
         <v/>
       </c>
       <c r="G20" s="8">
-        <f>IFERROR(G$42/G$25,"n/a")</f>
+        <f>IFERROR(G$28/G$31,"n/a")</f>
         <v/>
       </c>
       <c r="H20" s="8">
-        <f>IFERROR(H$42/H$25,"n/a")</f>
+        <f>IFERROR(H$28/H$31,"n/a")</f>
         <v/>
       </c>
       <c r="I20" s="8">
-        <f>IFERROR(I$42/I$25,"n/a")</f>
+        <f>IFERROR(I$28/I$31,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7458,1927 +7574,2112 @@
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
+          <t>CĐKT</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="16" t="n"/>
+      <c r="F24" s="16" t="n"/>
+      <c r="G24" s="16" t="n"/>
+      <c r="H24" s="16" t="n"/>
+      <c r="I24" s="16" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="17" t="inlineStr">
         <is>
+          <t>Tài sản</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="16" t="n"/>
+      <c r="F25" s="16" t="n"/>
+      <c r="G25" s="16" t="n"/>
+      <c r="H25" s="16" t="n"/>
+      <c r="I25" s="16" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>Tiền và tương đương tiền</t>
+        </is>
+      </c>
+      <c r="B26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>Phải thu khách hàng</t>
+        </is>
+      </c>
+      <c r="B27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>Hàng tồn kho, ròng</t>
+        </is>
+      </c>
+      <c r="B28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>TÀI SẢN NGẮN HẠN</t>
+        </is>
+      </c>
+      <c r="B29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>GTCL tài sản cố định vô hình</t>
+        </is>
+      </c>
+      <c r="B30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
           <t>TỔNG CỘNG TÀI SẢN</t>
         </is>
       </c>
-      <c r="B25" s="18">
+      <c r="B31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C25" s="18">
+      <c r="C31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D25" s="18">
+      <c r="D31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E25" s="18">
+      <c r="E31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F25" s="18">
+      <c r="F31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G25" s="18">
+      <c r="G31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H25" s="18">
+      <c r="H31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I25" s="18">
+      <c r="I31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>NỢ PHẢI TRẢ</t>
-        </is>
-      </c>
-      <c r="B26" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C26" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D26" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E26" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F26" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G26" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I26" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>Nợ ngắn hạn</t>
-        </is>
-      </c>
-      <c r="B27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>Nợ dài hạn</t>
-        </is>
-      </c>
-      <c r="B28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>Vay ngắn hạn</t>
-        </is>
-      </c>
-      <c r="B29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>Vay dài hạn</t>
-        </is>
-      </c>
-      <c r="B30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>Doanh thu thuần</t>
-        </is>
-      </c>
-      <c r="B31" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C31" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D31" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E31" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F31" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G31" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I31" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
+          <t>Nguồn vốn</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="n"/>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="16" t="n"/>
+      <c r="E32" s="16" t="n"/>
+      <c r="F32" s="16" t="n"/>
+      <c r="G32" s="16" t="n"/>
+      <c r="H32" s="16" t="n"/>
+      <c r="I32" s="16" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>Phải trả người bán</t>
+        </is>
+      </c>
+      <c r="B33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>Vay ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>Nợ ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>Vay dài hạn</t>
+        </is>
+      </c>
+      <c r="B36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>Nợ dài hạn</t>
+        </is>
+      </c>
+      <c r="B37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>NỢ PHẢI TRẢ</t>
+        </is>
+      </c>
+      <c r="B38" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C38" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I38" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="20">
+        <f>I39+0.65*J52</f>
+        <v/>
+      </c>
+      <c r="K39" s="20">
+        <f>J39+0.65*K52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>Tăng VCSH/LN cổ đông cty mẹ</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="n"/>
+      <c r="C40" s="23">
+        <f>(C39-B39)/C52</f>
+        <v/>
+      </c>
+      <c r="D40" s="23">
+        <f>(D39-C39)/D52</f>
+        <v/>
+      </c>
+      <c r="E40" s="23">
+        <f>(E39-D39)/E52</f>
+        <v/>
+      </c>
+      <c r="F40" s="23">
+        <f>(F39-E39)/F52</f>
+        <v/>
+      </c>
+      <c r="G40" s="23">
+        <f>(G39-F39)/G52</f>
+        <v/>
+      </c>
+      <c r="H40" s="23">
+        <f>(H39-G39)/H52</f>
+        <v/>
+      </c>
+      <c r="I40" s="23">
+        <f>(I39-H39)/I52</f>
+        <v/>
+      </c>
+      <c r="J40" s="24" t="n"/>
+      <c r="K40" s="24" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>Lợi ích của cổ đông thiểu số</t>
+        </is>
+      </c>
+      <c r="B41" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C41" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D41" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I41" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J41">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(J$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>Kết quả hoạt động kinh doanh</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>Doanh thu thuần</t>
+        </is>
+      </c>
+      <c r="B43" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C43" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D43" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I43" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J43" s="20" t="n">
+        <v>35676000000000</v>
+      </c>
+      <c r="K43" s="20" t="n">
+        <v>35676000000000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
           <t>Giá vốn hàng bán</t>
         </is>
       </c>
-      <c r="B32" s="18">
+      <c r="B44" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C32" s="18">
+      <c r="C44" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D32" s="18">
+      <c r="D44" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E32" s="18">
+      <c r="E44" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F32" s="18">
+      <c r="F44" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G32" s="18">
+      <c r="G44" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H32" s="18">
+      <c r="H44" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I32" s="18">
+      <c r="I44" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>Lợi nhuận gộp</t>
         </is>
       </c>
-      <c r="B33" s="18">
+      <c r="B45" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C33" s="18">
+      <c r="C45" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D33" s="18">
+      <c r="D45" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E33" s="18">
+      <c r="E45" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F33" s="18">
+      <c r="F45" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G33" s="18">
+      <c r="G45" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H33" s="18">
+      <c r="H45" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I33" s="18">
+      <c r="I45" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="J45" s="20" t="n">
+        <v>9486000000000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="18" t="inlineStr">
         <is>
           <t>Chi phí bán hàng</t>
         </is>
       </c>
-      <c r="B34" s="18">
+      <c r="B46" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C34" s="18">
+      <c r="C46" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D34" s="18">
+      <c r="D46" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E34" s="18">
+      <c r="E46" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F34" s="18">
+      <c r="F46" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G34" s="18">
+      <c r="G46" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H34" s="18">
+      <c r="H46" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I34" s="18">
+      <c r="I46" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="18" t="inlineStr">
         <is>
           <t>Chi phí quản lý doanh nghiệp</t>
         </is>
       </c>
-      <c r="B35" s="18">
+      <c r="B47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C35" s="18">
+      <c r="C47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D35" s="18">
+      <c r="D47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E35" s="18">
+      <c r="E47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F35" s="18">
+      <c r="F47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G35" s="18">
+      <c r="G47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H35" s="18">
+      <c r="H47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I35" s="18">
+      <c r="I47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="18" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) từ hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="B36" s="18">
+      <c r="B48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C36" s="18">
+      <c r="C48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D36" s="18">
+      <c r="D48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E36" s="18">
+      <c r="E48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F36" s="18">
+      <c r="F48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G36" s="18">
+      <c r="G48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H36" s="18">
+      <c r="H48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I36" s="18">
+      <c r="I48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="18" t="inlineStr">
         <is>
           <t>Chi phí lãi vay</t>
         </is>
       </c>
-      <c r="B37" s="18">
+      <c r="B49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C37" s="18">
+      <c r="C49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D37" s="18">
+      <c r="D49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E37" s="18">
+      <c r="E49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F37" s="18">
+      <c r="F49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G37" s="18">
+      <c r="G49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H37" s="18">
+      <c r="H49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I37" s="18">
+      <c r="I49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="18" t="inlineStr">
+        <is>
+          <t>Lãi/(lỗ) trước thuế</t>
+        </is>
+      </c>
+      <c r="B50" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C50" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D50" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E50" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F50" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G50" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I50" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="15" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) thuần sau thuế</t>
         </is>
       </c>
-      <c r="B38" s="18">
+      <c r="B51" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C38" s="18">
+      <c r="C51" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D38" s="18">
+      <c r="D51" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E38" s="18">
+      <c r="E51" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F38" s="18">
+      <c r="F51" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G38" s="18">
+      <c r="G51" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H38" s="18">
+      <c r="H51" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I38" s="18">
+      <c r="I51" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="J51" s="20" t="n">
+        <v>1500000000000</v>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="15" t="inlineStr">
         <is>
           <t>Lợi nhuận của Cổ đông của Công ty mẹ</t>
         </is>
       </c>
-      <c r="B39" s="18">
+      <c r="B52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C39" s="18">
+      <c r="C52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D39" s="18">
+      <c r="D52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E39" s="18">
+      <c r="E52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F39" s="18">
+      <c r="F52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G39" s="18">
+      <c r="G52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H39" s="18">
+      <c r="H52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I39" s="18">
+      <c r="I52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t>Phải thu khách hàng</t>
-        </is>
-      </c>
-      <c r="B40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="17" t="inlineStr">
-        <is>
-          <t>Phải trả người bán</t>
-        </is>
-      </c>
-      <c r="B41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>Hàng tồn kho, ròng</t>
-        </is>
-      </c>
-      <c r="B42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>Tiền và tương đương tiền</t>
-        </is>
-      </c>
-      <c r="B43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="17" t="inlineStr">
-        <is>
-          <t>TÀI SẢN NGẮN HẠN</t>
-        </is>
-      </c>
-      <c r="B44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="17" t="inlineStr">
-        <is>
-          <t>GTCL tài sản cố định vô hình</t>
-        </is>
-      </c>
-      <c r="B45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="17" t="inlineStr">
+      <c r="J52" s="20" t="n">
+        <v>1500000000000</v>
+      </c>
+      <c r="K52" s="20" t="n">
+        <v>2828497462890</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="25" t="inlineStr">
+        <is>
+          <t>Lưu chuyển tiền tệ</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="18" t="inlineStr">
         <is>
           <t>Khấu hao TSCĐ và BĐSĐT</t>
         </is>
       </c>
-      <c r="B46" s="18">
+      <c r="B54" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(B$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C46" s="18">
+      <c r="C54" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(C$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D46" s="18">
+      <c r="D54" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(D$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E46" s="18">
+      <c r="E54" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(E$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F46" s="18">
+      <c r="F54" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(F$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G46" s="18">
+      <c r="G54" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(G$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H46" s="18">
+      <c r="H54" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(H$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I46" s="18">
+      <c r="I54" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(I$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="17" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="18" t="inlineStr">
         <is>
           <t>Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác</t>
         </is>
       </c>
-      <c r="B47" s="18">
+      <c r="B55" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(B$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C47" s="18">
+      <c r="C55" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(C$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D47" s="18">
+      <c r="D55" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(D$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E47" s="18">
+      <c r="E55" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(E$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F47" s="18">
+      <c r="F55" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(F$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G47" s="18">
+      <c r="G55" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(G$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H47" s="18">
+      <c r="H55" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(H$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I47" s="18">
+      <c r="I55" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(I$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="17" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="18" t="inlineStr">
         <is>
           <t>Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh</t>
         </is>
       </c>
-      <c r="B48" s="18">
+      <c r="B56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(B$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C48" s="18">
+      <c r="C56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(C$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D48" s="18">
+      <c r="D56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(D$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E48" s="18">
+      <c r="E56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(E$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F48" s="18">
+      <c r="F56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(F$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G48" s="18">
+      <c r="G56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(G$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H48" s="18">
+      <c r="H56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(H$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I48" s="18">
+      <c r="I56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(I$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" s="19" t="inlineStr">
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60">
+      <c r="A60" s="26" t="inlineStr">
         <is>
           <t>CHỈ SỐ THÊM</t>
         </is>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B60" s="16" t="n">
         <v>2018</v>
       </c>
-      <c r="C52" s="6" t="n">
+      <c r="C60" s="16" t="n">
         <v>2019</v>
       </c>
-      <c r="D52" s="6" t="n">
+      <c r="D60" s="16" t="n">
         <v>2020</v>
       </c>
-      <c r="E52" s="6" t="n">
+      <c r="E60" s="16" t="n">
         <v>2021</v>
       </c>
-      <c r="F52" s="6" t="n">
+      <c r="F60" s="16" t="n">
         <v>2022</v>
       </c>
-      <c r="G52" s="6" t="n">
+      <c r="G60" s="16" t="n">
         <v>2023</v>
       </c>
-      <c r="H52" s="6" t="n">
+      <c r="H60" s="16" t="n">
         <v>2024</v>
       </c>
-      <c r="I52" s="6" t="n">
+      <c r="I60" s="16" t="n">
         <v>2025</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="19" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="26" t="inlineStr">
         <is>
           <t>Khả năng sinh lời &amp; hiệu quả sử dụng vốn</t>
         </is>
       </c>
-      <c r="B53" s="20" t="n"/>
-      <c r="C53" s="20" t="n"/>
-      <c r="D53" s="20" t="n"/>
-      <c r="E53" s="20" t="n"/>
-      <c r="F53" s="20" t="n"/>
-      <c r="G53" s="20" t="n"/>
-      <c r="H53" s="20" t="n"/>
-      <c r="I53" s="20" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="20" t="inlineStr">
+      <c r="B61" s="27" t="n"/>
+      <c r="C61" s="27" t="n"/>
+      <c r="D61" s="27" t="n"/>
+      <c r="E61" s="27" t="n"/>
+      <c r="F61" s="27" t="n"/>
+      <c r="G61" s="27" t="n"/>
+      <c r="H61" s="27" t="n"/>
+      <c r="I61" s="27" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="27" t="inlineStr">
         <is>
           <t>ROCE</t>
         </is>
       </c>
-      <c r="B54" s="21">
-        <f>IFERROR(B$56/(B$25-B$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C54" s="21">
-        <f>IFERROR(C$56/(C$25-C$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D54" s="21">
-        <f>IFERROR(D$56/(D$25-D$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E54" s="21">
-        <f>IFERROR(E$56/(E$25-E$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F54" s="21">
-        <f>IFERROR(F$56/(F$25-F$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G54" s="21">
-        <f>IFERROR(G$56/(G$25-G$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H54" s="21">
-        <f>IFERROR(H$56/(H$25-H$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I54" s="21">
-        <f>IFERROR(I$56/(I$25-I$27),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="20" t="inlineStr">
+      <c r="B62" s="28">
+        <f>IFERROR(B$64/(B$31-B$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C62" s="28">
+        <f>IFERROR(C$64/(C$31-C$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D62" s="28">
+        <f>IFERROR(D$64/(D$31-D$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E62" s="28">
+        <f>IFERROR(E$64/(E$31-E$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F62" s="28">
+        <f>IFERROR(F$64/(F$31-F$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G62" s="28">
+        <f>IFERROR(G$64/(G$31-G$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H62" s="28">
+        <f>IFERROR(H$64/(H$31-H$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I62" s="28">
+        <f>IFERROR(I$64/(I$31-I$35),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="27" t="inlineStr">
         <is>
           <t>CROIC</t>
         </is>
       </c>
-      <c r="B55" s="21">
-        <f>IFERROR(B$60/(B$25-B$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C55" s="21">
-        <f>IFERROR(C$60/(C$25-C$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D55" s="21">
-        <f>IFERROR(D$60/(D$25-D$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E55" s="21">
-        <f>IFERROR(E$60/(E$25-E$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F55" s="21">
-        <f>IFERROR(F$60/(F$25-F$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G55" s="21">
-        <f>IFERROR(G$60/(G$25-G$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H55" s="21">
-        <f>IFERROR(H$60/(H$25-H$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I55" s="21">
-        <f>IFERROR(I$60/(I$25-I$27),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="20" t="inlineStr">
+      <c r="B63" s="28">
+        <f>IFERROR(B$68/(B$31-B$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C63" s="28">
+        <f>IFERROR(C$68/(C$31-C$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D63" s="28">
+        <f>IFERROR(D$68/(D$31-D$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E63" s="28">
+        <f>IFERROR(E$68/(E$31-E$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F63" s="28">
+        <f>IFERROR(F$68/(F$31-F$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G63" s="28">
+        <f>IFERROR(G$68/(G$31-G$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H63" s="28">
+        <f>IFERROR(H$68/(H$31-H$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I63" s="28">
+        <f>IFERROR(I$68/(I$31-I$35),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="27" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B56" s="22">
-        <f>IFERROR(B$36+ABS(B$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C56" s="22">
-        <f>IFERROR(C$36+ABS(C$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D56" s="22">
-        <f>IFERROR(D$36+ABS(D$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E56" s="22">
-        <f>IFERROR(E$36+ABS(E$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F56" s="22">
-        <f>IFERROR(F$36+ABS(F$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G56" s="22">
-        <f>IFERROR(G$36+ABS(G$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H56" s="22">
-        <f>IFERROR(H$36+ABS(H$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I56" s="22">
-        <f>IFERROR(I$36+ABS(I$37),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="20" t="inlineStr">
+      <c r="B64" s="29">
+        <f>IFERROR(B$48+ABS(B$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C64" s="29">
+        <f>IFERROR(C$48+ABS(C$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D64" s="29">
+        <f>IFERROR(D$48+ABS(D$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E64" s="29">
+        <f>IFERROR(E$48+ABS(E$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F64" s="29">
+        <f>IFERROR(F$48+ABS(F$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G64" s="29">
+        <f>IFERROR(G$48+ABS(G$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H64" s="29">
+        <f>IFERROR(H$48+ABS(H$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I64" s="29">
+        <f>IFERROR(I$48+ABS(I$49),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="27" t="inlineStr">
         <is>
           <t>EBIT/DT</t>
         </is>
       </c>
-      <c r="B57" s="21">
-        <f>IFERROR(B$56/B$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C57" s="21">
-        <f>IFERROR(C$56/C$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D57" s="21">
-        <f>IFERROR(D$56/D$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E57" s="21">
-        <f>IFERROR(E$56/E$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F57" s="21">
-        <f>IFERROR(F$56/F$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G57" s="21">
-        <f>IFERROR(G$56/G$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H57" s="21">
-        <f>IFERROR(H$56/H$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I57" s="21">
-        <f>IFERROR(I$56/I$31,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="20" t="inlineStr">
+      <c r="B65" s="28">
+        <f>IFERROR(B$64/B$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C65" s="28">
+        <f>IFERROR(C$64/C$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D65" s="28">
+        <f>IFERROR(D$64/D$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E65" s="28">
+        <f>IFERROR(E$64/E$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F65" s="28">
+        <f>IFERROR(F$64/F$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G65" s="28">
+        <f>IFERROR(G$64/G$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H65" s="28">
+        <f>IFERROR(H$64/H$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I65" s="28">
+        <f>IFERROR(I$64/I$43,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="27" t="inlineStr">
         <is>
           <t>DT/TS</t>
         </is>
       </c>
-      <c r="B58" s="21">
-        <f>IFERROR(B$31/B$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C58" s="21">
-        <f>IFERROR(C$31/C$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D58" s="21">
-        <f>IFERROR(D$31/D$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E58" s="21">
-        <f>IFERROR(E$31/E$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F58" s="21">
-        <f>IFERROR(F$31/F$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G58" s="21">
-        <f>IFERROR(G$31/G$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H58" s="21">
-        <f>IFERROR(H$31/H$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I58" s="21">
-        <f>IFERROR(I$31/I$25,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="19" t="inlineStr">
+      <c r="B66" s="28">
+        <f>IFERROR(B$43/B$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C66" s="28">
+        <f>IFERROR(C$43/C$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D66" s="28">
+        <f>IFERROR(D$43/D$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E66" s="28">
+        <f>IFERROR(E$43/E$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F66" s="28">
+        <f>IFERROR(F$43/F$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G66" s="28">
+        <f>IFERROR(G$43/G$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H66" s="28">
+        <f>IFERROR(H$43/H$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I66" s="28">
+        <f>IFERROR(I$43/I$31,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="26" t="inlineStr">
         <is>
           <t>Dòng tiền &amp; tái đầu tư</t>
         </is>
       </c>
-      <c r="B59" s="20" t="n"/>
-      <c r="C59" s="20" t="n"/>
-      <c r="D59" s="20" t="n"/>
-      <c r="E59" s="20" t="n"/>
-      <c r="F59" s="20" t="n"/>
-      <c r="G59" s="20" t="n"/>
-      <c r="H59" s="20" t="n"/>
-      <c r="I59" s="20" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="20" t="inlineStr">
+      <c r="B67" s="27" t="n"/>
+      <c r="C67" s="27" t="n"/>
+      <c r="D67" s="27" t="n"/>
+      <c r="E67" s="27" t="n"/>
+      <c r="F67" s="27" t="n"/>
+      <c r="G67" s="27" t="n"/>
+      <c r="H67" s="27" t="n"/>
+      <c r="I67" s="27" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="27" t="inlineStr">
         <is>
           <t>FCF</t>
         </is>
       </c>
-      <c r="B60" s="22">
-        <f>IFERROR(B$48-ABS(B$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C60" s="22">
-        <f>IFERROR(C$48-ABS(C$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D60" s="22">
-        <f>IFERROR(D$48-ABS(D$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E60" s="22">
-        <f>IFERROR(E$48-ABS(E$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F60" s="22">
-        <f>IFERROR(F$48-ABS(F$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G60" s="22">
-        <f>IFERROR(G$48-ABS(G$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H60" s="22">
-        <f>IFERROR(H$48-ABS(H$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I60" s="22">
-        <f>IFERROR(I$48-ABS(I$47),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="20" t="inlineStr">
+      <c r="B68" s="29">
+        <f>IFERROR(B$56-ABS(B$55),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C68" s="29">
+        <f>IFERROR(C$56-ABS(C$55),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D68" s="29">
+        <f>IFERROR(D$56-ABS(D$55),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E68" s="29">
+        <f>IFERROR(E$56-ABS(E$55),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F68" s="29">
+        <f>IFERROR(F$56-ABS(F$55),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G68" s="29">
+        <f>IFERROR(G$56-ABS(G$55),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H68" s="29">
+        <f>IFERROR(H$56-ABS(H$55),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I68" s="29">
+        <f>IFERROR(I$56-ABS(I$55),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="27" t="inlineStr">
         <is>
           <t>FCF/DT</t>
         </is>
       </c>
-      <c r="B61" s="21">
-        <f>IFERROR(B$60/B$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C61" s="21">
-        <f>IFERROR(C$60/C$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D61" s="21">
-        <f>IFERROR(D$60/D$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E61" s="21">
-        <f>IFERROR(E$60/E$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F61" s="21">
-        <f>IFERROR(F$60/F$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G61" s="21">
-        <f>IFERROR(G$60/G$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H61" s="21">
-        <f>IFERROR(H$60/H$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I61" s="21">
-        <f>IFERROR(I$60/I$31,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="20" t="inlineStr">
+      <c r="B69" s="28">
+        <f>IFERROR(B$68/B$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C69" s="28">
+        <f>IFERROR(C$68/C$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D69" s="28">
+        <f>IFERROR(D$68/D$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E69" s="28">
+        <f>IFERROR(E$68/E$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F69" s="28">
+        <f>IFERROR(F$68/F$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G69" s="28">
+        <f>IFERROR(G$68/G$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H69" s="28">
+        <f>IFERROR(H$68/H$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I69" s="28">
+        <f>IFERROR(I$68/I$43,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="27" t="inlineStr">
         <is>
           <t>FCF/Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B62" s="21">
-        <f>IFERROR(B$60/B$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C62" s="21">
-        <f>IFERROR(C$60/C$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D62" s="21">
-        <f>IFERROR(D$60/D$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E62" s="21">
-        <f>IFERROR(E$60/E$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F62" s="21">
-        <f>IFERROR(F$60/F$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G62" s="21">
-        <f>IFERROR(G$60/G$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H62" s="21">
-        <f>IFERROR(H$60/H$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I62" s="21">
-        <f>IFERROR(I$60/I$27,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="20" t="inlineStr">
+      <c r="B70" s="28">
+        <f>IFERROR(B$68/B$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C70" s="28">
+        <f>IFERROR(C$68/C$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D70" s="28">
+        <f>IFERROR(D$68/D$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E70" s="28">
+        <f>IFERROR(E$68/E$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F70" s="28">
+        <f>IFERROR(F$68/F$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G70" s="28">
+        <f>IFERROR(G$68/G$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H70" s="28">
+        <f>IFERROR(H$68/H$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I70" s="28">
+        <f>IFERROR(I$68/I$35,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="27" t="inlineStr">
         <is>
           <t>Capex</t>
         </is>
       </c>
-      <c r="B63" s="22">
-        <f>IFERROR(ABS(B$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C63" s="22">
-        <f>IFERROR(ABS(C$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D63" s="22">
-        <f>IFERROR(ABS(D$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E63" s="22">
-        <f>IFERROR(ABS(E$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F63" s="22">
-        <f>IFERROR(ABS(F$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G63" s="22">
-        <f>IFERROR(ABS(G$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H63" s="22">
-        <f>IFERROR(ABS(H$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I63" s="22">
-        <f>IFERROR(ABS(I$47),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="20" t="inlineStr">
+      <c r="B71" s="29">
+        <f>IFERROR(ABS(B$55),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C71" s="29">
+        <f>IFERROR(ABS(C$55),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D71" s="29">
+        <f>IFERROR(ABS(D$55),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E71" s="29">
+        <f>IFERROR(ABS(E$55),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F71" s="29">
+        <f>IFERROR(ABS(F$55),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G71" s="29">
+        <f>IFERROR(ABS(G$55),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H71" s="29">
+        <f>IFERROR(ABS(H$55),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I71" s="29">
+        <f>IFERROR(ABS(I$55),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="27" t="inlineStr">
         <is>
           <t>Capex/TS</t>
         </is>
       </c>
-      <c r="B64" s="21">
-        <f>IFERROR(B$63/B$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C64" s="21">
-        <f>IFERROR(C$63/C$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D64" s="21">
-        <f>IFERROR(D$63/D$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E64" s="21">
-        <f>IFERROR(E$63/E$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F64" s="21">
-        <f>IFERROR(F$63/F$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G64" s="21">
-        <f>IFERROR(G$63/G$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H64" s="21">
-        <f>IFERROR(H$63/H$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I64" s="21">
-        <f>IFERROR(I$63/I$25,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="20" t="inlineStr">
+      <c r="B72" s="28">
+        <f>IFERROR(B$71/B$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C72" s="28">
+        <f>IFERROR(C$71/C$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D72" s="28">
+        <f>IFERROR(D$71/D$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E72" s="28">
+        <f>IFERROR(E$71/E$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F72" s="28">
+        <f>IFERROR(F$71/F$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G72" s="28">
+        <f>IFERROR(G$71/G$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H72" s="28">
+        <f>IFERROR(H$71/H$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I72" s="28">
+        <f>IFERROR(I$71/I$31,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="27" t="inlineStr">
         <is>
           <t>Capex/LNST</t>
         </is>
       </c>
-      <c r="B65" s="21">
-        <f>IFERROR(B$63/ABS(B$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C65" s="21">
-        <f>IFERROR(C$63/ABS(C$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D65" s="21">
-        <f>IFERROR(D$63/ABS(D$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E65" s="21">
-        <f>IFERROR(E$63/ABS(E$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F65" s="21">
-        <f>IFERROR(F$63/ABS(F$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G65" s="21">
-        <f>IFERROR(G$63/ABS(G$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H65" s="21">
-        <f>IFERROR(H$63/ABS(H$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I65" s="21">
-        <f>IFERROR(I$63/ABS(I$38),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="20" t="inlineStr">
+      <c r="B73" s="28">
+        <f>IFERROR(B$71/ABS(B$51),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C73" s="28">
+        <f>IFERROR(C$71/ABS(C$51),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D73" s="28">
+        <f>IFERROR(D$71/ABS(D$51),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E73" s="28">
+        <f>IFERROR(E$71/ABS(E$51),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F73" s="28">
+        <f>IFERROR(F$71/ABS(F$51),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G73" s="28">
+        <f>IFERROR(G$71/ABS(G$51),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H73" s="28">
+        <f>IFERROR(H$71/ABS(H$51),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I73" s="28">
+        <f>IFERROR(I$71/ABS(I$51),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="27" t="inlineStr">
         <is>
           <t>Chi phí khấu hao/Lợi nhuận gộp</t>
         </is>
       </c>
-      <c r="B66" s="21">
-        <f>IFERROR(ABS(B$46)/B$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C66" s="21">
-        <f>IFERROR(ABS(C$46)/C$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D66" s="21">
-        <f>IFERROR(ABS(D$46)/D$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E66" s="21">
-        <f>IFERROR(ABS(E$46)/E$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F66" s="21">
-        <f>IFERROR(ABS(F$46)/F$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G66" s="21">
-        <f>IFERROR(ABS(G$46)/G$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H66" s="21">
-        <f>IFERROR(ABS(H$46)/H$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I66" s="21">
-        <f>IFERROR(ABS(I$46)/I$33,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="20" t="inlineStr">
+      <c r="B74" s="28">
+        <f>IFERROR(ABS(B$54)/B$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C74" s="28">
+        <f>IFERROR(ABS(C$54)/C$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D74" s="28">
+        <f>IFERROR(ABS(D$54)/D$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E74" s="28">
+        <f>IFERROR(ABS(E$54)/E$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F74" s="28">
+        <f>IFERROR(ABS(F$54)/F$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G74" s="28">
+        <f>IFERROR(ABS(G$54)/G$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H74" s="28">
+        <f>IFERROR(ABS(H$54)/H$45,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I74" s="28">
+        <f>IFERROR(ABS(I$54)/I$45,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="27" t="inlineStr">
         <is>
           <t>EBIT/Chi phí lãi vay</t>
         </is>
       </c>
-      <c r="B67" s="23">
-        <f>IFERROR(B$56/ABS(B$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C67" s="23">
-        <f>IFERROR(C$56/ABS(C$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D67" s="23">
-        <f>IFERROR(D$56/ABS(D$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E67" s="23">
-        <f>IFERROR(E$56/ABS(E$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F67" s="23">
-        <f>IFERROR(F$56/ABS(F$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G67" s="23">
-        <f>IFERROR(G$56/ABS(G$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H67" s="23">
-        <f>IFERROR(H$56/ABS(H$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I67" s="23">
-        <f>IFERROR(I$56/ABS(I$37),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="19" t="inlineStr">
+      <c r="B75" s="30">
+        <f>IFERROR(B$64/ABS(B$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C75" s="30">
+        <f>IFERROR(C$64/ABS(C$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D75" s="30">
+        <f>IFERROR(D$64/ABS(D$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E75" s="30">
+        <f>IFERROR(E$64/ABS(E$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F75" s="30">
+        <f>IFERROR(F$64/ABS(F$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G75" s="30">
+        <f>IFERROR(G$64/ABS(G$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H75" s="30">
+        <f>IFERROR(H$64/ABS(H$49),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I75" s="30">
+        <f>IFERROR(I$64/ABS(I$49),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="26" t="inlineStr">
         <is>
           <t>Vốn lưu động &amp; hiệu quả hoạt động</t>
         </is>
       </c>
-      <c r="B68" s="20" t="n"/>
-      <c r="C68" s="20" t="n"/>
-      <c r="D68" s="20" t="n"/>
-      <c r="E68" s="20" t="n"/>
-      <c r="F68" s="20" t="n"/>
-      <c r="G68" s="20" t="n"/>
-      <c r="H68" s="20" t="n"/>
-      <c r="I68" s="20" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="20" t="inlineStr">
+      <c r="B76" s="27" t="n"/>
+      <c r="C76" s="27" t="n"/>
+      <c r="D76" s="27" t="n"/>
+      <c r="E76" s="27" t="n"/>
+      <c r="F76" s="27" t="n"/>
+      <c r="G76" s="27" t="n"/>
+      <c r="H76" s="27" t="n"/>
+      <c r="I76" s="27" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="27" t="inlineStr">
         <is>
           <t>Vòng quay tiền mặt</t>
         </is>
       </c>
-      <c r="B69" s="24">
+      <c r="B77" s="31">
         <f>IFERROR(B$17+B$18-B$16,"n/a")</f>
         <v/>
       </c>
-      <c r="C69" s="24">
+      <c r="C77" s="31">
         <f>IFERROR(C$17+C$18-C$16,"n/a")</f>
         <v/>
       </c>
-      <c r="D69" s="24">
+      <c r="D77" s="31">
         <f>IFERROR(D$17+D$18-D$16,"n/a")</f>
         <v/>
       </c>
-      <c r="E69" s="24">
+      <c r="E77" s="31">
         <f>IFERROR(E$17+E$18-E$16,"n/a")</f>
         <v/>
       </c>
-      <c r="F69" s="24">
+      <c r="F77" s="31">
         <f>IFERROR(F$17+F$18-F$16,"n/a")</f>
         <v/>
       </c>
-      <c r="G69" s="24">
+      <c r="G77" s="31">
         <f>IFERROR(G$17+G$18-G$16,"n/a")</f>
         <v/>
       </c>
-      <c r="H69" s="24">
+      <c r="H77" s="31">
         <f>IFERROR(H$17+H$18-H$16,"n/a")</f>
         <v/>
       </c>
-      <c r="I69" s="24">
+      <c r="I77" s="31">
         <f>IFERROR(I$17+I$18-I$16,"n/a")</f>
         <v/>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="20" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="27" t="inlineStr">
         <is>
           <t>HTK/DT</t>
         </is>
       </c>
-      <c r="B70" s="21">
-        <f>IFERROR(B$42/B$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C70" s="21">
-        <f>IFERROR(C$42/C$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D70" s="21">
-        <f>IFERROR(D$42/D$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E70" s="21">
-        <f>IFERROR(E$42/E$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F70" s="21">
-        <f>IFERROR(F$42/F$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G70" s="21">
-        <f>IFERROR(G$42/G$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H70" s="21">
-        <f>IFERROR(H$42/H$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I70" s="21">
-        <f>IFERROR(I$42/I$31,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="20" t="inlineStr">
+      <c r="B78" s="28">
+        <f>IFERROR(B$28/B$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C78" s="28">
+        <f>IFERROR(C$28/C$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D78" s="28">
+        <f>IFERROR(D$28/D$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E78" s="28">
+        <f>IFERROR(E$28/E$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F78" s="28">
+        <f>IFERROR(F$28/F$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G78" s="28">
+        <f>IFERROR(G$28/G$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H78" s="28">
+        <f>IFERROR(H$28/H$43,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I78" s="28">
+        <f>IFERROR(I$28/I$43,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="27" t="inlineStr">
         <is>
           <t>HTK/TS</t>
         </is>
       </c>
-      <c r="B71" s="21">
-        <f>IFERROR(B$42/B$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C71" s="21">
-        <f>IFERROR(C$42/C$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D71" s="21">
-        <f>IFERROR(D$42/D$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E71" s="21">
-        <f>IFERROR(E$42/E$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F71" s="21">
-        <f>IFERROR(F$42/F$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G71" s="21">
-        <f>IFERROR(G$42/G$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H71" s="21">
-        <f>IFERROR(H$42/H$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I71" s="21">
-        <f>IFERROR(I$42/I$25,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="20" t="inlineStr">
+      <c r="B79" s="28">
+        <f>IFERROR(B$28/B$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C79" s="28">
+        <f>IFERROR(C$28/C$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D79" s="28">
+        <f>IFERROR(D$28/D$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E79" s="28">
+        <f>IFERROR(E$28/E$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F79" s="28">
+        <f>IFERROR(F$28/F$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G79" s="28">
+        <f>IFERROR(G$28/G$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H79" s="28">
+        <f>IFERROR(H$28/H$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I79" s="28">
+        <f>IFERROR(I$28/I$31,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="27" t="inlineStr">
         <is>
           <t>DT/TS</t>
         </is>
       </c>
-      <c r="B72" s="21">
-        <f>IFERROR(B$31/B$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C72" s="21">
-        <f>IFERROR(C$31/C$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D72" s="21">
-        <f>IFERROR(D$31/D$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E72" s="21">
-        <f>IFERROR(E$31/E$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F72" s="21">
-        <f>IFERROR(F$31/F$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G72" s="21">
-        <f>IFERROR(G$31/G$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H72" s="21">
-        <f>IFERROR(H$31/H$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I72" s="21">
-        <f>IFERROR(I$31/I$25,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="19" t="inlineStr">
+      <c r="B80" s="28">
+        <f>IFERROR(B$43/B$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C80" s="28">
+        <f>IFERROR(C$43/C$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D80" s="28">
+        <f>IFERROR(D$43/D$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E80" s="28">
+        <f>IFERROR(E$43/E$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F80" s="28">
+        <f>IFERROR(F$43/F$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G80" s="28">
+        <f>IFERROR(G$43/G$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H80" s="28">
+        <f>IFERROR(H$43/H$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I80" s="28">
+        <f>IFERROR(I$43/I$31,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="26" t="inlineStr">
         <is>
           <t>Khả năng thanh toán</t>
         </is>
       </c>
-      <c r="B73" s="20" t="n"/>
-      <c r="C73" s="20" t="n"/>
-      <c r="D73" s="20" t="n"/>
-      <c r="E73" s="20" t="n"/>
-      <c r="F73" s="20" t="n"/>
-      <c r="G73" s="20" t="n"/>
-      <c r="H73" s="20" t="n"/>
-      <c r="I73" s="20" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="20" t="inlineStr">
+      <c r="B81" s="27" t="n"/>
+      <c r="C81" s="27" t="n"/>
+      <c r="D81" s="27" t="n"/>
+      <c r="E81" s="27" t="n"/>
+      <c r="F81" s="27" t="n"/>
+      <c r="G81" s="27" t="n"/>
+      <c r="H81" s="27" t="n"/>
+      <c r="I81" s="27" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="27" t="inlineStr">
         <is>
           <t>(TS ngắn hạn − HTK)/Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B74" s="23">
-        <f>IFERROR((B$44-B$42)/B$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C74" s="23">
-        <f>IFERROR((C$44-C$42)/C$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D74" s="23">
-        <f>IFERROR((D$44-D$42)/D$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E74" s="23">
-        <f>IFERROR((E$44-E$42)/E$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F74" s="23">
-        <f>IFERROR((F$44-F$42)/F$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G74" s="23">
-        <f>IFERROR((G$44-G$42)/G$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H74" s="23">
-        <f>IFERROR((H$44-H$42)/H$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I74" s="23">
-        <f>IFERROR((I$44-I$42)/I$27,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="20" t="inlineStr">
+      <c r="B82" s="30">
+        <f>IFERROR((B$29-B$28)/B$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C82" s="30">
+        <f>IFERROR((C$29-C$28)/C$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D82" s="30">
+        <f>IFERROR((D$29-D$28)/D$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E82" s="30">
+        <f>IFERROR((E$29-E$28)/E$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F82" s="30">
+        <f>IFERROR((F$29-F$28)/F$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G82" s="30">
+        <f>IFERROR((G$29-G$28)/G$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H82" s="30">
+        <f>IFERROR((H$29-H$28)/H$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I82" s="30">
+        <f>IFERROR((I$29-I$28)/I$35,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="27" t="inlineStr">
         <is>
           <t>TS ngắn hạn/Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B75" s="23">
-        <f>IFERROR(B$44/B$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C75" s="23">
-        <f>IFERROR(C$44/C$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D75" s="23">
-        <f>IFERROR(D$44/D$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E75" s="23">
-        <f>IFERROR(E$44/E$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F75" s="23">
-        <f>IFERROR(F$44/F$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G75" s="23">
-        <f>IFERROR(G$44/G$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H75" s="23">
-        <f>IFERROR(H$44/H$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I75" s="23">
-        <f>IFERROR(I$44/I$27,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="19" t="inlineStr">
+      <c r="B83" s="30">
+        <f>IFERROR(B$29/B$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C83" s="30">
+        <f>IFERROR(C$29/C$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D83" s="30">
+        <f>IFERROR(D$29/D$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E83" s="30">
+        <f>IFERROR(E$29/E$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F83" s="30">
+        <f>IFERROR(F$29/F$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G83" s="30">
+        <f>IFERROR(G$29/G$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H83" s="30">
+        <f>IFERROR(H$29/H$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I83" s="30">
+        <f>IFERROR(I$29/I$35,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="26" t="inlineStr">
         <is>
           <t>Tài sản &amp; cơ cấu tài sản</t>
         </is>
       </c>
-      <c r="B76" s="20" t="n"/>
-      <c r="C76" s="20" t="n"/>
-      <c r="D76" s="20" t="n"/>
-      <c r="E76" s="20" t="n"/>
-      <c r="F76" s="20" t="n"/>
-      <c r="G76" s="20" t="n"/>
-      <c r="H76" s="20" t="n"/>
-      <c r="I76" s="20" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="20" t="inlineStr">
+      <c r="B84" s="27" t="n"/>
+      <c r="C84" s="27" t="n"/>
+      <c r="D84" s="27" t="n"/>
+      <c r="E84" s="27" t="n"/>
+      <c r="F84" s="27" t="n"/>
+      <c r="G84" s="27" t="n"/>
+      <c r="H84" s="27" t="n"/>
+      <c r="I84" s="27" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="27" t="inlineStr">
         <is>
           <t>TSCĐ vô hình</t>
         </is>
       </c>
-      <c r="B77" s="22">
-        <f>IFERROR(B$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C77" s="22">
-        <f>IFERROR(C$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D77" s="22">
-        <f>IFERROR(D$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E77" s="22">
-        <f>IFERROR(E$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F77" s="22">
-        <f>IFERROR(F$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G77" s="22">
-        <f>IFERROR(G$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H77" s="22">
-        <f>IFERROR(H$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I77" s="22">
-        <f>IFERROR(I$45,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="20" t="inlineStr">
+      <c r="B85" s="29">
+        <f>IFERROR(B$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C85" s="29">
+        <f>IFERROR(C$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D85" s="29">
+        <f>IFERROR(D$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E85" s="29">
+        <f>IFERROR(E$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F85" s="29">
+        <f>IFERROR(F$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G85" s="29">
+        <f>IFERROR(G$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H85" s="29">
+        <f>IFERROR(H$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I85" s="29">
+        <f>IFERROR(I$30,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="27" t="inlineStr">
         <is>
           <t>Tài sản vô hình/Giá trị sổ sách</t>
         </is>
       </c>
-      <c r="B78" s="21">
-        <f>IFERROR(B$45/B$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C78" s="21">
-        <f>IFERROR(C$45/C$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D78" s="21">
-        <f>IFERROR(D$45/D$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E78" s="21">
-        <f>IFERROR(E$45/E$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F78" s="21">
-        <f>IFERROR(F$45/F$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G78" s="21">
-        <f>IFERROR(G$45/G$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H78" s="21">
-        <f>IFERROR(H$45/H$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I78" s="21">
-        <f>IFERROR(I$45/I$24,"n/a")</f>
+      <c r="B86" s="28">
+        <f>IFERROR(B$30/B$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C86" s="28">
+        <f>IFERROR(C$30/C$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D86" s="28">
+        <f>IFERROR(D$30/D$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E86" s="28">
+        <f>IFERROR(E$30/E$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F86" s="28">
+        <f>IFERROR(F$30/F$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G86" s="28">
+        <f>IFERROR(G$30/G$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H86" s="28">
+        <f>IFERROR(H$30/H$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I86" s="28">
+        <f>IFERROR(I$30/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:I2">
-    <cfRule type="cellIs" priority="14" operator="greaterThanOrEqual" dxfId="0">
-      <formula>0.15</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="15" operator="lessThan" dxfId="1">
-      <formula>0.15</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4:I5">
-    <cfRule type="cellIs" priority="11" operator="lessThan" dxfId="1">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="12" operator="greaterThanOrEqual" dxfId="0">
-      <formula>0.15</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="13" operator="between" dxfId="2">
-      <formula>0.1</formula>
-      <formula>0.15</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B6:I6">
     <cfRule type="cellIs" priority="8" operator="greaterThanOrEqual" dxfId="0">
       <formula>0.3</formula>
@@ -9389,11 +9690,6 @@
     <cfRule type="cellIs" priority="10" operator="between" dxfId="2">
       <formula>0.1</formula>
       <formula>0.3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B7:I7">
-    <cfRule type="cellIs" priority="7" operator="greaterThanOrEqual" dxfId="0">
-      <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:I8 B11:I11">
@@ -9419,6 +9715,922 @@
       <formula>0.3</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B2:K2">
+    <cfRule type="cellIs" priority="14" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0.15</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="15" operator="lessThan" dxfId="1">
+      <formula>0.15</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4:K5">
+    <cfRule type="cellIs" priority="11" operator="lessThan" dxfId="1">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0.15</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="13" operator="between" dxfId="2">
+      <formula>0.1</formula>
+      <formula>0.15</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:K7">
+    <cfRule type="cellIs" priority="7" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="8.125" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="32" t="n"/>
+      <c r="B1" s="32" t="inlineStr">
+        <is>
+          <t>Q4/2025</t>
+        </is>
+      </c>
+      <c r="C1" s="32" t="inlineStr">
+        <is>
+          <t>Q1/2026</t>
+        </is>
+      </c>
+      <c r="D1" s="32" t="inlineStr">
+        <is>
+          <t>Q2/2026</t>
+        </is>
+      </c>
+      <c r="E1" s="32" t="inlineStr">
+        <is>
+          <t>Q3/2026</t>
+        </is>
+      </c>
+      <c r="F1" s="32" t="inlineStr">
+        <is>
+          <t>Q4/2026</t>
+        </is>
+      </c>
+      <c r="G1" s="32" t="inlineStr">
+        <is>
+          <t>Q1/2027</t>
+        </is>
+      </c>
+      <c r="H1" s="32" t="inlineStr">
+        <is>
+          <t>Q2/2027</t>
+        </is>
+      </c>
+      <c r="I1" s="32" t="inlineStr">
+        <is>
+          <t>Q3/2027</t>
+        </is>
+      </c>
+      <c r="J1" s="32" t="inlineStr">
+        <is>
+          <t>Q4/2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="32" t="inlineStr">
+        <is>
+          <t>Số CP</t>
+        </is>
+      </c>
+      <c r="B2" s="33" t="n">
+        <v>511721959</v>
+      </c>
+      <c r="C2" s="33" t="n">
+        <v>511721959</v>
+      </c>
+      <c r="D2" s="33" t="n">
+        <v>511721959</v>
+      </c>
+      <c r="E2" s="33" t="n">
+        <v>511721959</v>
+      </c>
+      <c r="F2" s="33" t="n">
+        <v>511721959</v>
+      </c>
+      <c r="G2" s="33" t="n">
+        <v>511721959</v>
+      </c>
+      <c r="H2" s="33" t="n">
+        <v>511721959</v>
+      </c>
+      <c r="I2" s="33" t="n">
+        <v>511721959</v>
+      </c>
+      <c r="J2" s="33" t="n">
+        <v>511721959</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="32" t="inlineStr">
+        <is>
+          <t>Thị giá</t>
+        </is>
+      </c>
+      <c r="B3" s="33">
+        <f>[1]Sheet1!$E$2</f>
+        <v/>
+      </c>
+      <c r="C3" s="33">
+        <f>[1]Sheet1!$E$2</f>
+        <v/>
+      </c>
+      <c r="D3" s="33">
+        <f>[1]Sheet1!$E$2</f>
+        <v/>
+      </c>
+      <c r="E3" s="33">
+        <f>[1]Sheet1!$E$2</f>
+        <v/>
+      </c>
+      <c r="F3" s="33">
+        <f>[1]Sheet1!$E$2</f>
+        <v/>
+      </c>
+      <c r="G3" s="33">
+        <f>[1]Sheet1!$E$2</f>
+        <v/>
+      </c>
+      <c r="H3" s="33">
+        <f>[1]Sheet1!$E$2</f>
+        <v/>
+      </c>
+      <c r="I3" s="33">
+        <f>[1]Sheet1!$E$2</f>
+        <v/>
+      </c>
+      <c r="J3" s="33">
+        <f>[1]Sheet1!$E$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="32" t="inlineStr">
+        <is>
+          <t>Vốn hoá</t>
+        </is>
+      </c>
+      <c r="B4" s="33">
+        <f>B2*B3</f>
+        <v/>
+      </c>
+      <c r="C4" s="33">
+        <f>C2*C3</f>
+        <v/>
+      </c>
+      <c r="D4" s="33">
+        <f>D2*D3</f>
+        <v/>
+      </c>
+      <c r="E4" s="33">
+        <f>E2*E3</f>
+        <v/>
+      </c>
+      <c r="F4" s="33">
+        <f>F2*F3</f>
+        <v/>
+      </c>
+      <c r="G4" s="33">
+        <f>G2*G3</f>
+        <v/>
+      </c>
+      <c r="H4" s="33">
+        <f>H2*H3</f>
+        <v/>
+      </c>
+      <c r="I4" s="33">
+        <f>I2*I3</f>
+        <v/>
+      </c>
+      <c r="J4" s="33">
+        <f>J2*J3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="G5" s="33" t="n"/>
+      <c r="H5" s="33" t="n"/>
+      <c r="I5" s="33" t="n"/>
+      <c r="J5" s="33" t="n"/>
+      <c r="K5" s="34" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>VCSH</t>
+        </is>
+      </c>
+      <c r="B6" s="32" t="n"/>
+      <c r="C6" s="35" t="n">
+        <v>14401000000000</v>
+      </c>
+      <c r="D6" s="35" t="n">
+        <v>13913000000000</v>
+      </c>
+      <c r="E6" s="35">
+        <f>$D$6*(($F$6/$D$6)^(1/2))</f>
+        <v/>
+      </c>
+      <c r="F6" s="33">
+        <f>chi_so_tai_chinh!J39</f>
+        <v/>
+      </c>
+      <c r="G6" s="35">
+        <f>$F$6*((J6/$F$6)^(1/4))</f>
+        <v/>
+      </c>
+      <c r="H6" s="35">
+        <f>$F$6*((J6/$F$6)^(2/4))</f>
+        <v/>
+      </c>
+      <c r="I6" s="35">
+        <f>$F$6*((J6/$F$6)^(3/4))</f>
+        <v/>
+      </c>
+      <c r="J6" s="33">
+        <f>chi_so_tai_chinh!K39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="32" t="inlineStr">
+        <is>
+          <t>LICĐKKS</t>
+        </is>
+      </c>
+      <c r="B7" s="32" t="n"/>
+      <c r="C7" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="35">
+        <f>[2]CĐKT!J135*1000000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>BV</t>
+        </is>
+      </c>
+      <c r="B8" s="32" t="n"/>
+      <c r="C8" s="35">
+        <f>C6-C7</f>
+        <v/>
+      </c>
+      <c r="D8" s="35">
+        <f>D6-D7</f>
+        <v/>
+      </c>
+      <c r="E8" s="35">
+        <f>E6-E7</f>
+        <v/>
+      </c>
+      <c r="F8" s="35">
+        <f>F6-F7</f>
+        <v/>
+      </c>
+      <c r="G8" s="35">
+        <f>G6-G7</f>
+        <v/>
+      </c>
+      <c r="H8" s="35">
+        <f>H6-H7</f>
+        <v/>
+      </c>
+      <c r="I8" s="35">
+        <f>I6-I7</f>
+        <v/>
+      </c>
+      <c r="J8" s="35">
+        <f>J6-J7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="36" t="inlineStr">
+        <is>
+          <t>BVPS</t>
+        </is>
+      </c>
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="37">
+        <f>C8/C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="37">
+        <f>D8/D2</f>
+        <v/>
+      </c>
+      <c r="E9" s="37">
+        <f>E8/E2</f>
+        <v/>
+      </c>
+      <c r="F9" s="37">
+        <f>F8/F2</f>
+        <v/>
+      </c>
+      <c r="G9" s="37">
+        <f>G8/G2</f>
+        <v/>
+      </c>
+      <c r="H9" s="37">
+        <f>H8/H2</f>
+        <v/>
+      </c>
+      <c r="I9" s="37">
+        <f>I8/I2</f>
+        <v/>
+      </c>
+      <c r="J9" s="37">
+        <f>J8/J2</f>
+        <v/>
+      </c>
+      <c r="K9" s="38" t="n"/>
+      <c r="L9" s="38" t="n"/>
+      <c r="M9" s="38" t="n"/>
+      <c r="N9" s="38" t="n"/>
+      <c r="O9" s="38" t="n"/>
+      <c r="P9" s="38" t="n"/>
+      <c r="Q9" s="38" t="n"/>
+      <c r="R9" s="38" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="36" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="39">
+        <f>C3/C9</f>
+        <v/>
+      </c>
+      <c r="D10" s="39">
+        <f>D3/D9</f>
+        <v/>
+      </c>
+      <c r="E10" s="39">
+        <f>E3/E9</f>
+        <v/>
+      </c>
+      <c r="F10" s="39">
+        <f>F3/F9</f>
+        <v/>
+      </c>
+      <c r="G10" s="39">
+        <f>G3/G9</f>
+        <v/>
+      </c>
+      <c r="H10" s="39">
+        <f>H3/H9</f>
+        <v/>
+      </c>
+      <c r="I10" s="39">
+        <f>I3/I9</f>
+        <v/>
+      </c>
+      <c r="J10" s="39">
+        <f>J3/J9</f>
+        <v/>
+      </c>
+      <c r="K10" s="38" t="n"/>
+      <c r="L10" s="38" t="n"/>
+      <c r="M10" s="38" t="n"/>
+      <c r="N10" s="38" t="n"/>
+      <c r="O10" s="38" t="n"/>
+      <c r="P10" s="38" t="n"/>
+      <c r="Q10" s="38" t="n"/>
+      <c r="R10" s="38" t="n"/>
+    </row>
+    <row r="11">
+      <c r="C11" s="40" t="n"/>
+      <c r="D11" s="40" t="n"/>
+      <c r="E11" s="40" t="n"/>
+      <c r="F11" s="40" t="n"/>
+      <c r="I11" s="38" t="n"/>
+      <c r="J11" s="38" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>Trailing Earning</t>
+        </is>
+      </c>
+      <c r="B12" s="35" t="n">
+        <v>2828000000000</v>
+      </c>
+      <c r="C12" s="35">
+        <f>$B$12*(($F$12/$B$12)^(1/4))</f>
+        <v/>
+      </c>
+      <c r="D12" s="35">
+        <f>$B$12*(($F$12/$B$12)^(2/4))</f>
+        <v/>
+      </c>
+      <c r="E12" s="35">
+        <f>$B$12*(($F$12/$B$12)^(3/4))</f>
+        <v/>
+      </c>
+      <c r="F12" s="35" t="n">
+        <v>3139080000000</v>
+      </c>
+      <c r="G12" s="35">
+        <f>$F$12*(($J$12/$F$12)^(1/4))</f>
+        <v/>
+      </c>
+      <c r="H12" s="35">
+        <f>$F$12*(($J$12/$F$12)^(2/4))</f>
+        <v/>
+      </c>
+      <c r="I12" s="35">
+        <f>$F$12*(($J$12/$F$12)^(3/4))</f>
+        <v/>
+      </c>
+      <c r="J12" s="35">
+        <f>chi_so_tai_chinh!K52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="36" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B13" s="37">
+        <f>B12/B2</f>
+        <v/>
+      </c>
+      <c r="C13" s="37">
+        <f>C12/C2</f>
+        <v/>
+      </c>
+      <c r="D13" s="37">
+        <f>D12/D2</f>
+        <v/>
+      </c>
+      <c r="E13" s="37">
+        <f>E12/E2</f>
+        <v/>
+      </c>
+      <c r="F13" s="37">
+        <f>F12/F2</f>
+        <v/>
+      </c>
+      <c r="G13" s="37">
+        <f>G12/G2</f>
+        <v/>
+      </c>
+      <c r="H13" s="37">
+        <f>H12/H2</f>
+        <v/>
+      </c>
+      <c r="I13" s="37">
+        <f>I12/I2</f>
+        <v/>
+      </c>
+      <c r="J13" s="37">
+        <f>J12/J2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="36" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="B14" s="39">
+        <f>B3/B13</f>
+        <v/>
+      </c>
+      <c r="C14" s="39">
+        <f>C3/C13</f>
+        <v/>
+      </c>
+      <c r="D14" s="39">
+        <f>D3/D13</f>
+        <v/>
+      </c>
+      <c r="E14" s="39">
+        <f>E3/E13</f>
+        <v/>
+      </c>
+      <c r="F14" s="39">
+        <f>F3/F13</f>
+        <v/>
+      </c>
+      <c r="G14" s="39">
+        <f>G3/G13</f>
+        <v/>
+      </c>
+      <c r="H14" s="39">
+        <f>H3/H13</f>
+        <v/>
+      </c>
+      <c r="I14" s="39">
+        <f>I3/I13</f>
+        <v/>
+      </c>
+      <c r="J14" s="39">
+        <f>J3/J13</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25.375" customWidth="1" min="1" max="1"/>
+    <col width="17.125" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="41" t="n"/>
+      <c r="B1" s="41" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C1" s="41" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D1" s="41" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E1" s="41" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="41" t="inlineStr">
+        <is>
+          <t>Doanh thu kế hoạch</t>
+        </is>
+      </c>
+      <c r="B2" s="42" t="n">
+        <v>25834930000000</v>
+      </c>
+      <c r="C2" s="42" t="n">
+        <v>35597952000000</v>
+      </c>
+      <c r="D2" s="42" t="n">
+        <v>37147627000000</v>
+      </c>
+      <c r="E2" s="42" t="n">
+        <v>31606954000000</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="41" t="inlineStr">
+        <is>
+          <t>DT thực hiện</t>
+        </is>
+      </c>
+      <c r="B3" s="42">
+        <f>chi_so_tai_chinh!F43</f>
+        <v/>
+      </c>
+      <c r="C3" s="42">
+        <f>chi_so_tai_chinh!G43</f>
+        <v/>
+      </c>
+      <c r="D3" s="42">
+        <f>chi_so_tai_chinh!H43</f>
+        <v/>
+      </c>
+      <c r="E3" s="42">
+        <f>chi_so_tai_chinh!I43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="43" t="inlineStr">
+        <is>
+          <t>%thực hiện</t>
+        </is>
+      </c>
+      <c r="B4" s="44">
+        <f>B3/B2</f>
+        <v/>
+      </c>
+      <c r="C4" s="44">
+        <f>C3/C2</f>
+        <v/>
+      </c>
+      <c r="D4" s="44">
+        <f>D3/D2</f>
+        <v/>
+      </c>
+      <c r="E4" s="44">
+        <f>E3/E2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="41" t="inlineStr">
+        <is>
+          <t>Lợi nhuận trước thuế kế hoạch</t>
+        </is>
+      </c>
+      <c r="B5" s="42" t="n">
+        <v>1640396000000</v>
+      </c>
+      <c r="C5" s="42" t="n">
+        <v>2473882000000</v>
+      </c>
+      <c r="D5" s="42" t="n">
+        <v>2637880000000</v>
+      </c>
+      <c r="E5" s="42" t="n">
+        <v>2474805000000</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="41" t="inlineStr">
+        <is>
+          <t>LN trước thuế KH</t>
+        </is>
+      </c>
+      <c r="B6" s="42">
+        <f>chi_so_tai_chinh!F50</f>
+        <v/>
+      </c>
+      <c r="C6" s="42">
+        <f>chi_so_tai_chinh!G50</f>
+        <v/>
+      </c>
+      <c r="D6" s="42">
+        <f>chi_so_tai_chinh!H50</f>
+        <v/>
+      </c>
+      <c r="E6" s="42">
+        <f>chi_so_tai_chinh!I50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>%thực hiện</t>
+        </is>
+      </c>
+      <c r="B7" s="44">
+        <f>B6/B5</f>
+        <v/>
+      </c>
+      <c r="C7" s="44">
+        <f>C6/C5</f>
+        <v/>
+      </c>
+      <c r="D7" s="44">
+        <f>D6/D5</f>
+        <v/>
+      </c>
+      <c r="E7" s="44">
+        <f>E6/E5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="41" t="inlineStr">
+        <is>
+          <t>Lợi nhuận sau thuế kế hoạch</t>
+        </is>
+      </c>
+      <c r="B8" s="42" t="n">
+        <v>1319573000000</v>
+      </c>
+      <c r="C8" s="42" t="n">
+        <v>1937198000000</v>
+      </c>
+      <c r="D8" s="42" t="n">
+        <v>2089201000000</v>
+      </c>
+      <c r="E8" s="42" t="n">
+        <v>1959650000000</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="41" t="inlineStr">
+        <is>
+          <t>LNST thực hiện</t>
+        </is>
+      </c>
+      <c r="B9" s="42">
+        <f>chi_so_tai_chinh!F51</f>
+        <v/>
+      </c>
+      <c r="C9" s="42">
+        <f>chi_so_tai_chinh!G51</f>
+        <v/>
+      </c>
+      <c r="D9" s="42">
+        <f>chi_so_tai_chinh!H51</f>
+        <v/>
+      </c>
+      <c r="E9" s="42">
+        <f>chi_so_tai_chinh!I51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>%thực hiện</t>
+        </is>
+      </c>
+      <c r="B10" s="44">
+        <f>B9/B8</f>
+        <v/>
+      </c>
+      <c r="C10" s="44">
+        <f>C9/C8</f>
+        <v/>
+      </c>
+      <c r="D10" s="44">
+        <f>D9/D8</f>
+        <v/>
+      </c>
+      <c r="E10" s="44">
+        <f>E9/E8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="41" t="n"/>
+      <c r="B11" s="41" t="n"/>
+      <c r="C11" s="41" t="n"/>
+      <c r="D11" s="41" t="n"/>
+      <c r="E11" s="41" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="41" t="n"/>
+      <c r="B12" s="41" t="n"/>
+      <c r="C12" s="41" t="n"/>
+      <c r="D12" s="41" t="n"/>
+      <c r="E12" s="41" t="n"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>Trung vị %thực hiện DT</t>
+        </is>
+      </c>
+      <c r="B13" s="44">
+        <f>MEDIAN(B4:D4)</f>
+        <v/>
+      </c>
+      <c r="C13" s="41" t="n"/>
+      <c r="D13" s="41" t="n"/>
+      <c r="E13" s="41" t="n"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>Trung vị %thực hiện LNTT</t>
+        </is>
+      </c>
+      <c r="B14" s="44">
+        <f>MEDIAN(B7:D7)</f>
+        <v/>
+      </c>
+      <c r="C14" s="41" t="n"/>
+      <c r="D14" s="41" t="n"/>
+      <c r="E14" s="41" t="n"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>Trung vị %thực hiện LNST</t>
+        </is>
+      </c>
+      <c r="B15" s="44">
+        <f>MEDIAN(B10:D10)</f>
+        <v/>
+      </c>
+      <c r="C15" s="41" t="n"/>
+      <c r="D15" s="41" t="n"/>
+      <c r="E15" s="41" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="41" t="n"/>
+      <c r="B16" s="41" t="n"/>
+      <c r="C16" s="41" t="n"/>
+      <c r="D16" s="41" t="n"/>
+      <c r="E16" s="41" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="41" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành DT trên 95%</t>
+        </is>
+      </c>
+      <c r="B17" s="45">
+        <f>COUNTIF(B4:F4,"&gt;=95%")/COUNT(B4:F4)</f>
+        <v/>
+      </c>
+      <c r="C17" s="41" t="n"/>
+      <c r="D17" s="41" t="n"/>
+      <c r="E17" s="41" t="n"/>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="41" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành LNST trên 95%</t>
+        </is>
+      </c>
+      <c r="B18" s="45">
+        <f>COUNTIF(B7:F7,"&gt;=95%")/COUNT(B7:F7)</f>
+        <v/>
+      </c>
+      <c r="C18" s="41" t="n"/>
+      <c r="D18" s="41" t="n"/>
+      <c r="E18" s="41" t="n"/>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="41" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành LNTT trên 95%</t>
+        </is>
+      </c>
+      <c r="B19" s="45">
+        <f>COUNTIF(B10:F10,"&gt;=95%")/COUNT(B10:F10)</f>
+        <v/>
+      </c>
+      <c r="C19" s="41" t="n"/>
+      <c r="D19" s="41" t="n"/>
+      <c r="E19" s="41" t="n"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B13:B15">
+    <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="3">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4:E4">
+    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" dxfId="3">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:E7">
+    <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" dxfId="3">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10:E10">
+    <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" dxfId="3">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/financials/PNJ/PNJ.xlsx
+++ b/financials/PNJ/PNJ.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="12000" yWindow="4785" windowWidth="12000" windowHeight="8115" tabRatio="600" firstSheet="4" activeTab="5" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="4545" windowWidth="24000" windowHeight="8355" tabRatio="600" firstSheet="3" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,10 +13,6 @@
     <sheet name="Dự phóng tăng trưởng" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Sheet1" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId7"/>
-    <externalReference r:id="rId8"/>
-  </externalReferences>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -358,7 +354,7 @@
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="18">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -489,38 +485,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -592,59 +556,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook r:id="rId1">
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="B2">
-            <v>21850</v>
-          </cell>
-          <cell r="E2">
-            <v>32650</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook r:id="rId1">
-    <sheetNames>
-      <sheetName val="CĐKT"/>
-      <sheetName val="KQHĐKD"/>
-      <sheetName val="LCTT"/>
-      <sheetName val="Tổng quan"/>
-      <sheetName val="Dự báo tăng trưởng"/>
-      <sheetName val="Hiệu quả thực hiện KH"/>
-      <sheetName val="Số CH"/>
-      <sheetName val="Chart"/>
-      <sheetName val="Phân tích"/>
-      <sheetName val="Chỉ số"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10101,41 +10012,32 @@
           <t>Thị giá</t>
         </is>
       </c>
-      <c r="B3" s="27">
-        <f>[1]Sheet1!$E$2</f>
-        <v/>
-      </c>
-      <c r="C3" s="27">
-        <f>[1]Sheet1!$E$2</f>
-        <v/>
-      </c>
-      <c r="D3" s="27">
-        <f>[1]Sheet1!$E$2</f>
-        <v/>
-      </c>
-      <c r="E3" s="27">
-        <f>[1]Sheet1!$E$2</f>
-        <v/>
-      </c>
-      <c r="F3" s="27">
-        <f>[1]Sheet1!$E$2</f>
-        <v/>
-      </c>
-      <c r="G3" s="27">
-        <f>[1]Sheet1!$E$2</f>
-        <v/>
-      </c>
-      <c r="H3" s="27">
-        <f>[1]Sheet1!$E$2</f>
-        <v/>
-      </c>
-      <c r="I3" s="27">
-        <f>[1]Sheet1!$E$2</f>
-        <v/>
-      </c>
-      <c r="J3" s="27">
-        <f>[1]Sheet1!$E$2</f>
-        <v/>
+      <c r="B3" s="27" t="n">
+        <v>32650</v>
+      </c>
+      <c r="C3" s="27" t="n">
+        <v>32650</v>
+      </c>
+      <c r="D3" s="27" t="n">
+        <v>32650</v>
+      </c>
+      <c r="E3" s="27" t="n">
+        <v>32650</v>
+      </c>
+      <c r="F3" s="27" t="n">
+        <v>32650</v>
+      </c>
+      <c r="G3" s="27" t="n">
+        <v>32650</v>
+      </c>
+      <c r="H3" s="27" t="n">
+        <v>32650</v>
+      </c>
+      <c r="I3" s="27" t="n">
+        <v>32650</v>
+      </c>
+      <c r="J3" s="27" t="n">
+        <v>32650</v>
       </c>
     </row>
     <row r="4">
@@ -10232,7 +10134,10 @@
           <t>LICĐKKS</t>
         </is>
       </c>
-      <c r="B7" s="25" t="n"/>
+      <c r="B7" s="25">
+        <f>chi_so_tai_chinh!I41</f>
+        <v/>
+      </c>
       <c r="C7" s="62" t="n">
         <v>0</v>
       </c>
@@ -10254,9 +10159,8 @@
       <c r="I7" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="62">
-        <f>[2]CĐKT!J135*1000000000</f>
-        <v/>
+      <c r="J7" s="62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">

--- a/financials/PNJ/PNJ.xlsx
+++ b/financials/PNJ/PNJ.xlsx
@@ -11,6 +11,8 @@
     <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Dự phóng tăng trưởng" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,22 +21,21 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="167" formatCode="0.00\x"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="169" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <name val="Tahoma"/>
@@ -82,6 +83,12 @@
     </font>
     <font>
       <name val="Tahoma"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
       <charset val="1"/>
       <family val="2"/>
       <color rgb="FF008000"/>
@@ -92,11 +99,72 @@
       <charset val="1"/>
       <family val="2"/>
       <b val="1"/>
+      <color rgb="FF008000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF7030A0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <charset val="163"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <charset val="163"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF008000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
       <color theme="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <color rgb="FF7030A0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -110,24 +178,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.7999816888943144"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
         <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -160,62 +228,83 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color auto="1"/>
       </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="41" fontId="17" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="17" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
@@ -234,6 +323,14 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6603,14 +6700,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38.33203125" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="3" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="38.375" customWidth="1" min="1" max="1"/>
+    <col width="18.25" customWidth="1" min="2" max="2"/>
+    <col width="20.5" customWidth="1" min="9" max="9"/>
+    <col width="17.125" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6651,6 +6747,18 @@
         <f>balance_sheet!I1</f>
         <v/>
       </c>
+      <c r="J1" s="6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K1" s="6" t="n">
+        <v>2027</v>
+      </c>
+      <c r="L1" s="6" t="n">
+        <v>2028</v>
+      </c>
+      <c r="M1" s="6" t="n">
+        <v>2029</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -6664,31 +6772,47 @@
         </is>
       </c>
       <c r="C2" s="8">
-        <f>IFERROR(C$39/((C$24+B$24)/2),"n/a")</f>
+        <f>IFERROR(C$54/((C$39+B$39)/2),"n/a")</f>
         <v/>
       </c>
       <c r="D2" s="8">
-        <f>IFERROR(D$39/((D$24+C$24)/2),"n/a")</f>
+        <f>IFERROR(D$54/((D$39+C$39)/2),"n/a")</f>
         <v/>
       </c>
       <c r="E2" s="8">
-        <f>IFERROR(E$39/((E$24+D$24)/2),"n/a")</f>
+        <f>IFERROR(E$54/((E$39+D$39)/2),"n/a")</f>
         <v/>
       </c>
       <c r="F2" s="8">
-        <f>IFERROR(F$39/((F$24+E$24)/2),"n/a")</f>
+        <f>IFERROR(F$54/((F$39+E$39)/2),"n/a")</f>
         <v/>
       </c>
       <c r="G2" s="8">
-        <f>IFERROR(G$39/((G$24+F$24)/2),"n/a")</f>
+        <f>IFERROR(G$54/((G$39+F$39)/2),"n/a")</f>
         <v/>
       </c>
       <c r="H2" s="8">
-        <f>IFERROR(H$39/((H$24+G$24)/2),"n/a")</f>
+        <f>IFERROR(H$54/((H$39+G$39)/2),"n/a")</f>
         <v/>
       </c>
       <c r="I2" s="8">
-        <f>IFERROR(I$39/((I$24+H$24)/2),"n/a")</f>
+        <f>IFERROR(I$54/((I$39+H$39)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="J2" s="8">
+        <f>IFERROR(J$54/((J$39+I$39)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="K2" s="8">
+        <f>IFERROR(K$54/((K$39+J$39)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="L2" s="8">
+        <f>IFERROR(L$54/((L$39+K$39)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="M2" s="8">
+        <f>IFERROR(M$54/((M$39+L$39)/2),"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6704,31 +6828,31 @@
         </is>
       </c>
       <c r="C3" s="8">
-        <f>IFERROR(C$38/((C$25+B$25)/2),"n/a")</f>
+        <f>IFERROR(C$52/((C$31+B$31)/2),"n/a")</f>
         <v/>
       </c>
       <c r="D3" s="8">
-        <f>IFERROR(D$38/((D$25+C$25)/2),"n/a")</f>
+        <f>IFERROR(D$52/((D$31+C$31)/2),"n/a")</f>
         <v/>
       </c>
       <c r="E3" s="8">
-        <f>IFERROR(E$38/((E$25+D$25)/2),"n/a")</f>
+        <f>IFERROR(E$52/((E$31+D$31)/2),"n/a")</f>
         <v/>
       </c>
       <c r="F3" s="8">
-        <f>IFERROR(F$38/((F$25+E$25)/2),"n/a")</f>
+        <f>IFERROR(F$52/((F$31+E$31)/2),"n/a")</f>
         <v/>
       </c>
       <c r="G3" s="8">
-        <f>IFERROR(G$38/((G$25+F$25)/2),"n/a")</f>
+        <f>IFERROR(G$52/((G$31+F$31)/2),"n/a")</f>
         <v/>
       </c>
       <c r="H3" s="8">
-        <f>IFERROR(H$38/((H$25+G$25)/2),"n/a")</f>
+        <f>IFERROR(H$52/((H$31+G$31)/2),"n/a")</f>
         <v/>
       </c>
       <c r="I3" s="8">
-        <f>IFERROR(I$38/((I$25+H$25)/2),"n/a")</f>
+        <f>IFERROR(I$52/((I$31+H$31)/2),"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6744,31 +6868,47 @@
         </is>
       </c>
       <c r="C4" s="8">
-        <f>IFERROR((C$39-B$39)/ABS(B$39),"n/a")</f>
+        <f>IFERROR((C$54-B$54)/ABS(B$54),"n/a")</f>
         <v/>
       </c>
       <c r="D4" s="8">
-        <f>IFERROR((D$39-C$39)/ABS(C$39),"n/a")</f>
+        <f>IFERROR((D$54-C$54)/ABS(C$54),"n/a")</f>
         <v/>
       </c>
       <c r="E4" s="8">
-        <f>IFERROR((E$39-D$39)/ABS(D$39),"n/a")</f>
+        <f>IFERROR((E$54-D$54)/ABS(D$54),"n/a")</f>
         <v/>
       </c>
       <c r="F4" s="8">
-        <f>IFERROR((F$39-E$39)/ABS(E$39),"n/a")</f>
+        <f>IFERROR((F$54-E$54)/ABS(E$54),"n/a")</f>
         <v/>
       </c>
       <c r="G4" s="8">
-        <f>IFERROR((G$39-F$39)/ABS(F$39),"n/a")</f>
+        <f>IFERROR((G$54-F$54)/ABS(F$54),"n/a")</f>
         <v/>
       </c>
       <c r="H4" s="8">
-        <f>IFERROR((H$39-G$39)/ABS(G$39),"n/a")</f>
+        <f>IFERROR((H$54-G$54)/ABS(G$54),"n/a")</f>
         <v/>
       </c>
       <c r="I4" s="8">
-        <f>IFERROR((I$39-H$39)/ABS(H$39),"n/a")</f>
+        <f>IFERROR((I$54-H$54)/ABS(H$54),"n/a")</f>
+        <v/>
+      </c>
+      <c r="J4" s="8">
+        <f>IFERROR((J$54-I$54)/ABS(I$54),"n/a")</f>
+        <v/>
+      </c>
+      <c r="K4" s="8">
+        <f>IFERROR((K$54-J$54)/ABS(J$54),"n/a")</f>
+        <v/>
+      </c>
+      <c r="L4" s="8">
+        <f>IFERROR((L$54-K$54)/ABS(K$54),"n/a")</f>
+        <v/>
+      </c>
+      <c r="M4" s="8">
+        <f>IFERROR((M$54-L$54)/ABS(L$54),"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6784,31 +6924,47 @@
         </is>
       </c>
       <c r="C5" s="8">
-        <f>IFERROR((C$31-B$31)/ABS(B$31),"n/a")</f>
+        <f>IFERROR((C$44-B$44)/ABS(B$44),"n/a")</f>
         <v/>
       </c>
       <c r="D5" s="8">
-        <f>IFERROR((D$31-C$31)/ABS(C$31),"n/a")</f>
+        <f>IFERROR((D$44-C$44)/ABS(C$44),"n/a")</f>
         <v/>
       </c>
       <c r="E5" s="8">
-        <f>IFERROR((E$31-D$31)/ABS(D$31),"n/a")</f>
+        <f>IFERROR((E$44-D$44)/ABS(D$44),"n/a")</f>
         <v/>
       </c>
       <c r="F5" s="8">
-        <f>IFERROR((F$31-E$31)/ABS(E$31),"n/a")</f>
+        <f>IFERROR((F$44-E$44)/ABS(E$44),"n/a")</f>
         <v/>
       </c>
       <c r="G5" s="8">
-        <f>IFERROR((G$31-F$31)/ABS(F$31),"n/a")</f>
+        <f>IFERROR((G$44-F$44)/ABS(F$44),"n/a")</f>
         <v/>
       </c>
       <c r="H5" s="8">
-        <f>IFERROR((H$31-G$31)/ABS(G$31),"n/a")</f>
+        <f>IFERROR((H$44-G$44)/ABS(G$44),"n/a")</f>
         <v/>
       </c>
       <c r="I5" s="8">
-        <f>IFERROR((I$31-H$31)/ABS(H$31),"n/a")</f>
+        <f>IFERROR((I$44-H$44)/ABS(H$44),"n/a")</f>
+        <v/>
+      </c>
+      <c r="J5" s="8">
+        <f>IFERROR((J$44-I$44)/ABS(I$44),"n/a")</f>
+        <v/>
+      </c>
+      <c r="K5" s="8">
+        <f>IFERROR((K$44-J$44)/ABS(J$44),"n/a")</f>
+        <v/>
+      </c>
+      <c r="L5" s="8">
+        <f>IFERROR((L$44-K$44)/ABS(K$44),"n/a")</f>
+        <v/>
+      </c>
+      <c r="M5" s="8">
+        <f>IFERROR((M$44-L$44)/ABS(L$44),"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6819,35 +6975,51 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <f>IFERROR(B$33/B$31,"n/a")</f>
+        <f>IFERROR(B$46/B$44,"n/a")</f>
         <v/>
       </c>
       <c r="C6" s="8">
-        <f>IFERROR(C$33/C$31,"n/a")</f>
+        <f>IFERROR(C$46/C$44,"n/a")</f>
         <v/>
       </c>
       <c r="D6" s="8">
-        <f>IFERROR(D$33/D$31,"n/a")</f>
+        <f>IFERROR(D$46/D$44,"n/a")</f>
         <v/>
       </c>
       <c r="E6" s="8">
-        <f>IFERROR(E$33/E$31,"n/a")</f>
+        <f>IFERROR(E$46/E$44,"n/a")</f>
         <v/>
       </c>
       <c r="F6" s="8">
-        <f>IFERROR(F$33/F$31,"n/a")</f>
+        <f>IFERROR(F$46/F$44,"n/a")</f>
         <v/>
       </c>
       <c r="G6" s="8">
-        <f>IFERROR(G$33/G$31,"n/a")</f>
+        <f>IFERROR(G$46/G$44,"n/a")</f>
         <v/>
       </c>
       <c r="H6" s="8">
-        <f>IFERROR(H$33/H$31,"n/a")</f>
+        <f>IFERROR(H$46/H$44,"n/a")</f>
         <v/>
       </c>
       <c r="I6" s="8">
-        <f>IFERROR(I$33/I$31,"n/a")</f>
+        <f>IFERROR(I$46/I$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J6" s="8">
+        <f>IFERROR(J$46/J$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="K6" s="8">
+        <f>IFERROR(K$46/K$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="L6" s="8">
+        <f>IFERROR(L$46/L$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="M6" s="8">
+        <f>IFERROR(M$46/M$44,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6858,35 +7030,51 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>IFERROR(B$38/B$31,"n/a")</f>
+        <f>IFERROR(B$54/B$44,"n/a")</f>
         <v/>
       </c>
       <c r="C7" s="8">
-        <f>IFERROR(C$38/C$31,"n/a")</f>
+        <f>IFERROR(C$54/C$44,"n/a")</f>
         <v/>
       </c>
       <c r="D7" s="8">
-        <f>IFERROR(D$38/D$31,"n/a")</f>
+        <f>IFERROR(D$54/D$44,"n/a")</f>
         <v/>
       </c>
       <c r="E7" s="8">
-        <f>IFERROR(E$38/E$31,"n/a")</f>
+        <f>IFERROR(E$54/E$44,"n/a")</f>
         <v/>
       </c>
       <c r="F7" s="8">
-        <f>IFERROR(F$38/F$31,"n/a")</f>
+        <f>IFERROR(F$54/F$44,"n/a")</f>
         <v/>
       </c>
       <c r="G7" s="8">
-        <f>IFERROR(G$38/G$31,"n/a")</f>
+        <f>IFERROR(G$54/G$44,"n/a")</f>
         <v/>
       </c>
       <c r="H7" s="8">
-        <f>IFERROR(H$38/H$31,"n/a")</f>
+        <f>IFERROR(H$54/H$44,"n/a")</f>
         <v/>
       </c>
       <c r="I7" s="8">
-        <f>IFERROR(I$38/I$31,"n/a")</f>
+        <f>IFERROR(I$54/I$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="J7" s="8">
+        <f>IFERROR(J$54/J$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="K7" s="8">
+        <f>IFERROR(K$54/K$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="L7" s="8">
+        <f>IFERROR(L$54/L$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="M7" s="8">
+        <f>IFERROR(M$54/M$44,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6897,35 +7085,35 @@
         </is>
       </c>
       <c r="B8" s="9">
-        <f>IFERROR((B$29+B$30)/B$24,"n/a")</f>
+        <f>IFERROR((B$34+B$36)/B$39,"n/a")</f>
         <v/>
       </c>
       <c r="C8" s="9">
-        <f>IFERROR((C$29+C$30)/C$24,"n/a")</f>
+        <f>IFERROR((C$34+C$36)/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D8" s="9">
-        <f>IFERROR((D$29+D$30)/D$24,"n/a")</f>
+        <f>IFERROR((D$34+D$36)/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E8" s="9">
-        <f>IFERROR((E$29+E$30)/E$24,"n/a")</f>
+        <f>IFERROR((E$34+E$36)/E$39,"n/a")</f>
         <v/>
       </c>
       <c r="F8" s="9">
-        <f>IFERROR((F$29+F$30)/F$24,"n/a")</f>
+        <f>IFERROR((F$34+F$36)/F$39,"n/a")</f>
         <v/>
       </c>
       <c r="G8" s="9">
-        <f>IFERROR((G$29+G$30)/G$24,"n/a")</f>
+        <f>IFERROR((G$34+G$36)/G$39,"n/a")</f>
         <v/>
       </c>
       <c r="H8" s="9">
-        <f>IFERROR((H$29+H$30)/H$24,"n/a")</f>
+        <f>IFERROR((H$34+H$36)/H$39,"n/a")</f>
         <v/>
       </c>
       <c r="I8" s="9">
-        <f>IFERROR((I$29+I$30)/I$24,"n/a")</f>
+        <f>IFERROR((I$34+I$36)/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6936,35 +7124,35 @@
         </is>
       </c>
       <c r="B9" s="9">
-        <f>IFERROR(B$30/B$24,"n/a")</f>
+        <f>IFERROR(B$36/B$39,"n/a")</f>
         <v/>
       </c>
       <c r="C9" s="9">
-        <f>IFERROR(C$30/C$24,"n/a")</f>
+        <f>IFERROR(C$36/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D9" s="9">
-        <f>IFERROR(D$30/D$24,"n/a")</f>
+        <f>IFERROR(D$36/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E9" s="9">
-        <f>IFERROR(E$30/E$24,"n/a")</f>
+        <f>IFERROR(E$36/E$39,"n/a")</f>
         <v/>
       </c>
       <c r="F9" s="9">
-        <f>IFERROR(F$30/F$24,"n/a")</f>
+        <f>IFERROR(F$36/F$39,"n/a")</f>
         <v/>
       </c>
       <c r="G9" s="9">
-        <f>IFERROR(G$30/G$24,"n/a")</f>
+        <f>IFERROR(G$36/G$39,"n/a")</f>
         <v/>
       </c>
       <c r="H9" s="9">
-        <f>IFERROR(H$30/H$24,"n/a")</f>
+        <f>IFERROR(H$36/H$39,"n/a")</f>
         <v/>
       </c>
       <c r="I9" s="9">
-        <f>IFERROR(I$30/I$24,"n/a")</f>
+        <f>IFERROR(I$36/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -6975,35 +7163,35 @@
         </is>
       </c>
       <c r="B10" s="9">
-        <f>IFERROR(B$29/B$24,"n/a")</f>
+        <f>IFERROR(B$34/B$39,"n/a")</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(C$29/C$24,"n/a")</f>
+        <f>IFERROR(C$34/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>IFERROR(D$29/D$24,"n/a")</f>
+        <f>IFERROR(D$34/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E10" s="9">
-        <f>IFERROR(E$29/E$24,"n/a")</f>
+        <f>IFERROR(E$34/E$39,"n/a")</f>
         <v/>
       </c>
       <c r="F10" s="9">
-        <f>IFERROR(F$29/F$24,"n/a")</f>
+        <f>IFERROR(F$34/F$39,"n/a")</f>
         <v/>
       </c>
       <c r="G10" s="9">
-        <f>IFERROR(G$29/G$24,"n/a")</f>
+        <f>IFERROR(G$34/G$39,"n/a")</f>
         <v/>
       </c>
       <c r="H10" s="9">
-        <f>IFERROR(H$29/H$24,"n/a")</f>
+        <f>IFERROR(H$34/H$39,"n/a")</f>
         <v/>
       </c>
       <c r="I10" s="9">
-        <f>IFERROR(I$29/I$24,"n/a")</f>
+        <f>IFERROR(I$34/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7014,35 +7202,35 @@
         </is>
       </c>
       <c r="B11" s="9">
-        <f>IFERROR(B$26/B$24,"n/a")</f>
+        <f>IFERROR(B$38/B$39,"n/a")</f>
         <v/>
       </c>
       <c r="C11" s="9">
-        <f>IFERROR(C$26/C$24,"n/a")</f>
+        <f>IFERROR(C$38/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D11" s="9">
-        <f>IFERROR(D$26/D$24,"n/a")</f>
+        <f>IFERROR(D$38/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E11" s="9">
-        <f>IFERROR(E$26/E$24,"n/a")</f>
+        <f>IFERROR(E$38/E$39,"n/a")</f>
         <v/>
       </c>
       <c r="F11" s="9">
-        <f>IFERROR(F$26/F$24,"n/a")</f>
+        <f>IFERROR(F$38/F$39,"n/a")</f>
         <v/>
       </c>
       <c r="G11" s="9">
-        <f>IFERROR(G$26/G$24,"n/a")</f>
+        <f>IFERROR(G$38/G$39,"n/a")</f>
         <v/>
       </c>
       <c r="H11" s="9">
-        <f>IFERROR(H$26/H$24,"n/a")</f>
+        <f>IFERROR(H$38/H$39,"n/a")</f>
         <v/>
       </c>
       <c r="I11" s="9">
-        <f>IFERROR(I$26/I$24,"n/a")</f>
+        <f>IFERROR(I$38/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7053,35 +7241,35 @@
         </is>
       </c>
       <c r="B12" s="9">
-        <f>IFERROR(B$28/B$24,"n/a")</f>
+        <f>IFERROR(B$37/B$39,"n/a")</f>
         <v/>
       </c>
       <c r="C12" s="9">
-        <f>IFERROR(C$28/C$24,"n/a")</f>
+        <f>IFERROR(C$37/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D12" s="9">
-        <f>IFERROR(D$28/D$24,"n/a")</f>
+        <f>IFERROR(D$37/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E12" s="9">
-        <f>IFERROR(E$28/E$24,"n/a")</f>
+        <f>IFERROR(E$37/E$39,"n/a")</f>
         <v/>
       </c>
       <c r="F12" s="9">
-        <f>IFERROR(F$28/F$24,"n/a")</f>
+        <f>IFERROR(F$37/F$39,"n/a")</f>
         <v/>
       </c>
       <c r="G12" s="9">
-        <f>IFERROR(G$28/G$24,"n/a")</f>
+        <f>IFERROR(G$37/G$39,"n/a")</f>
         <v/>
       </c>
       <c r="H12" s="9">
-        <f>IFERROR(H$28/H$24,"n/a")</f>
+        <f>IFERROR(H$37/H$39,"n/a")</f>
         <v/>
       </c>
       <c r="I12" s="9">
-        <f>IFERROR(I$28/I$24,"n/a")</f>
+        <f>IFERROR(I$37/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7092,35 +7280,35 @@
         </is>
       </c>
       <c r="B13" s="9">
-        <f>IFERROR(B$27/B$24,"n/a")</f>
+        <f>IFERROR(B$35/B$39,"n/a")</f>
         <v/>
       </c>
       <c r="C13" s="9">
-        <f>IFERROR(C$27/C$24,"n/a")</f>
+        <f>IFERROR(C$35/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D13" s="9">
-        <f>IFERROR(D$27/D$24,"n/a")</f>
+        <f>IFERROR(D$35/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E13" s="9">
-        <f>IFERROR(E$27/E$24,"n/a")</f>
+        <f>IFERROR(E$35/E$39,"n/a")</f>
         <v/>
       </c>
       <c r="F13" s="9">
-        <f>IFERROR(F$27/F$24,"n/a")</f>
+        <f>IFERROR(F$35/F$39,"n/a")</f>
         <v/>
       </c>
       <c r="G13" s="9">
-        <f>IFERROR(G$27/G$24,"n/a")</f>
+        <f>IFERROR(G$35/G$39,"n/a")</f>
         <v/>
       </c>
       <c r="H13" s="9">
-        <f>IFERROR(H$27/H$24,"n/a")</f>
+        <f>IFERROR(H$35/H$39,"n/a")</f>
         <v/>
       </c>
       <c r="I13" s="9">
-        <f>IFERROR(I$27/I$24,"n/a")</f>
+        <f>IFERROR(I$35/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7131,35 +7319,35 @@
         </is>
       </c>
       <c r="B14" s="8">
-        <f>IFERROR((ABS(B$34)+ABS(B$35))/B$33,"n/a")</f>
+        <f>IFERROR((ABS(B$47)+ABS(B$48))/B$46,"n/a")</f>
         <v/>
       </c>
       <c r="C14" s="8">
-        <f>IFERROR((ABS(C$34)+ABS(C$35))/C$33,"n/a")</f>
+        <f>IFERROR((ABS(C$47)+ABS(C$48))/C$46,"n/a")</f>
         <v/>
       </c>
       <c r="D14" s="8">
-        <f>IFERROR((ABS(D$34)+ABS(D$35))/D$33,"n/a")</f>
+        <f>IFERROR((ABS(D$47)+ABS(D$48))/D$46,"n/a")</f>
         <v/>
       </c>
       <c r="E14" s="8">
-        <f>IFERROR((ABS(E$34)+ABS(E$35))/E$33,"n/a")</f>
+        <f>IFERROR((ABS(E$47)+ABS(E$48))/E$46,"n/a")</f>
         <v/>
       </c>
       <c r="F14" s="8">
-        <f>IFERROR((ABS(F$34)+ABS(F$35))/F$33,"n/a")</f>
+        <f>IFERROR((ABS(F$47)+ABS(F$48))/F$46,"n/a")</f>
         <v/>
       </c>
       <c r="G14" s="8">
-        <f>IFERROR((ABS(G$34)+ABS(G$35))/G$33,"n/a")</f>
+        <f>IFERROR((ABS(G$47)+ABS(G$48))/G$46,"n/a")</f>
         <v/>
       </c>
       <c r="H14" s="8">
-        <f>IFERROR((ABS(H$34)+ABS(H$35))/H$33,"n/a")</f>
+        <f>IFERROR((ABS(H$47)+ABS(H$48))/H$46,"n/a")</f>
         <v/>
       </c>
       <c r="I14" s="8">
-        <f>IFERROR((ABS(I$34)+ABS(I$35))/I$33,"n/a")</f>
+        <f>IFERROR((ABS(I$47)+ABS(I$48))/I$46,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7170,35 +7358,35 @@
         </is>
       </c>
       <c r="B15" s="8">
-        <f>IFERROR(ABS(B$37)/B$36,"n/a")</f>
+        <f>IFERROR(ABS(B$50)/B$49,"n/a")</f>
         <v/>
       </c>
       <c r="C15" s="8">
-        <f>IFERROR(ABS(C$37)/C$36,"n/a")</f>
+        <f>IFERROR(ABS(C$50)/C$49,"n/a")</f>
         <v/>
       </c>
       <c r="D15" s="8">
-        <f>IFERROR(ABS(D$37)/D$36,"n/a")</f>
+        <f>IFERROR(ABS(D$50)/D$49,"n/a")</f>
         <v/>
       </c>
       <c r="E15" s="8">
-        <f>IFERROR(ABS(E$37)/E$36,"n/a")</f>
+        <f>IFERROR(ABS(E$50)/E$49,"n/a")</f>
         <v/>
       </c>
       <c r="F15" s="8">
-        <f>IFERROR(ABS(F$37)/F$36,"n/a")</f>
+        <f>IFERROR(ABS(F$50)/F$49,"n/a")</f>
         <v/>
       </c>
       <c r="G15" s="8">
-        <f>IFERROR(ABS(G$37)/G$36,"n/a")</f>
+        <f>IFERROR(ABS(G$50)/G$49,"n/a")</f>
         <v/>
       </c>
       <c r="H15" s="8">
-        <f>IFERROR(ABS(H$37)/H$36,"n/a")</f>
+        <f>IFERROR(ABS(H$50)/H$49,"n/a")</f>
         <v/>
       </c>
       <c r="I15" s="8">
-        <f>IFERROR(ABS(I$37)/I$36,"n/a")</f>
+        <f>IFERROR(ABS(I$50)/I$49,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7214,31 +7402,31 @@
         </is>
       </c>
       <c r="C16" s="12">
-        <f>IFERROR(((C$41+B$41)/2)/ABS(C$32)*365,"n/a")</f>
+        <f>IFERROR(((C$33+B$33)/2)/ABS(C$45)*365,"n/a")</f>
         <v/>
       </c>
       <c r="D16" s="12">
-        <f>IFERROR(((D$41+C$41)/2)/ABS(D$32)*365,"n/a")</f>
+        <f>IFERROR(((D$33+C$33)/2)/ABS(D$45)*365,"n/a")</f>
         <v/>
       </c>
       <c r="E16" s="12">
-        <f>IFERROR(((E$41+D$41)/2)/ABS(E$32)*365,"n/a")</f>
+        <f>IFERROR(((E$33+D$33)/2)/ABS(E$45)*365,"n/a")</f>
         <v/>
       </c>
       <c r="F16" s="12">
-        <f>IFERROR(((F$41+E$41)/2)/ABS(F$32)*365,"n/a")</f>
+        <f>IFERROR(((F$33+E$33)/2)/ABS(F$45)*365,"n/a")</f>
         <v/>
       </c>
       <c r="G16" s="12">
-        <f>IFERROR(((G$41+F$41)/2)/ABS(G$32)*365,"n/a")</f>
+        <f>IFERROR(((G$33+F$33)/2)/ABS(G$45)*365,"n/a")</f>
         <v/>
       </c>
       <c r="H16" s="12">
-        <f>IFERROR(((H$41+G$41)/2)/ABS(H$32)*365,"n/a")</f>
+        <f>IFERROR(((H$33+G$33)/2)/ABS(H$45)*365,"n/a")</f>
         <v/>
       </c>
       <c r="I16" s="12">
-        <f>IFERROR(((I$41+H$41)/2)/ABS(I$32)*365,"n/a")</f>
+        <f>IFERROR(((I$33+H$33)/2)/ABS(I$45)*365,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7254,31 +7442,31 @@
         </is>
       </c>
       <c r="C17" s="12">
-        <f>IFERROR(((C$40+B$40)/2)/C$31*365,"n/a")</f>
+        <f>IFERROR(((C$27+B$27)/2)/C$44*365,"n/a")</f>
         <v/>
       </c>
       <c r="D17" s="12">
-        <f>IFERROR(((D$40+C$40)/2)/D$31*365,"n/a")</f>
+        <f>IFERROR(((D$27+C$27)/2)/D$44*365,"n/a")</f>
         <v/>
       </c>
       <c r="E17" s="12">
-        <f>IFERROR(((E$40+D$40)/2)/E$31*365,"n/a")</f>
+        <f>IFERROR(((E$27+D$27)/2)/E$44*365,"n/a")</f>
         <v/>
       </c>
       <c r="F17" s="12">
-        <f>IFERROR(((F$40+E$40)/2)/F$31*365,"n/a")</f>
+        <f>IFERROR(((F$27+E$27)/2)/F$44*365,"n/a")</f>
         <v/>
       </c>
       <c r="G17" s="12">
-        <f>IFERROR(((G$40+F$40)/2)/G$31*365,"n/a")</f>
+        <f>IFERROR(((G$27+F$27)/2)/G$44*365,"n/a")</f>
         <v/>
       </c>
       <c r="H17" s="12">
-        <f>IFERROR(((H$40+G$40)/2)/H$31*365,"n/a")</f>
+        <f>IFERROR(((H$27+G$27)/2)/H$44*365,"n/a")</f>
         <v/>
       </c>
       <c r="I17" s="12">
-        <f>IFERROR(((I$40+H$40)/2)/I$31*365,"n/a")</f>
+        <f>IFERROR(((I$27+H$27)/2)/I$44*365,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7294,31 +7482,31 @@
         </is>
       </c>
       <c r="C18" s="12">
-        <f>IFERROR(((C$42+B$42)/2)/ABS(C$32)*365,"n/a")</f>
+        <f>IFERROR(((C$28+B$28)/2)/ABS(C$45)*365,"n/a")</f>
         <v/>
       </c>
       <c r="D18" s="12">
-        <f>IFERROR(((D$42+C$42)/2)/ABS(D$32)*365,"n/a")</f>
+        <f>IFERROR(((D$28+C$28)/2)/ABS(D$45)*365,"n/a")</f>
         <v/>
       </c>
       <c r="E18" s="12">
-        <f>IFERROR(((E$42+D$42)/2)/ABS(E$32)*365,"n/a")</f>
+        <f>IFERROR(((E$28+D$28)/2)/ABS(E$45)*365,"n/a")</f>
         <v/>
       </c>
       <c r="F18" s="12">
-        <f>IFERROR(((F$42+E$42)/2)/ABS(F$32)*365,"n/a")</f>
+        <f>IFERROR(((F$28+E$28)/2)/ABS(F$45)*365,"n/a")</f>
         <v/>
       </c>
       <c r="G18" s="12">
-        <f>IFERROR(((G$42+F$42)/2)/ABS(G$32)*365,"n/a")</f>
+        <f>IFERROR(((G$28+F$28)/2)/ABS(G$45)*365,"n/a")</f>
         <v/>
       </c>
       <c r="H18" s="12">
-        <f>IFERROR(((H$42+G$42)/2)/ABS(H$32)*365,"n/a")</f>
+        <f>IFERROR(((H$28+G$28)/2)/ABS(H$45)*365,"n/a")</f>
         <v/>
       </c>
       <c r="I18" s="12">
-        <f>IFERROR(((I$42+H$42)/2)/ABS(I$32)*365,"n/a")</f>
+        <f>IFERROR(((I$28+H$28)/2)/ABS(I$45)*365,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7329,35 +7517,35 @@
         </is>
       </c>
       <c r="B19" s="8">
-        <f>IFERROR(B$43/B$25,"n/a")</f>
+        <f>IFERROR(B$26/B$31,"n/a")</f>
         <v/>
       </c>
       <c r="C19" s="8">
-        <f>IFERROR(C$43/C$25,"n/a")</f>
+        <f>IFERROR(C$26/C$31,"n/a")</f>
         <v/>
       </c>
       <c r="D19" s="8">
-        <f>IFERROR(D$43/D$25,"n/a")</f>
+        <f>IFERROR(D$26/D$31,"n/a")</f>
         <v/>
       </c>
       <c r="E19" s="8">
-        <f>IFERROR(E$43/E$25,"n/a")</f>
+        <f>IFERROR(E$26/E$31,"n/a")</f>
         <v/>
       </c>
       <c r="F19" s="8">
-        <f>IFERROR(F$43/F$25,"n/a")</f>
+        <f>IFERROR(F$26/F$31,"n/a")</f>
         <v/>
       </c>
       <c r="G19" s="8">
-        <f>IFERROR(G$43/G$25,"n/a")</f>
+        <f>IFERROR(G$26/G$31,"n/a")</f>
         <v/>
       </c>
       <c r="H19" s="8">
-        <f>IFERROR(H$43/H$25,"n/a")</f>
+        <f>IFERROR(H$26/H$31,"n/a")</f>
         <v/>
       </c>
       <c r="I19" s="8">
-        <f>IFERROR(I$43/I$25,"n/a")</f>
+        <f>IFERROR(I$26/I$31,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7368,35 +7556,35 @@
         </is>
       </c>
       <c r="B20" s="8">
-        <f>IFERROR(B$42/B$25,"n/a")</f>
+        <f>IFERROR(B$28/B$31,"n/a")</f>
         <v/>
       </c>
       <c r="C20" s="8">
-        <f>IFERROR(C$42/C$25,"n/a")</f>
+        <f>IFERROR(C$28/C$31,"n/a")</f>
         <v/>
       </c>
       <c r="D20" s="8">
-        <f>IFERROR(D$42/D$25,"n/a")</f>
+        <f>IFERROR(D$28/D$31,"n/a")</f>
         <v/>
       </c>
       <c r="E20" s="8">
-        <f>IFERROR(E$42/E$25,"n/a")</f>
+        <f>IFERROR(E$28/E$31,"n/a")</f>
         <v/>
       </c>
       <c r="F20" s="8">
-        <f>IFERROR(F$42/F$25,"n/a")</f>
+        <f>IFERROR(F$28/F$31,"n/a")</f>
         <v/>
       </c>
       <c r="G20" s="8">
-        <f>IFERROR(G$42/G$25,"n/a")</f>
+        <f>IFERROR(G$28/G$31,"n/a")</f>
         <v/>
       </c>
       <c r="H20" s="8">
-        <f>IFERROR(H$42/H$25,"n/a")</f>
+        <f>IFERROR(H$28/H$31,"n/a")</f>
         <v/>
       </c>
       <c r="I20" s="8">
-        <f>IFERROR(I$42/I$25,"n/a")</f>
+        <f>IFERROR(I$28/I$31,"n/a")</f>
         <v/>
       </c>
     </row>
@@ -7458,1928 +7646,2261 @@
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I24" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
+          <t>CĐKT</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="16" t="n"/>
+      <c r="F24" s="16" t="n"/>
+      <c r="G24" s="16" t="n"/>
+      <c r="H24" s="16" t="n"/>
+      <c r="I24" s="16" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="17" t="inlineStr">
         <is>
+          <t>Tài sản</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="16" t="n"/>
+      <c r="F25" s="16" t="n"/>
+      <c r="G25" s="16" t="n"/>
+      <c r="H25" s="16" t="n"/>
+      <c r="I25" s="16" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>Tiền và tương đương tiền</t>
+        </is>
+      </c>
+      <c r="B26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>Phải thu khách hàng</t>
+        </is>
+      </c>
+      <c r="B27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I27" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>Hàng tồn kho, ròng</t>
+        </is>
+      </c>
+      <c r="B28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>TÀI SẢN NGẮN HẠN</t>
+        </is>
+      </c>
+      <c r="B29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I29" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>GTCL tài sản cố định vô hình</t>
+        </is>
+      </c>
+      <c r="B30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I30" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
           <t>TỔNG CỘNG TÀI SẢN</t>
         </is>
       </c>
-      <c r="B25" s="18">
+      <c r="B31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C25" s="18">
+      <c r="C31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D25" s="18">
+      <c r="D31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E25" s="18">
+      <c r="E31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F25" s="18">
+      <c r="F31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G25" s="18">
+      <c r="G31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H25" s="18">
+      <c r="H31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I25" s="18">
+      <c r="I31" s="19">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>NỢ PHẢI TRẢ</t>
-        </is>
-      </c>
-      <c r="B26" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C26" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D26" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E26" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F26" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G26" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I26" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>Nợ ngắn hạn</t>
-        </is>
-      </c>
-      <c r="B27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I27" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>Nợ dài hạn</t>
-        </is>
-      </c>
-      <c r="B28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I28" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>Vay ngắn hạn</t>
-        </is>
-      </c>
-      <c r="B29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I29" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>Vay dài hạn</t>
-        </is>
-      </c>
-      <c r="B30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I30" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>Doanh thu thuần</t>
-        </is>
-      </c>
-      <c r="B31" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C31" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D31" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E31" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F31" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G31" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I31" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
+          <t>Nguồn vốn</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="n"/>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="16" t="n"/>
+      <c r="E32" s="16" t="n"/>
+      <c r="F32" s="16" t="n"/>
+      <c r="G32" s="16" t="n"/>
+      <c r="H32" s="16" t="n"/>
+      <c r="I32" s="16" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>Phải trả người bán</t>
+        </is>
+      </c>
+      <c r="B33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I33" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>Vay ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>Nợ ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I35" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>Vay dài hạn</t>
+        </is>
+      </c>
+      <c r="B36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I36" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>Nợ dài hạn</t>
+        </is>
+      </c>
+      <c r="B37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I37" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>NỢ PHẢI TRẢ</t>
+        </is>
+      </c>
+      <c r="B38" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C38" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I38" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I39" s="20">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="20">
+        <f>I39+J54</f>
+        <v/>
+      </c>
+      <c r="K39" s="20">
+        <f>J39+0.65*K54</f>
+        <v/>
+      </c>
+      <c r="L39" s="20">
+        <f>K39+0.65*L54</f>
+        <v/>
+      </c>
+      <c r="M39" s="20">
+        <f>L39+0.65*M54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>Tăng VCSH/LN cổ đông cty mẹ</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="n"/>
+      <c r="C40" s="23">
+        <f>(C39-B39)/C54</f>
+        <v/>
+      </c>
+      <c r="D40" s="23">
+        <f>(D39-C39)/D54</f>
+        <v/>
+      </c>
+      <c r="E40" s="23">
+        <f>(E39-D39)/E54</f>
+        <v/>
+      </c>
+      <c r="F40" s="23">
+        <f>(F39-E39)/F54</f>
+        <v/>
+      </c>
+      <c r="G40" s="23">
+        <f>(G39-F39)/G54</f>
+        <v/>
+      </c>
+      <c r="H40" s="23">
+        <f>(H39-G39)/H54</f>
+        <v/>
+      </c>
+      <c r="I40" s="23">
+        <f>(I39-H39)/I54</f>
+        <v/>
+      </c>
+      <c r="J40" s="24" t="n"/>
+      <c r="K40" s="24" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>Lợi ích của cổ đông thiểu số</t>
+        </is>
+      </c>
+      <c r="B41" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C41" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D41" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I41" s="19">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J41">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Lợi ích của cổ đông thiểu số",balance_sheet!$A:$A,0),MATCH(J$23,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>Kết quả hoạt động kinh doanh</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>Doanh thu bán hàng và cung cấp dịch vụ</t>
+        </is>
+      </c>
+      <c r="B43" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu bán hàng và cung cấp dịch vụ",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C43" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu bán hàng và cung cấp dịch vụ",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D43" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu bán hàng và cung cấp dịch vụ",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu bán hàng và cung cấp dịch vụ",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu bán hàng và cung cấp dịch vụ",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu bán hàng và cung cấp dịch vụ",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu bán hàng và cung cấp dịch vụ",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I43" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu bán hàng và cung cấp dịch vụ",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J43" s="20" t="n">
+        <v>39100000000000</v>
+      </c>
+      <c r="K43" s="20" t="n">
+        <v>43400000000000</v>
+      </c>
+      <c r="L43" s="20" t="n">
+        <v>50600000000000</v>
+      </c>
+      <c r="M43" s="20" t="n">
+        <v>57700000000000</v>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>Doanh thu thuần</t>
+        </is>
+      </c>
+      <c r="B44" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C44" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D44" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I44" s="20">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J44" s="20">
+        <f>J43*0.99</f>
+        <v/>
+      </c>
+      <c r="K44" s="20">
+        <f>K43*0.99</f>
+        <v/>
+      </c>
+      <c r="L44" s="20">
+        <f>L43*0.99</f>
+        <v/>
+      </c>
+      <c r="M44" s="20">
+        <f>M43*0.99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
           <t>Giá vốn hàng bán</t>
         </is>
       </c>
-      <c r="B32" s="18">
+      <c r="B45" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C32" s="18">
+      <c r="C45" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D32" s="18">
+      <c r="D45" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E32" s="18">
+      <c r="E45" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F32" s="18">
+      <c r="F45" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G32" s="18">
+      <c r="G45" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H32" s="18">
+      <c r="H45" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I32" s="18">
+      <c r="I45" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="15" t="inlineStr">
         <is>
           <t>Lợi nhuận gộp</t>
         </is>
       </c>
-      <c r="B33" s="18">
+      <c r="B46" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C33" s="18">
+      <c r="C46" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D33" s="18">
+      <c r="D46" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E33" s="18">
+      <c r="E46" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F33" s="18">
+      <c r="F46" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G33" s="18">
+      <c r="G46" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H33" s="18">
+      <c r="H46" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I33" s="18">
+      <c r="I46" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="J46" s="20" t="n">
+        <v>-2400000000000</v>
+      </c>
+      <c r="K46" s="20" t="n">
+        <v>3800000000000</v>
+      </c>
+      <c r="L46" s="20" t="n">
+        <v>5500000000000</v>
+      </c>
+      <c r="M46" s="20" t="n">
+        <v>6300000000000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="18" t="inlineStr">
         <is>
           <t>Chi phí bán hàng</t>
         </is>
       </c>
-      <c r="B34" s="18">
+      <c r="B47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C34" s="18">
+      <c r="C47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D34" s="18">
+      <c r="D47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E34" s="18">
+      <c r="E47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F34" s="18">
+      <c r="F47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G34" s="18">
+      <c r="G47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H34" s="18">
+      <c r="H47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I34" s="18">
+      <c r="I47" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="18" t="inlineStr">
         <is>
           <t>Chi phí quản lý doanh nghiệp</t>
         </is>
       </c>
-      <c r="B35" s="18">
+      <c r="B48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C35" s="18">
+      <c r="C48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D35" s="18">
+      <c r="D48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E35" s="18">
+      <c r="E48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F35" s="18">
+      <c r="F48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G35" s="18">
+      <c r="G48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H35" s="18">
+      <c r="H48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I35" s="18">
+      <c r="I48" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="18" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) từ hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="B36" s="18">
+      <c r="B49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C36" s="18">
+      <c r="C49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D36" s="18">
+      <c r="D49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E36" s="18">
+      <c r="E49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F36" s="18">
+      <c r="F49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G36" s="18">
+      <c r="G49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H36" s="18">
+      <c r="H49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I36" s="18">
+      <c r="I49" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="18" t="inlineStr">
         <is>
           <t>Chi phí lãi vay</t>
         </is>
       </c>
-      <c r="B37" s="18">
+      <c r="B50" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C37" s="18">
+      <c r="C50" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D37" s="18">
+      <c r="D50" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E37" s="18">
+      <c r="E50" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F37" s="18">
+      <c r="F50" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G37" s="18">
+      <c r="G50" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H37" s="18">
+      <c r="H50" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I37" s="18">
+      <c r="I50" s="19">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>Lãi/(lỗ) trước thuế</t>
+        </is>
+      </c>
+      <c r="B51" s="27">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C51" s="27">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D51" s="27">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E51" s="27">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F51" s="27">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G51" s="27">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="27">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I51" s="27">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) trước thuế",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J51" s="27" t="n">
+        <v>-6100000000000</v>
+      </c>
+      <c r="K51" s="27" t="n">
+        <v>200000000000</v>
+      </c>
+      <c r="L51" s="27" t="n">
+        <v>1600000000000</v>
+      </c>
+      <c r="M51" s="27" t="n">
+        <v>2000000000000</v>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="15" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) thuần sau thuế</t>
         </is>
       </c>
-      <c r="B38" s="18">
+      <c r="B52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C38" s="18">
+      <c r="C52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D38" s="18">
+      <c r="D52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E38" s="18">
+      <c r="E52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F38" s="18">
+      <c r="F52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G38" s="18">
+      <c r="G52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H38" s="18">
+      <c r="H52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I38" s="18">
+      <c r="I52" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="J52" s="27" t="n">
+        <v>-6600000000000</v>
+      </c>
+      <c r="K52" s="27">
+        <f>K51*0.797</f>
+        <v/>
+      </c>
+      <c r="L52" s="27">
+        <f>L51*0.797</f>
+        <v/>
+      </c>
+      <c r="M52" s="27">
+        <f>M51*0.797</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>LN sau thuế/LN trước thuế</t>
+        </is>
+      </c>
+      <c r="B53" s="28">
+        <f>B52/B51</f>
+        <v/>
+      </c>
+      <c r="C53" s="28">
+        <f>C52/C51</f>
+        <v/>
+      </c>
+      <c r="D53" s="28">
+        <f>D52/D51</f>
+        <v/>
+      </c>
+      <c r="E53" s="28">
+        <f>E52/E51</f>
+        <v/>
+      </c>
+      <c r="F53" s="28">
+        <f>F52/F51</f>
+        <v/>
+      </c>
+      <c r="G53" s="28">
+        <f>G52/G51</f>
+        <v/>
+      </c>
+      <c r="H53" s="28">
+        <f>H52/H51</f>
+        <v/>
+      </c>
+      <c r="I53" s="28">
+        <f>I52/I51</f>
+        <v/>
+      </c>
+      <c r="J53" s="28" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="15" t="inlineStr">
         <is>
           <t>Lợi nhuận của Cổ đông của Công ty mẹ</t>
         </is>
       </c>
-      <c r="B39" s="18">
+      <c r="B54" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(B$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C39" s="18">
+      <c r="C54" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(C$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D39" s="18">
+      <c r="D54" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(D$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E39" s="18">
+      <c r="E54" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(E$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F39" s="18">
+      <c r="F54" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(F$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G39" s="18">
+      <c r="G54" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(G$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H39" s="18">
+      <c r="H54" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(H$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I39" s="18">
+      <c r="I54" s="20">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(I$23,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t>Phải thu khách hàng</t>
-        </is>
-      </c>
-      <c r="B40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="17" t="inlineStr">
-        <is>
-          <t>Phải trả người bán</t>
-        </is>
-      </c>
-      <c r="B41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>Hàng tồn kho, ròng</t>
-        </is>
-      </c>
-      <c r="B42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>Tiền và tương đương tiền</t>
-        </is>
-      </c>
-      <c r="B43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I43" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="17" t="inlineStr">
-        <is>
-          <t>TÀI SẢN NGẮN HẠN</t>
-        </is>
-      </c>
-      <c r="B44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I44" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TÀI SẢN NGẮN HẠN",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="17" t="inlineStr">
-        <is>
-          <t>GTCL tài sản cố định vô hình</t>
-        </is>
-      </c>
-      <c r="B45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(B$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(C$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(D$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(E$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(F$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="G45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(G$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(H$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="I45" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("GTCL tài sản cố định vô hình",balance_sheet!$A:$A,0),MATCH(I$23,balance_sheet!$B$1:$I$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="17" t="inlineStr">
+      <c r="J54" s="20" t="n">
+        <v>-6600000000000</v>
+      </c>
+      <c r="K54" s="20" t="n">
+        <v>159400000000</v>
+      </c>
+      <c r="L54" s="20" t="n">
+        <v>1275200000000</v>
+      </c>
+      <c r="M54" s="20" t="n">
+        <v>1594000000000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="25" t="inlineStr">
+        <is>
+          <t>Lưu chuyển tiền tệ</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="18" t="inlineStr">
         <is>
           <t>Khấu hao TSCĐ và BĐSĐT</t>
         </is>
       </c>
-      <c r="B46" s="18">
+      <c r="B56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(B$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C46" s="18">
+      <c r="C56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(C$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D46" s="18">
+      <c r="D56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(D$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E46" s="18">
+      <c r="E56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(E$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F46" s="18">
+      <c r="F56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(F$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G46" s="18">
+      <c r="G56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(G$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H46" s="18">
+      <c r="H56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(H$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I46" s="18">
+      <c r="I56" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Khấu hao TSCĐ và BĐSĐT",cash_flow!$A:$A,0),MATCH(I$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="17" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="18" t="inlineStr">
         <is>
           <t>Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác</t>
         </is>
       </c>
-      <c r="B47" s="18">
+      <c r="B57" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(B$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C47" s="18">
+      <c r="C57" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(C$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D47" s="18">
+      <c r="D57" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(D$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E47" s="18">
+      <c r="E57" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(E$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F47" s="18">
+      <c r="F57" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(F$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G47" s="18">
+      <c r="G57" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(G$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H47" s="18">
+      <c r="H57" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(H$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I47" s="18">
+      <c r="I57" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác",cash_flow!$A:$A,0),MATCH(I$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="17" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="18" t="inlineStr">
         <is>
           <t>Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh</t>
         </is>
       </c>
-      <c r="B48" s="18">
+      <c r="B58" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(B$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C48" s="18">
+      <c r="C58" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(C$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D48" s="18">
+      <c r="D58" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(D$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E48" s="18">
+      <c r="E58" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(E$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F48" s="18">
+      <c r="F58" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(F$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G48" s="18">
+      <c r="G58" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(G$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H48" s="18">
+      <c r="H58" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(H$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I48" s="18">
+      <c r="I58" s="19">
         <f>IFERROR(INDEX(cash_flow!$B:$I,MATCH("Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh",cash_flow!$A:$A,0),MATCH(I$23,cash_flow!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" s="19" t="inlineStr">
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62">
+      <c r="A62" s="29" t="inlineStr">
         <is>
           <t>CHỈ SỐ THÊM</t>
         </is>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B62" s="16" t="n">
         <v>2018</v>
       </c>
-      <c r="C52" s="6" t="n">
+      <c r="C62" s="16" t="n">
         <v>2019</v>
       </c>
-      <c r="D52" s="6" t="n">
+      <c r="D62" s="16" t="n">
         <v>2020</v>
       </c>
-      <c r="E52" s="6" t="n">
+      <c r="E62" s="16" t="n">
         <v>2021</v>
       </c>
-      <c r="F52" s="6" t="n">
+      <c r="F62" s="16" t="n">
         <v>2022</v>
       </c>
-      <c r="G52" s="6" t="n">
+      <c r="G62" s="16" t="n">
         <v>2023</v>
       </c>
-      <c r="H52" s="6" t="n">
+      <c r="H62" s="16" t="n">
         <v>2024</v>
       </c>
-      <c r="I52" s="6" t="n">
+      <c r="I62" s="16" t="n">
         <v>2025</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="19" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="29" t="inlineStr">
         <is>
           <t>Khả năng sinh lời &amp; hiệu quả sử dụng vốn</t>
         </is>
       </c>
-      <c r="B53" s="20" t="n"/>
-      <c r="C53" s="20" t="n"/>
-      <c r="D53" s="20" t="n"/>
-      <c r="E53" s="20" t="n"/>
-      <c r="F53" s="20" t="n"/>
-      <c r="G53" s="20" t="n"/>
-      <c r="H53" s="20" t="n"/>
-      <c r="I53" s="20" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="20" t="inlineStr">
+      <c r="B63" s="30" t="n"/>
+      <c r="C63" s="30" t="n"/>
+      <c r="D63" s="30" t="n"/>
+      <c r="E63" s="30" t="n"/>
+      <c r="F63" s="30" t="n"/>
+      <c r="G63" s="30" t="n"/>
+      <c r="H63" s="30" t="n"/>
+      <c r="I63" s="30" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="30" t="inlineStr">
         <is>
           <t>ROCE</t>
         </is>
       </c>
-      <c r="B54" s="21">
-        <f>IFERROR(B$56/(B$25-B$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C54" s="21">
-        <f>IFERROR(C$56/(C$25-C$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D54" s="21">
-        <f>IFERROR(D$56/(D$25-D$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E54" s="21">
-        <f>IFERROR(E$56/(E$25-E$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F54" s="21">
-        <f>IFERROR(F$56/(F$25-F$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G54" s="21">
-        <f>IFERROR(G$56/(G$25-G$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H54" s="21">
-        <f>IFERROR(H$56/(H$25-H$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I54" s="21">
-        <f>IFERROR(I$56/(I$25-I$27),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="20" t="inlineStr">
+      <c r="B64" s="31">
+        <f>IFERROR(B$66/(B$31-B$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C64" s="31">
+        <f>IFERROR(C$66/(C$31-C$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D64" s="31">
+        <f>IFERROR(D$66/(D$31-D$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E64" s="31">
+        <f>IFERROR(E$66/(E$31-E$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F64" s="31">
+        <f>IFERROR(F$66/(F$31-F$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G64" s="31">
+        <f>IFERROR(G$66/(G$31-G$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H64" s="31">
+        <f>IFERROR(H$66/(H$31-H$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I64" s="31">
+        <f>IFERROR(I$66/(I$31-I$35),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="30" t="inlineStr">
         <is>
           <t>CROIC</t>
         </is>
       </c>
-      <c r="B55" s="21">
-        <f>IFERROR(B$60/(B$25-B$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C55" s="21">
-        <f>IFERROR(C$60/(C$25-C$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D55" s="21">
-        <f>IFERROR(D$60/(D$25-D$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E55" s="21">
-        <f>IFERROR(E$60/(E$25-E$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F55" s="21">
-        <f>IFERROR(F$60/(F$25-F$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G55" s="21">
-        <f>IFERROR(G$60/(G$25-G$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H55" s="21">
-        <f>IFERROR(H$60/(H$25-H$27),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I55" s="21">
-        <f>IFERROR(I$60/(I$25-I$27),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="20" t="inlineStr">
+      <c r="B65" s="31">
+        <f>IFERROR(B$70/(B$31-B$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C65" s="31">
+        <f>IFERROR(C$70/(C$31-C$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D65" s="31">
+        <f>IFERROR(D$70/(D$31-D$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E65" s="31">
+        <f>IFERROR(E$70/(E$31-E$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F65" s="31">
+        <f>IFERROR(F$70/(F$31-F$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G65" s="31">
+        <f>IFERROR(G$70/(G$31-G$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H65" s="31">
+        <f>IFERROR(H$70/(H$31-H$35),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I65" s="31">
+        <f>IFERROR(I$70/(I$31-I$35),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="30" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B56" s="22">
-        <f>IFERROR(B$36+ABS(B$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C56" s="22">
-        <f>IFERROR(C$36+ABS(C$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D56" s="22">
-        <f>IFERROR(D$36+ABS(D$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E56" s="22">
-        <f>IFERROR(E$36+ABS(E$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F56" s="22">
-        <f>IFERROR(F$36+ABS(F$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G56" s="22">
-        <f>IFERROR(G$36+ABS(G$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H56" s="22">
-        <f>IFERROR(H$36+ABS(H$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I56" s="22">
-        <f>IFERROR(I$36+ABS(I$37),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="20" t="inlineStr">
+      <c r="B66" s="32">
+        <f>IFERROR(B$49+ABS(B$50),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C66" s="32">
+        <f>IFERROR(C$49+ABS(C$50),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D66" s="32">
+        <f>IFERROR(D$49+ABS(D$50),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E66" s="32">
+        <f>IFERROR(E$49+ABS(E$50),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F66" s="32">
+        <f>IFERROR(F$49+ABS(F$50),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G66" s="32">
+        <f>IFERROR(G$49+ABS(G$50),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H66" s="32">
+        <f>IFERROR(H$49+ABS(H$50),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I66" s="32">
+        <f>IFERROR(I$49+ABS(I$50),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="30" t="inlineStr">
         <is>
           <t>EBIT/DT</t>
         </is>
       </c>
-      <c r="B57" s="21">
-        <f>IFERROR(B$56/B$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C57" s="21">
-        <f>IFERROR(C$56/C$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D57" s="21">
-        <f>IFERROR(D$56/D$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E57" s="21">
-        <f>IFERROR(E$56/E$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F57" s="21">
-        <f>IFERROR(F$56/F$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G57" s="21">
-        <f>IFERROR(G$56/G$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H57" s="21">
-        <f>IFERROR(H$56/H$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I57" s="21">
-        <f>IFERROR(I$56/I$31,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="20" t="inlineStr">
+      <c r="B67" s="31">
+        <f>IFERROR(B$66/B$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C67" s="31">
+        <f>IFERROR(C$66/C$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D67" s="31">
+        <f>IFERROR(D$66/D$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E67" s="31">
+        <f>IFERROR(E$66/E$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F67" s="31">
+        <f>IFERROR(F$66/F$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G67" s="31">
+        <f>IFERROR(G$66/G$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H67" s="31">
+        <f>IFERROR(H$66/H$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I67" s="31">
+        <f>IFERROR(I$66/I$44,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
         <is>
           <t>DT/TS</t>
         </is>
       </c>
-      <c r="B58" s="21">
-        <f>IFERROR(B$31/B$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C58" s="21">
-        <f>IFERROR(C$31/C$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D58" s="21">
-        <f>IFERROR(D$31/D$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E58" s="21">
-        <f>IFERROR(E$31/E$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F58" s="21">
-        <f>IFERROR(F$31/F$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G58" s="21">
-        <f>IFERROR(G$31/G$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H58" s="21">
-        <f>IFERROR(H$31/H$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I58" s="21">
-        <f>IFERROR(I$31/I$25,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="19" t="inlineStr">
+      <c r="B68" s="31">
+        <f>IFERROR(B$44/B$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C68" s="31">
+        <f>IFERROR(C$44/C$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D68" s="31">
+        <f>IFERROR(D$44/D$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E68" s="31">
+        <f>IFERROR(E$44/E$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F68" s="31">
+        <f>IFERROR(F$44/F$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G68" s="31">
+        <f>IFERROR(G$44/G$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H68" s="31">
+        <f>IFERROR(H$44/H$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I68" s="31">
+        <f>IFERROR(I$44/I$31,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>Dòng tiền &amp; tái đầu tư</t>
         </is>
       </c>
-      <c r="B59" s="20" t="n"/>
-      <c r="C59" s="20" t="n"/>
-      <c r="D59" s="20" t="n"/>
-      <c r="E59" s="20" t="n"/>
-      <c r="F59" s="20" t="n"/>
-      <c r="G59" s="20" t="n"/>
-      <c r="H59" s="20" t="n"/>
-      <c r="I59" s="20" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="20" t="inlineStr">
+      <c r="B69" s="30" t="n"/>
+      <c r="C69" s="30" t="n"/>
+      <c r="D69" s="30" t="n"/>
+      <c r="E69" s="30" t="n"/>
+      <c r="F69" s="30" t="n"/>
+      <c r="G69" s="30" t="n"/>
+      <c r="H69" s="30" t="n"/>
+      <c r="I69" s="30" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>FCF</t>
         </is>
       </c>
-      <c r="B60" s="22">
-        <f>IFERROR(B$48-ABS(B$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C60" s="22">
-        <f>IFERROR(C$48-ABS(C$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D60" s="22">
-        <f>IFERROR(D$48-ABS(D$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E60" s="22">
-        <f>IFERROR(E$48-ABS(E$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F60" s="22">
-        <f>IFERROR(F$48-ABS(F$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G60" s="22">
-        <f>IFERROR(G$48-ABS(G$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H60" s="22">
-        <f>IFERROR(H$48-ABS(H$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I60" s="22">
-        <f>IFERROR(I$48-ABS(I$47),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="20" t="inlineStr">
+      <c r="B70" s="32">
+        <f>IFERROR(B$58-ABS(B$57),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C70" s="32">
+        <f>IFERROR(C$58-ABS(C$57),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D70" s="32">
+        <f>IFERROR(D$58-ABS(D$57),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E70" s="32">
+        <f>IFERROR(E$58-ABS(E$57),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F70" s="32">
+        <f>IFERROR(F$58-ABS(F$57),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G70" s="32">
+        <f>IFERROR(G$58-ABS(G$57),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H70" s="32">
+        <f>IFERROR(H$58-ABS(H$57),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I70" s="32">
+        <f>IFERROR(I$58-ABS(I$57),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="30" t="inlineStr">
         <is>
           <t>FCF/DT</t>
         </is>
       </c>
-      <c r="B61" s="21">
-        <f>IFERROR(B$60/B$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C61" s="21">
-        <f>IFERROR(C$60/C$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D61" s="21">
-        <f>IFERROR(D$60/D$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E61" s="21">
-        <f>IFERROR(E$60/E$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F61" s="21">
-        <f>IFERROR(F$60/F$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G61" s="21">
-        <f>IFERROR(G$60/G$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H61" s="21">
-        <f>IFERROR(H$60/H$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I61" s="21">
-        <f>IFERROR(I$60/I$31,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="20" t="inlineStr">
+      <c r="B71" s="31">
+        <f>IFERROR(B$70/B$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C71" s="31">
+        <f>IFERROR(C$70/C$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D71" s="31">
+        <f>IFERROR(D$70/D$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E71" s="31">
+        <f>IFERROR(E$70/E$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F71" s="31">
+        <f>IFERROR(F$70/F$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G71" s="31">
+        <f>IFERROR(G$70/G$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H71" s="31">
+        <f>IFERROR(H$70/H$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I71" s="31">
+        <f>IFERROR(I$70/I$44,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="30" t="inlineStr">
         <is>
           <t>FCF/Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B62" s="21">
-        <f>IFERROR(B$60/B$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C62" s="21">
-        <f>IFERROR(C$60/C$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D62" s="21">
-        <f>IFERROR(D$60/D$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E62" s="21">
-        <f>IFERROR(E$60/E$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F62" s="21">
-        <f>IFERROR(F$60/F$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G62" s="21">
-        <f>IFERROR(G$60/G$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H62" s="21">
-        <f>IFERROR(H$60/H$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I62" s="21">
-        <f>IFERROR(I$60/I$27,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="20" t="inlineStr">
+      <c r="B72" s="31">
+        <f>IFERROR(B$70/B$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C72" s="31">
+        <f>IFERROR(C$70/C$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D72" s="31">
+        <f>IFERROR(D$70/D$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E72" s="31">
+        <f>IFERROR(E$70/E$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F72" s="31">
+        <f>IFERROR(F$70/F$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G72" s="31">
+        <f>IFERROR(G$70/G$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H72" s="31">
+        <f>IFERROR(H$70/H$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I72" s="31">
+        <f>IFERROR(I$70/I$35,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="30" t="inlineStr">
         <is>
           <t>Capex</t>
         </is>
       </c>
-      <c r="B63" s="22">
-        <f>IFERROR(ABS(B$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C63" s="22">
-        <f>IFERROR(ABS(C$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D63" s="22">
-        <f>IFERROR(ABS(D$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E63" s="22">
-        <f>IFERROR(ABS(E$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F63" s="22">
-        <f>IFERROR(ABS(F$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G63" s="22">
-        <f>IFERROR(ABS(G$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H63" s="22">
-        <f>IFERROR(ABS(H$47),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I63" s="22">
-        <f>IFERROR(ABS(I$47),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="20" t="inlineStr">
+      <c r="B73" s="32">
+        <f>IFERROR(ABS(B$57),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C73" s="32">
+        <f>IFERROR(ABS(C$57),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D73" s="32">
+        <f>IFERROR(ABS(D$57),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E73" s="32">
+        <f>IFERROR(ABS(E$57),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F73" s="32">
+        <f>IFERROR(ABS(F$57),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G73" s="32">
+        <f>IFERROR(ABS(G$57),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H73" s="32">
+        <f>IFERROR(ABS(H$57),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I73" s="32">
+        <f>IFERROR(ABS(I$57),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="30" t="inlineStr">
         <is>
           <t>Capex/TS</t>
         </is>
       </c>
-      <c r="B64" s="21">
-        <f>IFERROR(B$63/B$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C64" s="21">
-        <f>IFERROR(C$63/C$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D64" s="21">
-        <f>IFERROR(D$63/D$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E64" s="21">
-        <f>IFERROR(E$63/E$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F64" s="21">
-        <f>IFERROR(F$63/F$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G64" s="21">
-        <f>IFERROR(G$63/G$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H64" s="21">
-        <f>IFERROR(H$63/H$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I64" s="21">
-        <f>IFERROR(I$63/I$25,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="20" t="inlineStr">
+      <c r="B74" s="31">
+        <f>IFERROR(B$73/B$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C74" s="31">
+        <f>IFERROR(C$73/C$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D74" s="31">
+        <f>IFERROR(D$73/D$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E74" s="31">
+        <f>IFERROR(E$73/E$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F74" s="31">
+        <f>IFERROR(F$73/F$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G74" s="31">
+        <f>IFERROR(G$73/G$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H74" s="31">
+        <f>IFERROR(H$73/H$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I74" s="31">
+        <f>IFERROR(I$73/I$31,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
         <is>
           <t>Capex/LNST</t>
         </is>
       </c>
-      <c r="B65" s="21">
-        <f>IFERROR(B$63/ABS(B$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C65" s="21">
-        <f>IFERROR(C$63/ABS(C$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D65" s="21">
-        <f>IFERROR(D$63/ABS(D$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E65" s="21">
-        <f>IFERROR(E$63/ABS(E$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F65" s="21">
-        <f>IFERROR(F$63/ABS(F$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G65" s="21">
-        <f>IFERROR(G$63/ABS(G$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H65" s="21">
-        <f>IFERROR(H$63/ABS(H$38),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I65" s="21">
-        <f>IFERROR(I$63/ABS(I$38),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="20" t="inlineStr">
+      <c r="B75" s="31">
+        <f>IFERROR(B$73/ABS(B$52),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C75" s="31">
+        <f>IFERROR(C$73/ABS(C$52),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D75" s="31">
+        <f>IFERROR(D$73/ABS(D$52),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E75" s="31">
+        <f>IFERROR(E$73/ABS(E$52),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F75" s="31">
+        <f>IFERROR(F$73/ABS(F$52),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G75" s="31">
+        <f>IFERROR(G$73/ABS(G$52),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H75" s="31">
+        <f>IFERROR(H$73/ABS(H$52),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I75" s="31">
+        <f>IFERROR(I$73/ABS(I$52),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
         <is>
           <t>Chi phí khấu hao/Lợi nhuận gộp</t>
         </is>
       </c>
-      <c r="B66" s="21">
-        <f>IFERROR(ABS(B$46)/B$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C66" s="21">
-        <f>IFERROR(ABS(C$46)/C$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D66" s="21">
-        <f>IFERROR(ABS(D$46)/D$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E66" s="21">
-        <f>IFERROR(ABS(E$46)/E$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F66" s="21">
-        <f>IFERROR(ABS(F$46)/F$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G66" s="21">
-        <f>IFERROR(ABS(G$46)/G$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H66" s="21">
-        <f>IFERROR(ABS(H$46)/H$33,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I66" s="21">
-        <f>IFERROR(ABS(I$46)/I$33,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="20" t="inlineStr">
+      <c r="B76" s="31">
+        <f>IFERROR(ABS(B$56)/B$46,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C76" s="31">
+        <f>IFERROR(ABS(C$56)/C$46,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D76" s="31">
+        <f>IFERROR(ABS(D$56)/D$46,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E76" s="31">
+        <f>IFERROR(ABS(E$56)/E$46,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F76" s="31">
+        <f>IFERROR(ABS(F$56)/F$46,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G76" s="31">
+        <f>IFERROR(ABS(G$56)/G$46,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H76" s="31">
+        <f>IFERROR(ABS(H$56)/H$46,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I76" s="31">
+        <f>IFERROR(ABS(I$56)/I$46,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
         <is>
           <t>EBIT/Chi phí lãi vay</t>
         </is>
       </c>
-      <c r="B67" s="23">
-        <f>IFERROR(B$56/ABS(B$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="C67" s="23">
-        <f>IFERROR(C$56/ABS(C$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D67" s="23">
-        <f>IFERROR(D$56/ABS(D$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E67" s="23">
-        <f>IFERROR(E$56/ABS(E$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="F67" s="23">
-        <f>IFERROR(F$56/ABS(F$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="G67" s="23">
-        <f>IFERROR(G$56/ABS(G$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="H67" s="23">
-        <f>IFERROR(H$56/ABS(H$37),"n/a")</f>
-        <v/>
-      </c>
-      <c r="I67" s="23">
-        <f>IFERROR(I$56/ABS(I$37),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="19" t="inlineStr">
+      <c r="B77" s="33">
+        <f>IFERROR(B$66/ABS(B$50),"n/a")</f>
+        <v/>
+      </c>
+      <c r="C77" s="33">
+        <f>IFERROR(C$66/ABS(C$50),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D77" s="33">
+        <f>IFERROR(D$66/ABS(D$50),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E77" s="33">
+        <f>IFERROR(E$66/ABS(E$50),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F77" s="33">
+        <f>IFERROR(F$66/ABS(F$50),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G77" s="33">
+        <f>IFERROR(G$66/ABS(G$50),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H77" s="33">
+        <f>IFERROR(H$66/ABS(H$50),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I77" s="33">
+        <f>IFERROR(I$66/ABS(I$50),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="29" t="inlineStr">
         <is>
           <t>Vốn lưu động &amp; hiệu quả hoạt động</t>
         </is>
       </c>
-      <c r="B68" s="20" t="n"/>
-      <c r="C68" s="20" t="n"/>
-      <c r="D68" s="20" t="n"/>
-      <c r="E68" s="20" t="n"/>
-      <c r="F68" s="20" t="n"/>
-      <c r="G68" s="20" t="n"/>
-      <c r="H68" s="20" t="n"/>
-      <c r="I68" s="20" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="20" t="inlineStr">
+      <c r="B78" s="30" t="n"/>
+      <c r="C78" s="30" t="n"/>
+      <c r="D78" s="30" t="n"/>
+      <c r="E78" s="30" t="n"/>
+      <c r="F78" s="30" t="n"/>
+      <c r="G78" s="30" t="n"/>
+      <c r="H78" s="30" t="n"/>
+      <c r="I78" s="30" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="30" t="inlineStr">
         <is>
           <t>Vòng quay tiền mặt</t>
         </is>
       </c>
-      <c r="B69" s="24">
+      <c r="B79" s="34">
         <f>IFERROR(B$17+B$18-B$16,"n/a")</f>
         <v/>
       </c>
-      <c r="C69" s="24">
+      <c r="C79" s="34">
         <f>IFERROR(C$17+C$18-C$16,"n/a")</f>
         <v/>
       </c>
-      <c r="D69" s="24">
+      <c r="D79" s="34">
         <f>IFERROR(D$17+D$18-D$16,"n/a")</f>
         <v/>
       </c>
-      <c r="E69" s="24">
+      <c r="E79" s="34">
         <f>IFERROR(E$17+E$18-E$16,"n/a")</f>
         <v/>
       </c>
-      <c r="F69" s="24">
+      <c r="F79" s="34">
         <f>IFERROR(F$17+F$18-F$16,"n/a")</f>
         <v/>
       </c>
-      <c r="G69" s="24">
+      <c r="G79" s="34">
         <f>IFERROR(G$17+G$18-G$16,"n/a")</f>
         <v/>
       </c>
-      <c r="H69" s="24">
+      <c r="H79" s="34">
         <f>IFERROR(H$17+H$18-H$16,"n/a")</f>
         <v/>
       </c>
-      <c r="I69" s="24">
+      <c r="I79" s="34">
         <f>IFERROR(I$17+I$18-I$16,"n/a")</f>
         <v/>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="20" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="30" t="inlineStr">
         <is>
           <t>HTK/DT</t>
         </is>
       </c>
-      <c r="B70" s="21">
-        <f>IFERROR(B$42/B$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C70" s="21">
-        <f>IFERROR(C$42/C$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D70" s="21">
-        <f>IFERROR(D$42/D$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E70" s="21">
-        <f>IFERROR(E$42/E$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F70" s="21">
-        <f>IFERROR(F$42/F$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G70" s="21">
-        <f>IFERROR(G$42/G$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H70" s="21">
-        <f>IFERROR(H$42/H$31,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I70" s="21">
-        <f>IFERROR(I$42/I$31,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="20" t="inlineStr">
+      <c r="B80" s="31">
+        <f>IFERROR(B$28/B$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C80" s="31">
+        <f>IFERROR(C$28/C$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D80" s="31">
+        <f>IFERROR(D$28/D$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E80" s="31">
+        <f>IFERROR(E$28/E$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F80" s="31">
+        <f>IFERROR(F$28/F$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G80" s="31">
+        <f>IFERROR(G$28/G$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H80" s="31">
+        <f>IFERROR(H$28/H$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I80" s="31">
+        <f>IFERROR(I$28/I$44,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="30" t="inlineStr">
         <is>
           <t>HTK/TS</t>
         </is>
       </c>
-      <c r="B71" s="21">
-        <f>IFERROR(B$42/B$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C71" s="21">
-        <f>IFERROR(C$42/C$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D71" s="21">
-        <f>IFERROR(D$42/D$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E71" s="21">
-        <f>IFERROR(E$42/E$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F71" s="21">
-        <f>IFERROR(F$42/F$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G71" s="21">
-        <f>IFERROR(G$42/G$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H71" s="21">
-        <f>IFERROR(H$42/H$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I71" s="21">
-        <f>IFERROR(I$42/I$25,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="20" t="inlineStr">
+      <c r="B81" s="31">
+        <f>IFERROR(B$28/B$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C81" s="31">
+        <f>IFERROR(C$28/C$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D81" s="31">
+        <f>IFERROR(D$28/D$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E81" s="31">
+        <f>IFERROR(E$28/E$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F81" s="31">
+        <f>IFERROR(F$28/F$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G81" s="31">
+        <f>IFERROR(G$28/G$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H81" s="31">
+        <f>IFERROR(H$28/H$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I81" s="31">
+        <f>IFERROR(I$28/I$31,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="30" t="inlineStr">
         <is>
           <t>DT/TS</t>
         </is>
       </c>
-      <c r="B72" s="21">
-        <f>IFERROR(B$31/B$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C72" s="21">
-        <f>IFERROR(C$31/C$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D72" s="21">
-        <f>IFERROR(D$31/D$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E72" s="21">
-        <f>IFERROR(E$31/E$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F72" s="21">
-        <f>IFERROR(F$31/F$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G72" s="21">
-        <f>IFERROR(G$31/G$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H72" s="21">
-        <f>IFERROR(H$31/H$25,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I72" s="21">
-        <f>IFERROR(I$31/I$25,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="19" t="inlineStr">
+      <c r="B82" s="31">
+        <f>IFERROR(B$44/B$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C82" s="31">
+        <f>IFERROR(C$44/C$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D82" s="31">
+        <f>IFERROR(D$44/D$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E82" s="31">
+        <f>IFERROR(E$44/E$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F82" s="31">
+        <f>IFERROR(F$44/F$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G82" s="31">
+        <f>IFERROR(G$44/G$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H82" s="31">
+        <f>IFERROR(H$44/H$31,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I82" s="31">
+        <f>IFERROR(I$44/I$31,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="29" t="inlineStr">
         <is>
           <t>Khả năng thanh toán</t>
         </is>
       </c>
-      <c r="B73" s="20" t="n"/>
-      <c r="C73" s="20" t="n"/>
-      <c r="D73" s="20" t="n"/>
-      <c r="E73" s="20" t="n"/>
-      <c r="F73" s="20" t="n"/>
-      <c r="G73" s="20" t="n"/>
-      <c r="H73" s="20" t="n"/>
-      <c r="I73" s="20" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="20" t="inlineStr">
+      <c r="B83" s="30" t="n"/>
+      <c r="C83" s="30" t="n"/>
+      <c r="D83" s="30" t="n"/>
+      <c r="E83" s="30" t="n"/>
+      <c r="F83" s="30" t="n"/>
+      <c r="G83" s="30" t="n"/>
+      <c r="H83" s="30" t="n"/>
+      <c r="I83" s="30" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="30" t="inlineStr">
         <is>
           <t>(TS ngắn hạn − HTK)/Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B74" s="23">
-        <f>IFERROR((B$44-B$42)/B$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C74" s="23">
-        <f>IFERROR((C$44-C$42)/C$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D74" s="23">
-        <f>IFERROR((D$44-D$42)/D$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E74" s="23">
-        <f>IFERROR((E$44-E$42)/E$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F74" s="23">
-        <f>IFERROR((F$44-F$42)/F$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G74" s="23">
-        <f>IFERROR((G$44-G$42)/G$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H74" s="23">
-        <f>IFERROR((H$44-H$42)/H$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I74" s="23">
-        <f>IFERROR((I$44-I$42)/I$27,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="20" t="inlineStr">
+      <c r="B84" s="33">
+        <f>IFERROR((B$29-B$28)/B$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C84" s="33">
+        <f>IFERROR((C$29-C$28)/C$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D84" s="33">
+        <f>IFERROR((D$29-D$28)/D$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E84" s="33">
+        <f>IFERROR((E$29-E$28)/E$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F84" s="33">
+        <f>IFERROR((F$29-F$28)/F$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G84" s="33">
+        <f>IFERROR((G$29-G$28)/G$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H84" s="33">
+        <f>IFERROR((H$29-H$28)/H$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I84" s="33">
+        <f>IFERROR((I$29-I$28)/I$35,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="30" t="inlineStr">
         <is>
           <t>TS ngắn hạn/Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B75" s="23">
-        <f>IFERROR(B$44/B$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C75" s="23">
-        <f>IFERROR(C$44/C$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D75" s="23">
-        <f>IFERROR(D$44/D$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E75" s="23">
-        <f>IFERROR(E$44/E$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F75" s="23">
-        <f>IFERROR(F$44/F$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G75" s="23">
-        <f>IFERROR(G$44/G$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H75" s="23">
-        <f>IFERROR(H$44/H$27,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I75" s="23">
-        <f>IFERROR(I$44/I$27,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="19" t="inlineStr">
+      <c r="B85" s="33">
+        <f>IFERROR(B$29/B$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C85" s="33">
+        <f>IFERROR(C$29/C$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D85" s="33">
+        <f>IFERROR(D$29/D$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E85" s="33">
+        <f>IFERROR(E$29/E$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F85" s="33">
+        <f>IFERROR(F$29/F$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G85" s="33">
+        <f>IFERROR(G$29/G$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H85" s="33">
+        <f>IFERROR(H$29/H$35,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I85" s="33">
+        <f>IFERROR(I$29/I$35,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="29" t="inlineStr">
         <is>
           <t>Tài sản &amp; cơ cấu tài sản</t>
         </is>
       </c>
-      <c r="B76" s="20" t="n"/>
-      <c r="C76" s="20" t="n"/>
-      <c r="D76" s="20" t="n"/>
-      <c r="E76" s="20" t="n"/>
-      <c r="F76" s="20" t="n"/>
-      <c r="G76" s="20" t="n"/>
-      <c r="H76" s="20" t="n"/>
-      <c r="I76" s="20" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="20" t="inlineStr">
+      <c r="B86" s="30" t="n"/>
+      <c r="C86" s="30" t="n"/>
+      <c r="D86" s="30" t="n"/>
+      <c r="E86" s="30" t="n"/>
+      <c r="F86" s="30" t="n"/>
+      <c r="G86" s="30" t="n"/>
+      <c r="H86" s="30" t="n"/>
+      <c r="I86" s="30" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="30" t="inlineStr">
         <is>
           <t>TSCĐ vô hình</t>
         </is>
       </c>
-      <c r="B77" s="22">
-        <f>IFERROR(B$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C77" s="22">
-        <f>IFERROR(C$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D77" s="22">
-        <f>IFERROR(D$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E77" s="22">
-        <f>IFERROR(E$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F77" s="22">
-        <f>IFERROR(F$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G77" s="22">
-        <f>IFERROR(G$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H77" s="22">
-        <f>IFERROR(H$45,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I77" s="22">
-        <f>IFERROR(I$45,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="20" t="inlineStr">
+      <c r="B87" s="32">
+        <f>IFERROR(B$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C87" s="32">
+        <f>IFERROR(C$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D87" s="32">
+        <f>IFERROR(D$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E87" s="32">
+        <f>IFERROR(E$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F87" s="32">
+        <f>IFERROR(F$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G87" s="32">
+        <f>IFERROR(G$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H87" s="32">
+        <f>IFERROR(H$30,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I87" s="32">
+        <f>IFERROR(I$30,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="30" t="inlineStr">
         <is>
           <t>Tài sản vô hình/Giá trị sổ sách</t>
         </is>
       </c>
-      <c r="B78" s="21">
-        <f>IFERROR(B$45/B$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C78" s="21">
-        <f>IFERROR(C$45/C$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D78" s="21">
-        <f>IFERROR(D$45/D$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E78" s="21">
-        <f>IFERROR(E$45/E$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="F78" s="21">
-        <f>IFERROR(F$45/F$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="G78" s="21">
-        <f>IFERROR(G$45/G$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="H78" s="21">
-        <f>IFERROR(H$45/H$24,"n/a")</f>
-        <v/>
-      </c>
-      <c r="I78" s="21">
-        <f>IFERROR(I$45/I$24,"n/a")</f>
+      <c r="B88" s="31">
+        <f>IFERROR(B$30/B$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C88" s="31">
+        <f>IFERROR(C$30/C$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D88" s="31">
+        <f>IFERROR(D$30/D$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E88" s="31">
+        <f>IFERROR(E$30/E$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F88" s="31">
+        <f>IFERROR(F$30/F$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G88" s="31">
+        <f>IFERROR(G$30/G$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H88" s="31">
+        <f>IFERROR(H$30/H$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I88" s="31">
+        <f>IFERROR(I$30/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:I2">
-    <cfRule type="cellIs" priority="14" operator="greaterThanOrEqual" dxfId="0">
-      <formula>0.15</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="15" operator="lessThan" dxfId="1">
-      <formula>0.15</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B4:I5">
-    <cfRule type="cellIs" priority="11" operator="lessThan" dxfId="1">
-      <formula>0.1</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="12" operator="greaterThanOrEqual" dxfId="0">
-      <formula>0.15</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="13" operator="between" dxfId="2">
-      <formula>0.1</formula>
-      <formula>0.15</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6:I6">
+  <conditionalFormatting sqref="B6:M6">
     <cfRule type="cellIs" priority="8" operator="greaterThanOrEqual" dxfId="0">
       <formula>0.3</formula>
     </cfRule>
@@ -9389,11 +9910,6 @@
     <cfRule type="cellIs" priority="10" operator="between" dxfId="2">
       <formula>0.1</formula>
       <formula>0.3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B7:I7">
-    <cfRule type="cellIs" priority="7" operator="greaterThanOrEqual" dxfId="0">
-      <formula>0.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:I8 B11:I11">
@@ -9419,6 +9935,1289 @@
       <formula>0.3</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B2:M2">
+    <cfRule type="cellIs" priority="14" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0.15</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="15" operator="lessThan" dxfId="1">
+      <formula>0.15</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4:M5">
+    <cfRule type="cellIs" priority="11" operator="lessThan" dxfId="1">
+      <formula>0.1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0.15</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="13" operator="between" dxfId="2">
+      <formula>0.1</formula>
+      <formula>0.15</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:M7">
+    <cfRule type="cellIs" priority="7" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="15.625" customWidth="1" min="14" max="14"/>
+    <col width="15.625" customWidth="1" min="15" max="15"/>
+    <col width="15.625" customWidth="1" min="18" max="18"/>
+    <col width="8.125" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="23" max="23"/>
+    <col width="9" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="n"/>
+      <c r="B1" s="35" t="inlineStr">
+        <is>
+          <t>Q4/2025</t>
+        </is>
+      </c>
+      <c r="C1" s="35" t="inlineStr">
+        <is>
+          <t>Q1/2026</t>
+        </is>
+      </c>
+      <c r="D1" s="35" t="inlineStr">
+        <is>
+          <t>Q2/2026</t>
+        </is>
+      </c>
+      <c r="E1" s="35" t="inlineStr">
+        <is>
+          <t>Q3/2026</t>
+        </is>
+      </c>
+      <c r="F1" s="35" t="inlineStr">
+        <is>
+          <t>Q4/2026</t>
+        </is>
+      </c>
+      <c r="G1" s="35" t="inlineStr">
+        <is>
+          <t>Q1/2027</t>
+        </is>
+      </c>
+      <c r="H1" s="35" t="inlineStr">
+        <is>
+          <t>Q2/2027</t>
+        </is>
+      </c>
+      <c r="I1" s="35" t="inlineStr">
+        <is>
+          <t>Q3/2027</t>
+        </is>
+      </c>
+      <c r="J1" s="35" t="inlineStr">
+        <is>
+          <t>Q4/2027</t>
+        </is>
+      </c>
+      <c r="K1" s="35" t="inlineStr">
+        <is>
+          <t>Q1/2028</t>
+        </is>
+      </c>
+      <c r="L1" s="35" t="inlineStr">
+        <is>
+          <t>Q2/2028</t>
+        </is>
+      </c>
+      <c r="M1" s="35" t="inlineStr">
+        <is>
+          <t>Q3/2028</t>
+        </is>
+      </c>
+      <c r="N1" s="35" t="inlineStr">
+        <is>
+          <t>Q4/2028</t>
+        </is>
+      </c>
+      <c r="O1" s="35" t="inlineStr">
+        <is>
+          <t>Q1/2029</t>
+        </is>
+      </c>
+      <c r="P1" s="35" t="inlineStr">
+        <is>
+          <t>Q2/2029</t>
+        </is>
+      </c>
+      <c r="Q1" s="35" t="inlineStr">
+        <is>
+          <t>Q3/2029</t>
+        </is>
+      </c>
+      <c r="R1" s="35" t="inlineStr">
+        <is>
+          <t>Q4/2029</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="35" t="inlineStr">
+        <is>
+          <t>Số CP</t>
+        </is>
+      </c>
+      <c r="B2" s="36" t="n">
+        <v>511721959</v>
+      </c>
+      <c r="C2" s="36" t="n">
+        <v>511721959</v>
+      </c>
+      <c r="D2" s="36" t="n">
+        <v>511721959</v>
+      </c>
+      <c r="E2" s="36" t="n">
+        <v>511721959</v>
+      </c>
+      <c r="F2" s="36" t="n">
+        <v>511721959</v>
+      </c>
+      <c r="G2" s="37" t="n">
+        <v>1050000000</v>
+      </c>
+      <c r="H2" s="37" t="n">
+        <v>1050000000</v>
+      </c>
+      <c r="I2" s="37" t="n">
+        <v>1050000000</v>
+      </c>
+      <c r="J2" s="37" t="n">
+        <v>1050000000</v>
+      </c>
+      <c r="K2" s="37" t="n">
+        <v>1050000000</v>
+      </c>
+      <c r="L2" s="37" t="n">
+        <v>1050000000</v>
+      </c>
+      <c r="M2" s="37" t="n">
+        <v>1050000000</v>
+      </c>
+      <c r="N2" s="37" t="n">
+        <v>1050000000</v>
+      </c>
+      <c r="O2" s="37" t="n">
+        <v>1050000000</v>
+      </c>
+      <c r="P2" s="37" t="n">
+        <v>1050000000</v>
+      </c>
+      <c r="Q2" s="37" t="n">
+        <v>1050000000</v>
+      </c>
+      <c r="R2" s="37" t="n">
+        <v>1050000000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="35" t="inlineStr">
+        <is>
+          <t>Thị giá</t>
+        </is>
+      </c>
+      <c r="B3" s="36" t="n">
+        <v>17450</v>
+      </c>
+      <c r="C3" s="36" t="n">
+        <v>17450</v>
+      </c>
+      <c r="D3" s="36" t="n">
+        <v>17450</v>
+      </c>
+      <c r="E3" s="36" t="n">
+        <v>17450</v>
+      </c>
+      <c r="F3" s="36" t="n">
+        <v>17450</v>
+      </c>
+      <c r="G3" s="36" t="n">
+        <v>17450</v>
+      </c>
+      <c r="H3" s="36" t="n">
+        <v>17450</v>
+      </c>
+      <c r="I3" s="36" t="n">
+        <v>17450</v>
+      </c>
+      <c r="J3" s="36" t="n">
+        <v>17450</v>
+      </c>
+      <c r="K3" s="36" t="n">
+        <v>17450</v>
+      </c>
+      <c r="L3" s="36" t="n">
+        <v>17450</v>
+      </c>
+      <c r="M3" s="36" t="n">
+        <v>17450</v>
+      </c>
+      <c r="N3" s="36" t="n">
+        <v>17450</v>
+      </c>
+      <c r="O3" s="36" t="n">
+        <v>17450</v>
+      </c>
+      <c r="P3" s="36" t="n">
+        <v>17450</v>
+      </c>
+      <c r="Q3" s="36" t="n">
+        <v>17450</v>
+      </c>
+      <c r="R3" s="36" t="n">
+        <v>17450</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="35" t="inlineStr">
+        <is>
+          <t>Vốn hoá</t>
+        </is>
+      </c>
+      <c r="B4" s="36">
+        <f>B2*B3</f>
+        <v/>
+      </c>
+      <c r="C4" s="36">
+        <f>C2*C3</f>
+        <v/>
+      </c>
+      <c r="D4" s="36">
+        <f>D2*D3</f>
+        <v/>
+      </c>
+      <c r="E4" s="36">
+        <f>E2*E3</f>
+        <v/>
+      </c>
+      <c r="F4" s="36">
+        <f>F2*F3</f>
+        <v/>
+      </c>
+      <c r="G4" s="36">
+        <f>G2*G3</f>
+        <v/>
+      </c>
+      <c r="H4" s="36">
+        <f>H2*H3</f>
+        <v/>
+      </c>
+      <c r="I4" s="36">
+        <f>I2*I3</f>
+        <v/>
+      </c>
+      <c r="J4" s="36">
+        <f>J2*J3</f>
+        <v/>
+      </c>
+      <c r="K4" s="36">
+        <f>K2*K3</f>
+        <v/>
+      </c>
+      <c r="L4" s="36">
+        <f>L2*L3</f>
+        <v/>
+      </c>
+      <c r="M4" s="36">
+        <f>M2*M3</f>
+        <v/>
+      </c>
+      <c r="N4" s="36">
+        <f>N2*N3</f>
+        <v/>
+      </c>
+      <c r="O4" s="36">
+        <f>O2*O3</f>
+        <v/>
+      </c>
+      <c r="P4" s="36">
+        <f>P2*P3</f>
+        <v/>
+      </c>
+      <c r="Q4" s="36">
+        <f>Q2*Q3</f>
+        <v/>
+      </c>
+      <c r="R4" s="36">
+        <f>R2*R3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="G5" s="36" t="n"/>
+      <c r="H5" s="36" t="n"/>
+      <c r="I5" s="36" t="n"/>
+      <c r="J5" s="36" t="n"/>
+      <c r="K5" s="37" t="n"/>
+      <c r="L5" s="37" t="n"/>
+      <c r="M5" s="37" t="n"/>
+      <c r="N5" s="38" t="n"/>
+      <c r="O5" s="38" t="n"/>
+      <c r="P5" s="38" t="n"/>
+      <c r="Q5" s="38" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="35" t="inlineStr">
+        <is>
+          <t>VCSH</t>
+        </is>
+      </c>
+      <c r="B6" s="35" t="n"/>
+      <c r="C6" s="39" t="n">
+        <v>14401000000000</v>
+      </c>
+      <c r="D6" s="39" t="n">
+        <v>13913000000000</v>
+      </c>
+      <c r="E6" s="39">
+        <f>$D$6*(($F$6/$D$6)^(1/2))</f>
+        <v/>
+      </c>
+      <c r="F6" s="36">
+        <f>chi_so_tai_chinh!J39</f>
+        <v/>
+      </c>
+      <c r="G6" s="39">
+        <f>$F$6*((J6/$F$6)^(1/4))</f>
+        <v/>
+      </c>
+      <c r="H6" s="39">
+        <f>$F$6*((J6/$F$6)^(2/4))</f>
+        <v/>
+      </c>
+      <c r="I6" s="39">
+        <f>$F$6*((J6/$F$6)^(3/4))</f>
+        <v/>
+      </c>
+      <c r="J6" s="36">
+        <f>chi_so_tai_chinh!K39</f>
+        <v/>
+      </c>
+      <c r="K6" s="39">
+        <f>$J$6*(($N$6/$J$6)^(1/4))</f>
+        <v/>
+      </c>
+      <c r="L6" s="39">
+        <f>$J$6*(($N$6/$J$6)^(2/4))</f>
+        <v/>
+      </c>
+      <c r="M6" s="39">
+        <f>$J$6*(($N$6/$J$6)^(3/4))</f>
+        <v/>
+      </c>
+      <c r="N6" s="36">
+        <f>chi_so_tai_chinh!L39</f>
+        <v/>
+      </c>
+      <c r="O6" s="39">
+        <f>$N$6*(($R$6/$N$6)^(1/4))</f>
+        <v/>
+      </c>
+      <c r="P6" s="39">
+        <f>$N$6*(($R$6/$N$6)^(2/4))</f>
+        <v/>
+      </c>
+      <c r="Q6" s="39">
+        <f>$N$6*(($R$6/$N$6)^(3/4))</f>
+        <v/>
+      </c>
+      <c r="R6" s="36">
+        <f>chi_so_tai_chinh!M39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>LICĐKKS</t>
+        </is>
+      </c>
+      <c r="B7" s="35">
+        <f>chi_so_tai_chinh!I41</f>
+        <v/>
+      </c>
+      <c r="C7" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>BV</t>
+        </is>
+      </c>
+      <c r="B8" s="35" t="n"/>
+      <c r="C8" s="39">
+        <f>C6-C7</f>
+        <v/>
+      </c>
+      <c r="D8" s="39">
+        <f>D6-D7</f>
+        <v/>
+      </c>
+      <c r="E8" s="39">
+        <f>E6-E7</f>
+        <v/>
+      </c>
+      <c r="F8" s="39">
+        <f>F6-F7</f>
+        <v/>
+      </c>
+      <c r="G8" s="39">
+        <f>G6-G7</f>
+        <v/>
+      </c>
+      <c r="H8" s="39">
+        <f>H6-H7</f>
+        <v/>
+      </c>
+      <c r="I8" s="39">
+        <f>I6-I7</f>
+        <v/>
+      </c>
+      <c r="J8" s="39">
+        <f>J6-J7</f>
+        <v/>
+      </c>
+      <c r="K8" s="39">
+        <f>K6-K7</f>
+        <v/>
+      </c>
+      <c r="L8" s="39">
+        <f>L6-L7</f>
+        <v/>
+      </c>
+      <c r="M8" s="39">
+        <f>M6-M7</f>
+        <v/>
+      </c>
+      <c r="N8" s="39">
+        <f>N6-N7</f>
+        <v/>
+      </c>
+      <c r="O8" s="39">
+        <f>O6-O7</f>
+        <v/>
+      </c>
+      <c r="P8" s="39">
+        <f>P6-P7</f>
+        <v/>
+      </c>
+      <c r="Q8" s="39">
+        <f>Q6-Q7</f>
+        <v/>
+      </c>
+      <c r="R8" s="39">
+        <f>R6-R7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t>BVPS</t>
+        </is>
+      </c>
+      <c r="B9" s="40" t="n"/>
+      <c r="C9" s="41">
+        <f>C8/C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="41">
+        <f>D8/D2</f>
+        <v/>
+      </c>
+      <c r="E9" s="41">
+        <f>E8/E2</f>
+        <v/>
+      </c>
+      <c r="F9" s="41">
+        <f>F8/F2</f>
+        <v/>
+      </c>
+      <c r="G9" s="41">
+        <f>G8/G2</f>
+        <v/>
+      </c>
+      <c r="H9" s="41">
+        <f>H8/H2</f>
+        <v/>
+      </c>
+      <c r="I9" s="41">
+        <f>I8/I2</f>
+        <v/>
+      </c>
+      <c r="J9" s="41">
+        <f>J8/J2</f>
+        <v/>
+      </c>
+      <c r="K9" s="41">
+        <f>K8/K2</f>
+        <v/>
+      </c>
+      <c r="L9" s="41">
+        <f>L8/L2</f>
+        <v/>
+      </c>
+      <c r="M9" s="41">
+        <f>M8/M2</f>
+        <v/>
+      </c>
+      <c r="N9" s="41">
+        <f>N8/N2</f>
+        <v/>
+      </c>
+      <c r="O9" s="41">
+        <f>O8/O2</f>
+        <v/>
+      </c>
+      <c r="P9" s="41">
+        <f>P8/P2</f>
+        <v/>
+      </c>
+      <c r="Q9" s="41">
+        <f>Q8/Q2</f>
+        <v/>
+      </c>
+      <c r="R9" s="41">
+        <f>R8/R2</f>
+        <v/>
+      </c>
+      <c r="S9" s="42" t="n"/>
+      <c r="T9" s="42" t="n"/>
+      <c r="U9" s="42" t="n"/>
+      <c r="V9" s="42" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="40" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="B10" s="40" t="n"/>
+      <c r="C10" s="43">
+        <f>C3/C9</f>
+        <v/>
+      </c>
+      <c r="D10" s="43">
+        <f>D3/D9</f>
+        <v/>
+      </c>
+      <c r="E10" s="43">
+        <f>E3/E9</f>
+        <v/>
+      </c>
+      <c r="F10" s="43">
+        <f>F3/F9</f>
+        <v/>
+      </c>
+      <c r="G10" s="43">
+        <f>G3/G9</f>
+        <v/>
+      </c>
+      <c r="H10" s="43">
+        <f>H3/H9</f>
+        <v/>
+      </c>
+      <c r="I10" s="43">
+        <f>I3/I9</f>
+        <v/>
+      </c>
+      <c r="J10" s="43">
+        <f>J3/J9</f>
+        <v/>
+      </c>
+      <c r="K10" s="43">
+        <f>K3/K9</f>
+        <v/>
+      </c>
+      <c r="L10" s="43">
+        <f>L3/L9</f>
+        <v/>
+      </c>
+      <c r="M10" s="43">
+        <f>M3/M9</f>
+        <v/>
+      </c>
+      <c r="N10" s="43">
+        <f>N3/N9</f>
+        <v/>
+      </c>
+      <c r="O10" s="43">
+        <f>O3/O9</f>
+        <v/>
+      </c>
+      <c r="P10" s="43">
+        <f>P3/P9</f>
+        <v/>
+      </c>
+      <c r="Q10" s="43">
+        <f>Q3/Q9</f>
+        <v/>
+      </c>
+      <c r="R10" s="43">
+        <f>R3/R9</f>
+        <v/>
+      </c>
+      <c r="S10" s="42" t="n"/>
+      <c r="T10" s="42" t="n"/>
+      <c r="U10" s="42" t="n"/>
+      <c r="V10" s="42" t="n"/>
+    </row>
+    <row r="11">
+      <c r="C11" s="44" t="n"/>
+      <c r="D11" s="44" t="n"/>
+      <c r="E11" s="44" t="n"/>
+      <c r="F11" s="44" t="n"/>
+      <c r="I11" s="42" t="n"/>
+      <c r="J11" s="42" t="n"/>
+      <c r="K11" s="42" t="n"/>
+      <c r="L11" s="42" t="n"/>
+      <c r="M11" s="42" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>Trailing Earning</t>
+        </is>
+      </c>
+      <c r="B12" s="39" t="n">
+        <v>2828000000000</v>
+      </c>
+      <c r="C12" s="39">
+        <f>$B$12*(($F$12/$B$12)^(1/4))</f>
+        <v/>
+      </c>
+      <c r="D12" s="39">
+        <f>$B$12*(($F$12/$B$12)^(2/4))</f>
+        <v/>
+      </c>
+      <c r="E12" s="39">
+        <f>$B$12*(($F$12/$B$12)^(3/4))</f>
+        <v/>
+      </c>
+      <c r="F12" s="39" t="n">
+        <v>800000000000</v>
+      </c>
+      <c r="G12" s="39">
+        <f>$F$12*(($J$12/$F$12)^(1/4))</f>
+        <v/>
+      </c>
+      <c r="H12" s="39">
+        <f>$F$12*(($J$12/$F$12)^(2/4))</f>
+        <v/>
+      </c>
+      <c r="I12" s="39">
+        <f>$F$12*(($J$12/$F$12)^(3/4))</f>
+        <v/>
+      </c>
+      <c r="J12" s="39">
+        <f>chi_so_tai_chinh!K54</f>
+        <v/>
+      </c>
+      <c r="K12" s="39">
+        <f>$J$12*(($N$12/$J$12)^(1/4))</f>
+        <v/>
+      </c>
+      <c r="L12" s="39">
+        <f>$J$12*(($N$12/$J$12)^(2/4))</f>
+        <v/>
+      </c>
+      <c r="M12" s="39">
+        <f>$J$12*(($N$12/$J$12)^(3/4))</f>
+        <v/>
+      </c>
+      <c r="N12" s="39">
+        <f>chi_so_tai_chinh!L54</f>
+        <v/>
+      </c>
+      <c r="O12" s="39">
+        <f>$N$12*(($R$12/$N$12)^(1/4))</f>
+        <v/>
+      </c>
+      <c r="P12" s="39">
+        <f>$N$12*(($R$12/$N$12)^(2/4))</f>
+        <v/>
+      </c>
+      <c r="Q12" s="39">
+        <f>$N$12*(($R$12/$N$12)^(3/4))</f>
+        <v/>
+      </c>
+      <c r="R12" s="39">
+        <f>chi_so_tai_chinh!M54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="40" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B13" s="41">
+        <f>B12/B2</f>
+        <v/>
+      </c>
+      <c r="C13" s="41">
+        <f>C12/C2</f>
+        <v/>
+      </c>
+      <c r="D13" s="41">
+        <f>D12/D2</f>
+        <v/>
+      </c>
+      <c r="E13" s="41">
+        <f>E12/E2</f>
+        <v/>
+      </c>
+      <c r="F13" s="41">
+        <f>F12/F2</f>
+        <v/>
+      </c>
+      <c r="G13" s="41">
+        <f>G12/G2</f>
+        <v/>
+      </c>
+      <c r="H13" s="41">
+        <f>H12/H2</f>
+        <v/>
+      </c>
+      <c r="I13" s="41">
+        <f>I12/I2</f>
+        <v/>
+      </c>
+      <c r="J13" s="41">
+        <f>J12/J2</f>
+        <v/>
+      </c>
+      <c r="K13" s="41">
+        <f>K12/K2</f>
+        <v/>
+      </c>
+      <c r="L13" s="41">
+        <f>L12/L2</f>
+        <v/>
+      </c>
+      <c r="M13" s="41">
+        <f>M12/M2</f>
+        <v/>
+      </c>
+      <c r="N13" s="41">
+        <f>N12/N2</f>
+        <v/>
+      </c>
+      <c r="O13" s="41">
+        <f>O12/O2</f>
+        <v/>
+      </c>
+      <c r="P13" s="41">
+        <f>P12/P2</f>
+        <v/>
+      </c>
+      <c r="Q13" s="41">
+        <f>Q12/Q2</f>
+        <v/>
+      </c>
+      <c r="R13" s="41">
+        <f>R12/R2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="40" t="inlineStr">
+        <is>
+          <t>PE</t>
+        </is>
+      </c>
+      <c r="B14" s="43">
+        <f>B3/B13</f>
+        <v/>
+      </c>
+      <c r="C14" s="43">
+        <f>C3/C13</f>
+        <v/>
+      </c>
+      <c r="D14" s="43">
+        <f>D3/D13</f>
+        <v/>
+      </c>
+      <c r="E14" s="43">
+        <f>E3/E13</f>
+        <v/>
+      </c>
+      <c r="F14" s="43">
+        <f>F3/F13</f>
+        <v/>
+      </c>
+      <c r="G14" s="43">
+        <f>G3/G13</f>
+        <v/>
+      </c>
+      <c r="H14" s="43">
+        <f>H3/H13</f>
+        <v/>
+      </c>
+      <c r="I14" s="43">
+        <f>I3/I13</f>
+        <v/>
+      </c>
+      <c r="J14" s="43">
+        <f>J3/J13</f>
+        <v/>
+      </c>
+      <c r="K14" s="43">
+        <f>K3/K13</f>
+        <v/>
+      </c>
+      <c r="L14" s="43">
+        <f>L3/L13</f>
+        <v/>
+      </c>
+      <c r="M14" s="43">
+        <f>M3/M13</f>
+        <v/>
+      </c>
+      <c r="N14" s="43">
+        <f>N3/N13</f>
+        <v/>
+      </c>
+      <c r="O14" s="43">
+        <f>O3/O13</f>
+        <v/>
+      </c>
+      <c r="P14" s="43">
+        <f>P3/P13</f>
+        <v/>
+      </c>
+      <c r="Q14" s="43">
+        <f>Q3/Q13</f>
+        <v/>
+      </c>
+      <c r="R14" s="43">
+        <f>R3/R13</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25.375" customWidth="1" min="1" max="1"/>
+    <col width="17.125" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="45" t="n"/>
+      <c r="B1" s="45" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C1" s="45" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D1" s="45" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E1" s="45" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="45" t="inlineStr">
+        <is>
+          <t>Doanh thu kế hoạch</t>
+        </is>
+      </c>
+      <c r="B2" s="46" t="n">
+        <v>25834930000000</v>
+      </c>
+      <c r="C2" s="46" t="n">
+        <v>35597952000000</v>
+      </c>
+      <c r="D2" s="46" t="n">
+        <v>37147627000000</v>
+      </c>
+      <c r="E2" s="46" t="n">
+        <v>31606954000000</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="45" t="inlineStr">
+        <is>
+          <t>DT thực hiện</t>
+        </is>
+      </c>
+      <c r="B3" s="46">
+        <f>chi_so_tai_chinh!F44</f>
+        <v/>
+      </c>
+      <c r="C3" s="46">
+        <f>chi_so_tai_chinh!G44</f>
+        <v/>
+      </c>
+      <c r="D3" s="46">
+        <f>chi_so_tai_chinh!H44</f>
+        <v/>
+      </c>
+      <c r="E3" s="46">
+        <f>chi_so_tai_chinh!I44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="47" t="inlineStr">
+        <is>
+          <t>%thực hiện</t>
+        </is>
+      </c>
+      <c r="B4" s="48">
+        <f>B3/B2</f>
+        <v/>
+      </c>
+      <c r="C4" s="48">
+        <f>C3/C2</f>
+        <v/>
+      </c>
+      <c r="D4" s="48">
+        <f>D3/D2</f>
+        <v/>
+      </c>
+      <c r="E4" s="48">
+        <f>E3/E2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="45" t="inlineStr">
+        <is>
+          <t>Lợi nhuận trước thuế kế hoạch</t>
+        </is>
+      </c>
+      <c r="B5" s="46" t="n">
+        <v>1640396000000</v>
+      </c>
+      <c r="C5" s="46" t="n">
+        <v>2473882000000</v>
+      </c>
+      <c r="D5" s="46" t="n">
+        <v>2637880000000</v>
+      </c>
+      <c r="E5" s="46" t="n">
+        <v>2474805000000</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="45" t="inlineStr">
+        <is>
+          <t>LN trước thuế KH</t>
+        </is>
+      </c>
+      <c r="B6" s="46">
+        <f>chi_so_tai_chinh!F51</f>
+        <v/>
+      </c>
+      <c r="C6" s="46">
+        <f>chi_so_tai_chinh!G51</f>
+        <v/>
+      </c>
+      <c r="D6" s="46">
+        <f>chi_so_tai_chinh!H51</f>
+        <v/>
+      </c>
+      <c r="E6" s="46">
+        <f>chi_so_tai_chinh!I51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="47" t="inlineStr">
+        <is>
+          <t>%thực hiện</t>
+        </is>
+      </c>
+      <c r="B7" s="48">
+        <f>B6/B5</f>
+        <v/>
+      </c>
+      <c r="C7" s="48">
+        <f>C6/C5</f>
+        <v/>
+      </c>
+      <c r="D7" s="48">
+        <f>D6/D5</f>
+        <v/>
+      </c>
+      <c r="E7" s="48">
+        <f>E6/E5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="45" t="inlineStr">
+        <is>
+          <t>Lợi nhuận sau thuế kế hoạch</t>
+        </is>
+      </c>
+      <c r="B8" s="46" t="n">
+        <v>1319573000000</v>
+      </c>
+      <c r="C8" s="46" t="n">
+        <v>1937198000000</v>
+      </c>
+      <c r="D8" s="46" t="n">
+        <v>2089201000000</v>
+      </c>
+      <c r="E8" s="46" t="n">
+        <v>1959650000000</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="45" t="inlineStr">
+        <is>
+          <t>LNST thực hiện</t>
+        </is>
+      </c>
+      <c r="B9" s="46">
+        <f>chi_so_tai_chinh!F52</f>
+        <v/>
+      </c>
+      <c r="C9" s="46">
+        <f>chi_so_tai_chinh!G52</f>
+        <v/>
+      </c>
+      <c r="D9" s="46">
+        <f>chi_so_tai_chinh!H52</f>
+        <v/>
+      </c>
+      <c r="E9" s="46">
+        <f>chi_so_tai_chinh!I52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="47" t="inlineStr">
+        <is>
+          <t>%thực hiện</t>
+        </is>
+      </c>
+      <c r="B10" s="48">
+        <f>B9/B8</f>
+        <v/>
+      </c>
+      <c r="C10" s="48">
+        <f>C9/C8</f>
+        <v/>
+      </c>
+      <c r="D10" s="48">
+        <f>D9/D8</f>
+        <v/>
+      </c>
+      <c r="E10" s="48">
+        <f>E9/E8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="45" t="n"/>
+      <c r="B11" s="45" t="n"/>
+      <c r="C11" s="45" t="n"/>
+      <c r="D11" s="45" t="n"/>
+      <c r="E11" s="45" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="45" t="n"/>
+      <c r="B12" s="45" t="n"/>
+      <c r="C12" s="45" t="n"/>
+      <c r="D12" s="45" t="n"/>
+      <c r="E12" s="45" t="n"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="47" t="inlineStr">
+        <is>
+          <t>Trung vị %thực hiện DT</t>
+        </is>
+      </c>
+      <c r="B13" s="48">
+        <f>MEDIAN(B4:D4)</f>
+        <v/>
+      </c>
+      <c r="C13" s="45" t="n"/>
+      <c r="D13" s="45" t="n"/>
+      <c r="E13" s="45" t="n"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="47" t="inlineStr">
+        <is>
+          <t>Trung vị %thực hiện LNTT</t>
+        </is>
+      </c>
+      <c r="B14" s="48">
+        <f>MEDIAN(B7:D7)</f>
+        <v/>
+      </c>
+      <c r="C14" s="45" t="n"/>
+      <c r="D14" s="45" t="n"/>
+      <c r="E14" s="45" t="n"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="47" t="inlineStr">
+        <is>
+          <t>Trung vị %thực hiện LNST</t>
+        </is>
+      </c>
+      <c r="B15" s="48">
+        <f>MEDIAN(B10:D10)</f>
+        <v/>
+      </c>
+      <c r="C15" s="45" t="n"/>
+      <c r="D15" s="45" t="n"/>
+      <c r="E15" s="45" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="45" t="n"/>
+      <c r="B16" s="45" t="n"/>
+      <c r="C16" s="45" t="n"/>
+      <c r="D16" s="45" t="n"/>
+      <c r="E16" s="45" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="45" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành DT trên 95%</t>
+        </is>
+      </c>
+      <c r="B17" s="49">
+        <f>COUNTIF(B4:F4,"&gt;=95%")/COUNT(B4:F4)</f>
+        <v/>
+      </c>
+      <c r="C17" s="45" t="n"/>
+      <c r="D17" s="45" t="n"/>
+      <c r="E17" s="45" t="n"/>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="45" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành LNST trên 95%</t>
+        </is>
+      </c>
+      <c r="B18" s="49">
+        <f>COUNTIF(B7:F7,"&gt;=95%")/COUNT(B7:F7)</f>
+        <v/>
+      </c>
+      <c r="C18" s="45" t="n"/>
+      <c r="D18" s="45" t="n"/>
+      <c r="E18" s="45" t="n"/>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="45" t="inlineStr">
+        <is>
+          <t>Tỷ lệ hoàn thành LNTT trên 95%</t>
+        </is>
+      </c>
+      <c r="B19" s="49">
+        <f>COUNTIF(B10:F10,"&gt;=95%")/COUNT(B10:F10)</f>
+        <v/>
+      </c>
+      <c r="C19" s="45" t="n"/>
+      <c r="D19" s="45" t="n"/>
+      <c r="E19" s="45" t="n"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B13:B15">
+    <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="3">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4:E4">
+    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" dxfId="3">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:E7">
+    <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" dxfId="3">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10:E10">
+    <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" dxfId="3">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/financials/PNJ/PNJ.xlsx
+++ b/financials/PNJ/PNJ.xlsx
@@ -918,10 +918,18 @@
           <t>Đầu tư ngắn hạn</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
+      <c r="B7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F7" s="4" t="n">
         <v>0</v>
       </c>
@@ -1283,16 +1291,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>0</v>
+        <v>75193220197</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0</v>
+        <v>78031361551</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0</v>
+        <v>76790981951</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0</v>
+        <v>70025928617</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>0</v>
@@ -1406,10 +1414,18 @@
           <t>Tài sản lưu động khác</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr"/>
-      <c r="C23" s="4" t="inlineStr"/>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr"/>
+      <c r="B23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F23" s="4" t="n">
         <v>0</v>
       </c>
@@ -2298,16 +2314,16 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>0</v>
+        <v>85351824838</v>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0</v>
+        <v>88231580067</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>0</v>
+        <v>90983694027</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0</v>
+        <v>100468793615</v>
       </c>
       <c r="F52" s="4" t="n">
         <v>0</v>
@@ -2948,10 +2964,18 @@
           <t>Thuế thu nhập hoãn lại</t>
         </is>
       </c>
-      <c r="B73" s="4" t="inlineStr"/>
-      <c r="C73" s="4" t="inlineStr"/>
-      <c r="D73" s="4" t="inlineStr"/>
-      <c r="E73" s="4" t="inlineStr"/>
+      <c r="B73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F73" s="4" t="n">
         <v>0</v>
       </c>
@@ -3963,10 +3987,18 @@
           <t>Đầu tư nắm giữ đến ngày đáo hạn</t>
         </is>
       </c>
-      <c r="B106" s="4" t="inlineStr"/>
-      <c r="C106" s="4" t="inlineStr"/>
-      <c r="D106" s="4" t="inlineStr"/>
-      <c r="E106" s="4" t="inlineStr"/>
+      <c r="B106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F106" s="4" t="n">
         <v>0</v>
       </c>
@@ -4234,10 +4266,18 @@
           <t>Cổ phiếu ưu đãi</t>
         </is>
       </c>
-      <c r="B115" s="4" t="inlineStr"/>
-      <c r="C115" s="4" t="inlineStr"/>
-      <c r="D115" s="4" t="inlineStr"/>
-      <c r="E115" s="4" t="inlineStr"/>
+      <c r="B115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="F115" s="4" t="n">
         <v>0</v>
       </c>
